--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>350009</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>799698</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.764999985694885</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.748000025749207</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.748000025749207</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1320555</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>957905</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.781000018119812</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>303180</v>
+        <v>531528</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.758000016212463</v>
+        <v>0.763000011444092</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.735000014305115</v>
+        <v>0.745999991893768</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.735000014305115</v>
+        <v>0.749000012874603</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.754000008106232</v>
+        <v>0.751999974250793</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1192762</v>
+        <v>303180</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.763999998569489</v>
+        <v>0.758000016212463</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.737999975681305</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.763999998569489</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.737999975681305</v>
+        <v>0.754000008106232</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1409756</v>
+        <v>1192762</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.782999992370605</v>
+        <v>0.763999998569489</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.735000014305115</v>
+        <v>0.737999975681305</v>
       </c>
       <c r="E2717" t="n">
+        <v>0.763999998569489</v>
+      </c>
+      <c r="F2717" t="n">
         <v>0.737999975681305</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>0.759999990463257</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>478137</v>
+        <v>1409756</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.777999997138977</v>
+        <v>0.782999992370605</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.73199999332428</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.73199999332428</v>
+        <v>0.737999975681305</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.76800000667572</v>
+        <v>0.759999990463257</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>350009</v>
+        <v>478137</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.773999989032745</v>
+        <v>0.777999997138977</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.745000004768372</v>
+        <v>0.73199999332428</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.745000004768372</v>
+        <v>0.73199999332428</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.755999982357025</v>
+        <v>0.76800000667572</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>799698</v>
+        <v>350009</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.764999985694885</v>
+        <v>0.773999989032745</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.748000025749207</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.748000025749207</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="F2720" t="n">
         <v>0.755999982357025</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1320555</v>
+        <v>799698</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.773999989032745</v>
+        <v>0.764999985694885</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.75</v>
+        <v>0.748000025749207</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.75</v>
+        <v>0.748000025749207</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.762000024318695</v>
+        <v>0.755999982357025</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>957905</v>
+        <v>1320555</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.781000018119812</v>
+        <v>0.773999989032745</v>
       </c>
       <c r="D2722" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F2722" t="n">
         <v>0.762000024318695</v>
       </c>
-      <c r="E2722" t="n">
-        <v>0.762000024318695</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>0.774999976158142</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1098110</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.75900000333786</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.773000001907349</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.763000011444092</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.376928627490997</v>
+        <v>0.37692865729332</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849780082703</v>
+        <v>0.366849839687347</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198314905167</v>
+        <v>0.358198344707489</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.365433990955353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.325999289751053</v>
+        <v>0.325999319553375</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272104978561</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.363934010267258</v>
       </c>
       <c r="G20" t="n">
-        <v>0.32466122508049</v>
+        <v>0.324661195278168</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358264923096</v>
+        <v>0.307358235120773</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696359395981</v>
+        <v>0.308696389198303</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998284101486</v>
+        <v>0.292998313903809</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28283029794693</v>
+        <v>0.282830268144608</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.326041013002396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.290857315063477</v>
+        <v>0.290857285261154</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984805345535</v>
+        <v>0.288984835147858</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.331440001726151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.295673668384552</v>
+        <v>0.295673698186874</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.29174941778183</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335573911667</v>
+        <v>0.294335544109344</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.290054440498352</v>
+        <v>0.29005441069603</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500491857529</v>
+        <v>0.290500462055206</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720248699188</v>
+        <v>0.302720278501511</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166300058365</v>
+        <v>0.303166329860687</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560610532761</v>
+        <v>0.301560550928116</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471322774887</v>
+        <v>0.301471352577209</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229546546936</v>
+        <v>0.328229516744614</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37014964222908</v>
+        <v>0.370149672031403</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.38290473818779</v>
+        <v>0.382904708385468</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806297779083</v>
+        <v>0.373806327581406</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178721904755</v>
+        <v>0.359178751707077</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G71" t="n">
-        <v>0.355432897806168</v>
+        <v>0.355432868003845</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376801013947</v>
+        <v>0.358376771211624</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579116821289</v>
+        <v>0.352579087018967</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354184001684189</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306301593781</v>
+        <v>0.357306271791458</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G82" t="n">
-        <v>0.355432897806168</v>
+        <v>0.355432868003845</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157960414886</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332602739334</v>
+        <v>0.372332632541656</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701585292816</v>
+        <v>0.372701615095139</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.371502429246902</v>
+        <v>0.37150239944458</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36430898308754</v>
+        <v>0.364309012889862</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.33783882856369</v>
+        <v>0.337838798761368</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455947399139</v>
+        <v>0.317455977201462</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567800283432</v>
+        <v>0.312567830085754</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843703985214</v>
+        <v>0.331843733787537</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935912370682</v>
+        <v>0.331935942173004</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417677879333</v>
+        <v>0.308417648077011</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761246442795</v>
+        <v>0.319761216640472</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660098075867</v>
+        <v>0.312660068273544</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305824995041</v>
+        <v>0.313305795192719</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.31182986497879</v>
+        <v>0.311829835176468</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.323543339967728</v>
+        <v>0.32354336977005</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484555482864</v>
+        <v>0.338484525680542</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G206" t="n">
-        <v>0.340605288743973</v>
+        <v>0.340605318546295</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G207" t="n">
-        <v>0.340605288743973</v>
+        <v>0.340605318546295</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027339696884</v>
+        <v>0.351027369499207</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071468114853</v>
+        <v>0.354071438312531</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837928295135</v>
+        <v>0.356837958097458</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558049440384</v>
+        <v>0.324558079242706</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344154119492</v>
+        <v>0.322344124317169</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183267593384</v>
+        <v>0.330183297395706</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.319116413593292</v>
+        <v>0.31911638379097</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397192716599</v>
+        <v>0.332397162914276</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.350473880767822</v>
+        <v>0.3504738509655</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595537900925</v>
+        <v>0.352595508098602</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105822086334</v>
+        <v>0.350105792284012</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396292448044</v>
+        <v>0.351396322250366</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342436790466</v>
+        <v>0.379342466592789</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370961666107</v>
+        <v>0.38137099146843</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.410425990819931</v>
       </c>
       <c r="G276" t="n">
-        <v>0.378604471683502</v>
+        <v>0.37860444188118</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.407326996326447</v>
       </c>
       <c r="G282" t="n">
-        <v>0.375745743513107</v>
+        <v>0.37574577331543</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744902849197</v>
+        <v>0.394744873046875</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927668094635</v>
+        <v>0.432927638292313</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757841587067</v>
+        <v>0.433757871389389</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340749263763</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403621912003</v>
+        <v>0.453403651714325</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.488819926977158</v>
+        <v>0.48881995677948</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265508174896</v>
+        <v>0.507265567779541</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.47544601559639</v>
+        <v>0.475445985794067</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286052942276</v>
+        <v>0.483286023139954</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511876940727234</v>
+        <v>0.511877000331879</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841888904572</v>
+        <v>0.553841829299927</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718454837799</v>
+        <v>0.608718514442444</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>0.690375983715057</v>
       </c>
       <c r="G334" t="n">
-        <v>0.636849105358124</v>
+        <v>0.636849164962769</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999317169189</v>
+        <v>0.640999376773834</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076875686646</v>
+        <v>0.640076816082001</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553706169128</v>
+        <v>0.622553646564484</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942214012146</v>
+        <v>0.617942273616791</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863821029663</v>
+        <v>0.618863761425018</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607797026634216</v>
+        <v>0.607796967029572</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.6243976354599</v>
+        <v>0.624397695064545</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465383529663</v>
+        <v>0.635465443134308</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019772529602</v>
+        <v>0.617019712924957</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179735183716</v>
+        <v>0.609179794788361</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G362" t="n">
-        <v>0.612408339977264</v>
+        <v>0.612408399581909</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G363" t="n">
-        <v>0.612408339977264</v>
+        <v>0.612408399581909</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829379081726</v>
+        <v>0.608829319477081</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.61307030916214</v>
+        <v>0.613070249557495</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969201564789</v>
+        <v>0.581969141960144</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.57395875453949</v>
+        <v>0.573958694934845</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152719497681</v>
+        <v>0.587152659893036</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555260181427</v>
+        <v>0.580555200576782</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741868972778</v>
+        <v>0.544741928577423</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396740436554</v>
+        <v>0.550396800041199</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040091991425</v>
+        <v>0.548040151596069</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731421947479</v>
+        <v>0.536731362342834</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454092979431</v>
+        <v>0.549454033374786</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.542386293411255</v>
+        <v>0.54238623380661</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.52447909116745</v>
+        <v>0.524479150772095</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180927753448</v>
+        <v>0.521180868148804</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720021247864</v>
+        <v>0.528720080852509</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645861148834</v>
+        <v>0.603645801544189</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807531356812</v>
+        <v>0.592807471752167</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577048301697</v>
+        <v>0.596577107906342</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.595163106918335</v>
+        <v>0.59516316652298</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772026538849</v>
+        <v>0.609772086143494</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876224994659</v>
+        <v>0.599876284599304</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947294235229</v>
+        <v>0.565947234630585</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533352851868</v>
+        <v>0.564533293247223</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.53767317533493</v>
+        <v>0.537673115730286</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100714206696</v>
+        <v>0.506100654602051</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997350215912</v>
+        <v>0.515997409820557</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194525241852</v>
+        <v>0.488194495439529</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.51222687959671</v>
+        <v>0.512226819992065</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.518352925777435</v>
+        <v>0.51835298538208</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.493849337100983</v>
+        <v>0.49384930729866</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539623975754</v>
+        <v>0.482539653778076</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770077228546</v>
+        <v>0.478770047426224</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.48913711309433</v>
+        <v>0.489137142896652</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931717634201</v>
+        <v>0.467931687831879</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909840106964</v>
+        <v>0.451909810304642</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469816029071808</v>
+        <v>0.469815999269485</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>0.77700001001358</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>1050616</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.773000001907349</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.773000001907349</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.782999992370605</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.782999992370605</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37692865729332</v>
+        <v>0.376928627490997</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984724283218</v>
+        <v>0.373984754085541</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.36354997754097</v>
+        <v>0.363550007343292</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.376531988382339</v>
       </c>
       <c r="G13" t="n">
-        <v>0.33589968085289</v>
+        <v>0.335899710655212</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.354936003684998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316634178161621</v>
+        <v>0.316634207963943</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.365433990955353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.325999319553375</v>
+        <v>0.325999289751053</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012857913971</v>
+        <v>0.330012828111649</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272104978561</v>
+        <v>0.321272134780884</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.363934010267258</v>
       </c>
       <c r="G20" t="n">
-        <v>0.324661195278168</v>
+        <v>0.324661165475845</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671605825424</v>
+        <v>0.314671576023102</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979614973068</v>
+        <v>0.293979585170746</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830268144608</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984835147858</v>
+        <v>0.288984805345535</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.29174941778183</v>
+        <v>0.291749387979507</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114529371262</v>
+        <v>0.301114499568939</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289875984191895</v>
+        <v>0.289876013994217</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311625003815</v>
+        <v>0.300311654806137</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.30120375752449</v>
+        <v>0.301203727722168</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471352577209</v>
+        <v>0.301471322774887</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007637739182</v>
+        <v>0.335007607936859</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822822570801</v>
+        <v>0.358822792768478</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736722230911</v>
+        <v>0.372736692428589</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993936538696</v>
+        <v>0.382993906736374</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063541889191</v>
+        <v>0.384063571691513</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806327581406</v>
+        <v>0.373806297779083</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3575738966465</v>
+        <v>0.357573926448822</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178751707077</v>
+        <v>0.359178721904755</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579087018967</v>
+        <v>0.352579116821289</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183942079544</v>
+        <v>0.354183971881866</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122625112534</v>
+        <v>0.362122654914856</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157960414886</v>
+        <v>0.379157930612564</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.396589815616608</v>
+        <v>0.39658984541893</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027363300323</v>
+        <v>0.370027393102646</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.37150239944458</v>
+        <v>0.371502429246902</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.404626995325089</v>
       </c>
       <c r="G93" t="n">
-        <v>0.373255103826523</v>
+        <v>0.3732550740242</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920385837555</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.386929988861084</v>
       </c>
       <c r="G100" t="n">
-        <v>0.356930196285248</v>
+        <v>0.356930166482925</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304084062576</v>
+        <v>0.351304054260254</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.35065832734108</v>
+        <v>0.350658357143402</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.390929996967316</v>
       </c>
       <c r="G105" t="n">
-        <v>0.360620051622391</v>
+        <v>0.360620081424713</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.364309012889862</v>
+        <v>0.36430898308754</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313918113708</v>
+        <v>0.358313888311386</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513103961945</v>
+        <v>0.359513133764267</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.344238013029099</v>
       </c>
       <c r="G125" t="n">
-        <v>0.317548245191574</v>
+        <v>0.317548215389252</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169452190399</v>
+        <v>0.329169422388077</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420835971832</v>
+        <v>0.359420865774155</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886932134628</v>
+        <v>0.353886961936951</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163706302643</v>
+        <v>0.354163736104965</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.344756424427032</v>
+        <v>0.34475639462471</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.381830990314484</v>
       </c>
       <c r="G149" t="n">
-        <v>0.35222652554512</v>
+        <v>0.352226495742798</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619998216629</v>
+        <v>0.341619968414307</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712296009064</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843733787537</v>
+        <v>0.331843703985214</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212656736374</v>
+        <v>0.332212686538696</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.356635987758636</v>
       </c>
       <c r="G160" t="n">
-        <v>0.328984975814819</v>
+        <v>0.328984946012497</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382423639297</v>
+        <v>0.331382483243942</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309859752655</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761216640472</v>
+        <v>0.319761246442795</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660068273544</v>
+        <v>0.312660098075867</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.311829835176468</v>
+        <v>0.31182986497879</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.33643901348114</v>
       </c>
       <c r="G193" t="n">
-        <v>0.31035390496254</v>
+        <v>0.310353934764862</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.32354336977005</v>
+        <v>0.323543339967728</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484525680542</v>
+        <v>0.338484555482864</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G206" t="n">
-        <v>0.340605318546295</v>
+        <v>0.340605288743973</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G207" t="n">
-        <v>0.340605318546295</v>
+        <v>0.340605288743973</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027369499207</v>
+        <v>0.351027339696884</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071438312531</v>
+        <v>0.354071497917175</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333532810211</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998785018921</v>
+        <v>0.348998814821243</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751465797424</v>
+        <v>0.331751435995102</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.32612532377243</v>
+        <v>0.326125353574753</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897642850876</v>
+        <v>0.322897613048553</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328247010707855</v>
+        <v>0.328246980905533</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558079242706</v>
+        <v>0.324558049440384</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344124317169</v>
+        <v>0.322344154119492</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183297395706</v>
+        <v>0.330183267593384</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.31911638379097</v>
+        <v>0.319116413593292</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712296009064</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018429517746</v>
+        <v>0.344018399715424</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.377131998538971</v>
       </c>
       <c r="G250" t="n">
-        <v>0.347891867160797</v>
+        <v>0.34789189696312</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241235017776</v>
+        <v>0.353241264820099</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595508098602</v>
+        <v>0.352595537900925</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429829359055</v>
+        <v>0.385429799556732</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.37094983458519</v>
+        <v>0.370949864387512</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G267" t="n">
-        <v>0.380910634994507</v>
+        <v>0.380910664796829</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.412326008081436</v>
       </c>
       <c r="G272" t="n">
-        <v>0.380357176065445</v>
+        <v>0.380357146263123</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.38137099146843</v>
+        <v>0.381370931863785</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.410425990819931</v>
       </c>
       <c r="G276" t="n">
-        <v>0.37860444188118</v>
+        <v>0.378604471683502</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920385837555</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.407326996326447</v>
       </c>
       <c r="G282" t="n">
-        <v>0.37574577331543</v>
+        <v>0.375745743513107</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085336923599</v>
+        <v>0.374085307121277</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531818389893</v>
+        <v>0.373531848192215</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744873046875</v>
+        <v>0.394744902849197</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714666843414</v>
+        <v>0.430714637041092</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340779066086</v>
+        <v>0.436340808868408</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321194171906</v>
+        <v>0.441321164369583</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145651578903</v>
+        <v>0.467145621776581</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>0.524406015872955</v>
       </c>
       <c r="G303" t="n">
-        <v>0.48374730348587</v>
+        <v>0.483747273683548</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475445985794067</v>
+        <v>0.475446045398712</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286023139954</v>
+        <v>0.483286082744598</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774081230164</v>
+        <v>0.542774140834808</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495649337769</v>
+        <v>0.599495708942413</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267998218536</v>
+        <v>0.596267938613892</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.65488201379776</v>
       </c>
       <c r="G328" t="n">
-        <v>0.604107081890106</v>
+        <v>0.604107141494751</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>0.690375983715057</v>
       </c>
       <c r="G334" t="n">
-        <v>0.636849164962769</v>
+        <v>0.636849105358124</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634542942047119</v>
+        <v>0.634543001651764</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999376773834</v>
+        <v>0.640999317169189</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076816082001</v>
+        <v>0.64007693529129</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.62808758020401</v>
+        <v>0.628087520599365</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553646564484</v>
+        <v>0.622553706169128</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863761425018</v>
+        <v>0.618863821029663</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651720046997</v>
+        <v>0.597651660442352</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617481052875519</v>
+        <v>0.617480993270874</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.624397695064545</v>
+        <v>0.6243976354599</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465443134308</v>
+        <v>0.635465383529663</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165079116821</v>
+        <v>0.627165138721466</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019712924957</v>
+        <v>0.617019772529602</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179794788361</v>
+        <v>0.609179735183716</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G362" t="n">
-        <v>0.612408399581909</v>
+        <v>0.612408339977264</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G363" t="n">
-        <v>0.612408399581909</v>
+        <v>0.612408339977264</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645861148834</v>
+        <v>0.603645801544189</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>0.782999992370605</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>292780</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.787000000476837</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.767000019550323</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849839687347</v>
+        <v>0.366849809885025</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198344707489</v>
+        <v>0.358198314905167</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.354936003684998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316634207963943</v>
+        <v>0.316634178161621</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012828111649</v>
+        <v>0.330012857913971</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272104978561</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450531482697</v>
+        <v>0.321450561285019</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.363934010267258</v>
       </c>
       <c r="G20" t="n">
-        <v>0.324661165475845</v>
+        <v>0.324661195278168</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979585170746</v>
+        <v>0.293979614973068</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28283029794693</v>
+        <v>0.282830268144608</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984805345535</v>
+        <v>0.288984835147858</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.29174941778183</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114499568939</v>
+        <v>0.301114559173584</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335544109344</v>
+        <v>0.294335573911667</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500462055206</v>
+        <v>0.290500491857529</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311654806137</v>
+        <v>0.300311625003815</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.301203727722168</v>
+        <v>0.30120375752449</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560550928116</v>
+        <v>0.301560580730438</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471322774887</v>
+        <v>0.301471352577209</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869625329971</v>
+        <v>0.313869595527649</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229516744614</v>
+        <v>0.328229486942291</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822792768478</v>
+        <v>0.358822822570801</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736692428589</v>
+        <v>0.372736722230911</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993966341019</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063571691513</v>
+        <v>0.384063541889191</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806297779083</v>
+        <v>0.373806327581406</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203564882278</v>
+        <v>0.353203535079956</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.397127985954285</v>
       </c>
       <c r="G67" t="n">
-        <v>0.35427314043045</v>
+        <v>0.354273170232773</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573926448822</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579116821289</v>
+        <v>0.352579087018967</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183971881866</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.396028995513916</v>
       </c>
       <c r="G79" t="n">
-        <v>0.353292763233185</v>
+        <v>0.353292793035507</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122654914856</v>
+        <v>0.362122625112534</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060443878174</v>
+        <v>0.370060414075851</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.39658984541893</v>
+        <v>0.396589815616608</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332632541656</v>
+        <v>0.372332602739334</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701615095139</v>
+        <v>0.372701585292816</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027393102646</v>
+        <v>0.370027363300323</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.404626995325089</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3732550740242</v>
+        <v>0.373255103826523</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.368920385837555</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.386929988861084</v>
       </c>
       <c r="G100" t="n">
-        <v>0.356930166482925</v>
+        <v>0.356930196285248</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304054260254</v>
+        <v>0.351304084062576</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.350658357143402</v>
+        <v>0.35065832734108</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.390929996967316</v>
       </c>
       <c r="G105" t="n">
-        <v>0.360620081424713</v>
+        <v>0.360620051622391</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313888311386</v>
+        <v>0.358313918113708</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.337838798761368</v>
+        <v>0.33783882856369</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513133764267</v>
+        <v>0.359513103961945</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.344238013029099</v>
       </c>
       <c r="G125" t="n">
-        <v>0.317548215389252</v>
+        <v>0.317548245191574</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455977201462</v>
+        <v>0.317455947399139</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567830085754</v>
+        <v>0.312567800283432</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169422388077</v>
+        <v>0.329169452190399</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420865774155</v>
+        <v>0.359420835971832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886961936951</v>
+        <v>0.353886932134628</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163736104965</v>
+        <v>0.354163706302643</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.34475639462471</v>
+        <v>0.344756424427032</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.381830990314484</v>
       </c>
       <c r="G149" t="n">
-        <v>0.352226495742798</v>
+        <v>0.35222652554512</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619968414307</v>
+        <v>0.341619998216629</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212686538696</v>
+        <v>0.332212656736374</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.356635987758636</v>
       </c>
       <c r="G160" t="n">
-        <v>0.328984946012497</v>
+        <v>0.328984975814819</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382483243942</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935942173004</v>
+        <v>0.331935912370682</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417648077011</v>
+        <v>0.308417677879333</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309829950333</v>
+        <v>0.326309859752655</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305795192719</v>
+        <v>0.313305824995041</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.33643901348114</v>
       </c>
       <c r="G193" t="n">
-        <v>0.310353934764862</v>
+        <v>0.31035390496254</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071497917175</v>
+        <v>0.354071468114853</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837958097458</v>
+        <v>0.356837928295135</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333532810211</v>
+        <v>0.353333503007889</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998814821243</v>
+        <v>0.348998785018921</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751435995102</v>
+        <v>0.331751465797424</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.326125353574753</v>
+        <v>0.32612532377243</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328246980905533</v>
+        <v>0.328247010707855</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397162914276</v>
+        <v>0.332397192716599</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018399715424</v>
+        <v>0.344018429517746</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.377131998538971</v>
       </c>
       <c r="G250" t="n">
-        <v>0.34789189696312</v>
+        <v>0.347891867160797</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241264820099</v>
+        <v>0.353241235017776</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3504738509655</v>
+        <v>0.350473880767822</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105792284012</v>
+        <v>0.350105822086334</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396322250366</v>
+        <v>0.351396292448044</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429799556732</v>
+        <v>0.385429829359055</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609376907349</v>
+        <v>0.372609347105026</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.370949864387512</v>
+        <v>0.37094983458519</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G267" t="n">
-        <v>0.380910664796829</v>
+        <v>0.380910634994507</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342466592789</v>
+        <v>0.379342436790466</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.412326008081436</v>
       </c>
       <c r="G272" t="n">
-        <v>0.380357146263123</v>
+        <v>0.380357176065445</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370931863785</v>
+        <v>0.381370961666107</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.368920385837555</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085307121277</v>
+        <v>0.374085336923599</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531848192215</v>
+        <v>0.373531818389893</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714637041092</v>
+        <v>0.430714666843414</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927638292313</v>
+        <v>0.432927668094635</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757871389389</v>
+        <v>0.433757841587067</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340808868408</v>
+        <v>0.436340749263763</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321164369583</v>
+        <v>0.441321194171906</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403651714325</v>
+        <v>0.453403621912003</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145621776581</v>
+        <v>0.467145651578903</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>0.524406015872955</v>
       </c>
       <c r="G303" t="n">
-        <v>0.483747273683548</v>
+        <v>0.48374730348587</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.48881995677948</v>
+        <v>0.488819926977158</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265567779541</v>
+        <v>0.507265508174896</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475446045398712</v>
+        <v>0.47544601559639</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286082744598</v>
+        <v>0.483286052942276</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511877000331879</v>
+        <v>0.511876940727234</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774140834808</v>
+        <v>0.542774081230164</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841829299927</v>
+        <v>0.553841888904572</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495708942413</v>
+        <v>0.599495649337769</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267938613892</v>
+        <v>0.596267998218536</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.65488201379776</v>
       </c>
       <c r="G328" t="n">
-        <v>0.604107141494751</v>
+        <v>0.604107081890106</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718514442444</v>
+        <v>0.608718454837799</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634543001651764</v>
+        <v>0.634542942047119</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.64007693529129</v>
+        <v>0.640076875686646</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097331047058</v>
+        <v>0.616097271442413</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.628087520599365</v>
+        <v>0.62808758020401</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942273616791</v>
+        <v>0.617942214012146</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651660442352</v>
+        <v>0.597651720046997</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607796967029572</v>
+        <v>0.607797026634216</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617480993270874</v>
+        <v>0.617481052875519</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165138721466</v>
+        <v>0.627165079116821</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829319477081</v>
+        <v>0.608829379081726</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.613070249557495</v>
+        <v>0.61307030916214</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969141960144</v>
+        <v>0.581969201564789</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.573958694934845</v>
+        <v>0.57395875453949</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152659893036</v>
+        <v>0.587152719497681</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555200576782</v>
+        <v>0.580555260181427</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741928577423</v>
+        <v>0.544741868972778</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396800041199</v>
+        <v>0.550396740436554</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040151596069</v>
+        <v>0.548040091991425</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731362342834</v>
+        <v>0.536731421947479</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454033374786</v>
+        <v>0.549454092979431</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.54238623380661</v>
+        <v>0.542386293411255</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.524479150772095</v>
+        <v>0.52447909116745</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180868148804</v>
+        <v>0.521180927753448</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720080852509</v>
+        <v>0.528720021247864</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807471752167</v>
+        <v>0.592807531356812</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577107906342</v>
+        <v>0.596577048301697</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.59516316652298</v>
+        <v>0.595163106918335</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772086143494</v>
+        <v>0.609772026538849</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876284599304</v>
+        <v>0.599876224994659</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947234630585</v>
+        <v>0.565947294235229</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533293247223</v>
+        <v>0.564533352851868</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.537673115730286</v>
+        <v>0.53767317533493</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100654602051</v>
+        <v>0.506100714206696</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997409820557</v>
+        <v>0.515997350215912</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194495439529</v>
+        <v>0.488194525241852</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.512226819992065</v>
+        <v>0.51222687959671</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.51835298538208</v>
+        <v>0.518352925777435</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.49384930729866</v>
+        <v>0.493849337100983</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539653778076</v>
+        <v>0.482539623975754</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770047426224</v>
+        <v>0.478770077228546</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.489137142896652</v>
+        <v>0.48913711309433</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931687831879</v>
+        <v>0.467931717634201</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909810304642</v>
+        <v>0.451909840106964</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469815999269485</v>
+        <v>0.469816029071808</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>0.774999976158142</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>620590</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.781000018119812</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.777999997138977</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.768999993801117</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.768999993801117</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984724283218</v>
+        <v>0.373984754085541</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.410126000642776</v>
       </c>
       <c r="G7" t="n">
-        <v>0.365868508815765</v>
+        <v>0.365868479013443</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.406127005815506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.362301051616669</v>
+        <v>0.362301081418991</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198314905167</v>
+        <v>0.358198344707489</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012857913971</v>
+        <v>0.330012828111649</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272104978561</v>
+        <v>0.321272164583206</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696389198303</v>
+        <v>0.308696359395981</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998313903809</v>
+        <v>0.292998284101486</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205849885941</v>
+        <v>0.282205820083618</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830268144608</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.323742002248764</v>
       </c>
       <c r="G31" t="n">
-        <v>0.288806408643723</v>
+        <v>0.2888063788414</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984835147858</v>
+        <v>0.288984805345535</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.331440001726151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.295673698186874</v>
+        <v>0.295673668384552</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.29174941778183</v>
+        <v>0.291749358177185</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114559173584</v>
+        <v>0.301114529371262</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335573911667</v>
+        <v>0.294335544109344</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.29005441069603</v>
+        <v>0.290054440498352</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311625003815</v>
+        <v>0.300311654806137</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.30120375752449</v>
+        <v>0.301203727722168</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166329860687</v>
+        <v>0.303166300058365</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560580730438</v>
+        <v>0.301560550928116</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471352577209</v>
+        <v>0.301471322774887</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869595527649</v>
+        <v>0.313869625329971</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229486942291</v>
+        <v>0.328229516744614</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736722230911</v>
+        <v>0.372736692428589</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993966341019</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.382904708385468</v>
+        <v>0.38290473818779</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820700407028</v>
+        <v>0.377820730209351</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350759744644</v>
+        <v>0.383350729942322</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203535079956</v>
+        <v>0.353203564882278</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579087018967</v>
+        <v>0.352579116821289</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>0.401827991008759</v>
       </c>
       <c r="G78" t="n">
-        <v>0.358465969562531</v>
+        <v>0.358465999364853</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.396028995513916</v>
       </c>
       <c r="G79" t="n">
-        <v>0.353292793035507</v>
+        <v>0.353292763233185</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060414075851</v>
+        <v>0.370060443878174</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157900810242</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332602739334</v>
+        <v>0.372332632541656</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.371502429246902</v>
+        <v>0.37150239944458</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>0.399827986955643</v>
       </c>
       <c r="G96" t="n">
-        <v>0.368828147649765</v>
+        <v>0.368828177452087</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.393429011106491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.362925320863724</v>
+        <v>0.362925291061401</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.35065832734108</v>
+        <v>0.350658357143402</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.40022799372673</v>
       </c>
       <c r="G106" t="n">
-        <v>0.369197160005569</v>
+        <v>0.369197130203247</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36430898308754</v>
+        <v>0.364309012889862</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455947399139</v>
+        <v>0.317455977201462</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.350237011909485</v>
       </c>
       <c r="G129" t="n">
-        <v>0.323082119226456</v>
+        <v>0.323082089424133</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169452190399</v>
+        <v>0.329169481992722</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>0.374033004045486</v>
       </c>
       <c r="G137" t="n">
-        <v>0.345033138990402</v>
+        <v>0.34503310918808</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.380430996417999</v>
       </c>
       <c r="G142" t="n">
-        <v>0.350935071706772</v>
+        <v>0.350935101509094</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886932134628</v>
+        <v>0.353886961936951</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163706302643</v>
+        <v>0.354163736104965</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.344756424427032</v>
+        <v>0.34475639462471</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619998216629</v>
+        <v>0.341620028018951</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212656736374</v>
+        <v>0.332212686538696</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935912370682</v>
+        <v>0.331935942173004</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417677879333</v>
+        <v>0.308417648077011</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309859752655</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.341937988996506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.315426558256149</v>
+        <v>0.315426528453827</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G179" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>0.342038005590439</v>
       </c>
       <c r="G180" t="n">
-        <v>0.315518796443939</v>
+        <v>0.315518826246262</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G201" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484555482864</v>
+        <v>0.338484525680542</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>0.372732996940613</v>
       </c>
       <c r="G208" t="n">
-        <v>0.343833923339844</v>
+        <v>0.343833953142166</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G212" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G213" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333473205566</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998785018921</v>
+        <v>0.348998814821243</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G226" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.352436006069183</v>
       </c>
       <c r="G229" t="n">
-        <v>0.325110614299774</v>
+        <v>0.325110644102097</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558049440384</v>
+        <v>0.324558079242706</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G234" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.350473880767822</v>
+        <v>0.3504738509655</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105822086334</v>
+        <v>0.350105792284012</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.37565353512764</v>
+        <v>0.375653505325317</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429829359055</v>
+        <v>0.385429799556732</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.37094983458519</v>
+        <v>0.370949864387512</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G268" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G271" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370961666107</v>
+        <v>0.381370931863785</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G287" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G288" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744902849197</v>
+        <v>0.394744873046875</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714666843414</v>
+        <v>0.430714637041092</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>0.469814985990524</v>
       </c>
       <c r="G294" t="n">
-        <v>0.433388859033585</v>
+        <v>0.433388888835907</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927668094635</v>
+        <v>0.432927638292313</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340749263763</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403621912003</v>
+        <v>0.453403651714325</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.488819926977158</v>
+        <v>0.488819897174835</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265508174896</v>
+        <v>0.507265567779541</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.47544601559639</v>
+        <v>0.475446045398712</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839458465576</v>
+        <v>0.464839428663254</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>0.558399975299835</v>
       </c>
       <c r="G311" t="n">
-        <v>0.515105545520782</v>
+        <v>0.515105605125427</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511876940727234</v>
+        <v>0.511877000331879</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099805831909</v>
+        <v>0.521099865436554</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>0.593892991542816</v>
       </c>
       <c r="G317" t="n">
-        <v>0.547846734523773</v>
+        <v>0.547846794128418</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841888904572</v>
+        <v>0.553841829299927</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G320" t="n">
-        <v>0.557992041110992</v>
+        <v>0.557991981506348</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>0.601891994476318</v>
       </c>
       <c r="G321" t="n">
-        <v>0.555225551128387</v>
+        <v>0.555225610733032</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345497131348</v>
+        <v>0.595345556735992</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495649337769</v>
+        <v>0.599495708942413</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>0.661381006240845</v>
       </c>
       <c r="G329" t="n">
-        <v>0.610102236270905</v>
+        <v>0.61010217666626</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718454837799</v>
+        <v>0.608718514442444</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>0.696874976158142</v>
       </c>
       <c r="G339" t="n">
-        <v>0.642844200134277</v>
+        <v>0.642844259738922</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.653383016586304</v>
       </c>
       <c r="G345" t="n">
-        <v>0.602724313735962</v>
+        <v>0.602724373340607</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651720046997</v>
+        <v>0.597651660442352</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617481052875519</v>
+        <v>0.617480993270874</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465383529663</v>
+        <v>0.635465443134308</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165079116821</v>
+        <v>0.627165138721466</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179735183716</v>
+        <v>0.609179794788361</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>0.768999993801117</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>392266</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.781000018119812</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.767000019550323</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.76800000667572</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.368366360664368</v>
+        <v>0.36836639046669</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.354936003684998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316634207963943</v>
+        <v>0.316634178161621</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.363934010267258</v>
       </c>
       <c r="G20" t="n">
-        <v>0.324661165475845</v>
+        <v>0.324661195278168</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.348637014627457</v>
       </c>
       <c r="G24" t="n">
-        <v>0.311014920473099</v>
+        <v>0.311014950275421</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358235120773</v>
+        <v>0.307358264923096</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289876013994217</v>
+        <v>0.289875984191895</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500462055206</v>
+        <v>0.290500491857529</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311654806137</v>
+        <v>0.300311625003815</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.340938001871109</v>
       </c>
       <c r="G45" t="n">
-        <v>0.304146736860275</v>
+        <v>0.304146766662598</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560550928116</v>
+        <v>0.301560580730438</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471322774887</v>
+        <v>0.301471352577209</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869625329971</v>
+        <v>0.313869595527649</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822792768478</v>
+        <v>0.358822822570801</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063571691513</v>
+        <v>0.384063541889191</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573926448822</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579116821289</v>
+        <v>0.352579087018967</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183971881866</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157960414886</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>0.769999980926514</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>855766</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.795000016689301</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.740000009536743</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.773000001907349</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>682443</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.763000011444092</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -63288,13 +63288,36 @@
         <v>0.783999979496002</v>
       </c>
       <c r="D2736" t="n">
-        <v>0.763000011444092</v>
+        <v>0.762000024318695</v>
       </c>
       <c r="E2736" t="n">
         <v>0.779999971389771</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.762000024318695</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>212278</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.77700001001358</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.77700001001358</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.77700001001358</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.754000008106232</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>688158</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.726000010967255</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.769999980926514</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.730000019073486</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>263284</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.736999988555908</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>291424</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.721000015735626</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.721000015735626</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37692865729332</v>
+        <v>0.376928627490997</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.368366360664368</v>
+        <v>0.368366330862045</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.360035002231598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3211829662323</v>
+        <v>0.321182936429977</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671605825424</v>
+        <v>0.314671576023102</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358264923096</v>
+        <v>0.307358235120773</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696359395981</v>
+        <v>0.308696389198303</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998284101486</v>
+        <v>0.292998313903809</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205849885941</v>
+        <v>0.282205820083618</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979614973068</v>
+        <v>0.293979585170746</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.29174941778183</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114499568939</v>
+        <v>0.301114529371262</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720248699188</v>
+        <v>0.302720278501511</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471352577209</v>
+        <v>0.301471322774887</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869625329971</v>
+        <v>0.313869655132294</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229546546936</v>
+        <v>0.328229516744614</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.370149672031403</v>
+        <v>0.37014964222908</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350789546967</v>
+        <v>0.383350759744644</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G68" t="n">
-        <v>0.347851932048798</v>
+        <v>0.347851902246475</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573866844177</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178751707077</v>
+        <v>0.359178781509399</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376801013947</v>
+        <v>0.358376771211624</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>0.393929004669189</v>
       </c>
       <c r="G75" t="n">
-        <v>0.351419389247894</v>
+        <v>0.351419359445572</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.395428985357285</v>
       </c>
       <c r="G77" t="n">
-        <v>0.352757483720779</v>
+        <v>0.352757513523102</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306271791458</v>
+        <v>0.357306241989136</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122625112534</v>
+        <v>0.362122654914856</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060473680496</v>
+        <v>0.370060443878174</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.396589815616608</v>
+        <v>0.39658984541893</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027363300323</v>
+        <v>0.370027393102646</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304084062576</v>
+        <v>0.351304054260254</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.35065832734108</v>
+        <v>0.350658357143402</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.409426003694534</v>
       </c>
       <c r="G108" t="n">
-        <v>0.377682030200958</v>
+        <v>0.377682000398636</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313918113708</v>
+        <v>0.358313888311386</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.385930001735687</v>
       </c>
       <c r="G114" t="n">
-        <v>0.356007725000381</v>
+        <v>0.356007754802704</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.373333007097244</v>
       </c>
       <c r="G117" t="n">
-        <v>0.344387412071228</v>
+        <v>0.34438744187355</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513103961945</v>
+        <v>0.359513133764267</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.353235989809036</v>
       </c>
       <c r="G126" t="n">
-        <v>0.325848579406738</v>
+        <v>0.325848609209061</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455977201462</v>
+        <v>0.317455947399139</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420835971832</v>
+        <v>0.359420865774155</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.385930001735687</v>
       </c>
       <c r="G145" t="n">
-        <v>0.356007725000381</v>
+        <v>0.356007754802704</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163706302643</v>
+        <v>0.354163736104965</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.361434996128082</v>
       </c>
       <c r="G153" t="n">
-        <v>0.333411902189255</v>
+        <v>0.333411872386932</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843733787537</v>
+        <v>0.331843703985214</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212656736374</v>
+        <v>0.332212686538696</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382423639297</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.34213799238205</v>
       </c>
       <c r="G167" t="n">
-        <v>0.315611034631729</v>
+        <v>0.315611064434052</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.326402068138123</v>
+        <v>0.3264020383358</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309859752655</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660068273544</v>
+        <v>0.312660098075867</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.311829835176468</v>
+        <v>0.31182986497879</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.351437002420425</v>
       </c>
       <c r="G203" t="n">
-        <v>0.324189066886902</v>
+        <v>0.324189096689224</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027369499207</v>
+        <v>0.351027339696884</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071438312531</v>
+        <v>0.354071468114853</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333532810211</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998785018921</v>
+        <v>0.348998814821243</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.338300049304962</v>
+        <v>0.338300079107285</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751465797424</v>
+        <v>0.331751435995102</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897642850876</v>
+        <v>0.322897613048553</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328247010707855</v>
+        <v>0.328246980905533</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.353635996580124</v>
       </c>
       <c r="G232" t="n">
-        <v>0.32621756196022</v>
+        <v>0.326217591762543</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344124317169</v>
+        <v>0.322344154119492</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183297395706</v>
+        <v>0.330183267593384</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.353235989809036</v>
       </c>
       <c r="G236" t="n">
-        <v>0.325848579406738</v>
+        <v>0.325848609209061</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.31911638379097</v>
+        <v>0.319116413593292</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.326402068138123</v>
+        <v>0.3264020383358</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.359135001897812</v>
       </c>
       <c r="G243" t="n">
-        <v>0.33129021525383</v>
+        <v>0.331290245056152</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018429517746</v>
+        <v>0.344018399715424</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3504738509655</v>
+        <v>0.350473821163177</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.37565353512764</v>
+        <v>0.375653505325317</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.37094983458519</v>
+        <v>0.370949864387512</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.38137099146843</v>
+        <v>0.381370961666107</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>0.417724996805191</v>
       </c>
       <c r="G275" t="n">
-        <v>0.385337561368942</v>
+        <v>0.385337591171265</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085336923599</v>
+        <v>0.374085307121277</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531818389893</v>
+        <v>0.373531848192215</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744873046875</v>
+        <v>0.394744902849197</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714666843414</v>
+        <v>0.430714637041092</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340779066086</v>
+        <v>0.436340808868408</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321194171906</v>
+        <v>0.441321164369583</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145651578903</v>
+        <v>0.467145621776581</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475445985794067</v>
+        <v>0.47544601559639</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839458465576</v>
+        <v>0.464839488267899</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099805831909</v>
+        <v>0.521099865436554</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774081230164</v>
+        <v>0.542774140834808</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345497131348</v>
+        <v>0.595345556735992</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495649337769</v>
+        <v>0.599495708942413</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267998218536</v>
+        <v>0.596267938613892</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.652882993221283</v>
       </c>
       <c r="G327" t="n">
-        <v>0.60226309299469</v>
+        <v>0.602263033390045</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634542942047119</v>
+        <v>0.634543001651764</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999376773834</v>
+        <v>0.640999317169189</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>0.702874004840851</v>
       </c>
       <c r="G338" t="n">
-        <v>0.648378133773804</v>
+        <v>0.648378193378448</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076816082001</v>
+        <v>0.640076875686646</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.62808758020401</v>
+        <v>0.628087520599365</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553646564484</v>
+        <v>0.622553706169128</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863761425018</v>
+        <v>0.618863821029663</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651720046997</v>
+        <v>0.597651660442352</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.634886026382446</v>
       </c>
       <c r="G353" t="n">
-        <v>0.5856614112854</v>
+        <v>0.585661470890045</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617481052875519</v>
+        <v>0.617480993270874</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.624397695064545</v>
+        <v>0.6243976354599</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465443134308</v>
+        <v>0.635465383529663</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019712924957</v>
+        <v>0.617019772529602</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.740000009536743</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>428238</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.405427008867264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.361676603555679</v>
+        <v>0.361676573753357</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849839687347</v>
+        <v>0.366849809885025</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.36354997754097</v>
+        <v>0.363550007343292</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.365433990955353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.325999319553375</v>
+        <v>0.325999289751053</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272104978561</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>0.364533990621567</v>
       </c>
       <c r="G21" t="n">
-        <v>0.325196415185928</v>
+        <v>0.325196444988251</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696389198303</v>
+        <v>0.308696359395981</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998313903809</v>
+        <v>0.292998284101486</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205820083618</v>
+        <v>0.282205849885941</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979585170746</v>
+        <v>0.293979614973068</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830268144608</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.323742002248764</v>
       </c>
       <c r="G31" t="n">
-        <v>0.288806408643723</v>
+        <v>0.2888063788414</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.29174941778183</v>
+        <v>0.291749387979507</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114529371262</v>
+        <v>0.301114499568939</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335544109344</v>
+        <v>0.294335514307022</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720278501511</v>
+        <v>0.302720248699188</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869655132294</v>
+        <v>0.313869625329971</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229516744614</v>
+        <v>0.328229546546936</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007637739182</v>
+        <v>0.335007667541504</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.38290473818779</v>
+        <v>0.382904767990112</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820700407028</v>
+        <v>0.377820670604706</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350759744644</v>
+        <v>0.383350789546967</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.397127985954285</v>
       </c>
       <c r="G67" t="n">
-        <v>0.354273110628128</v>
+        <v>0.35427314043045</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3575738966465</v>
+        <v>0.357573866844177</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178781509399</v>
+        <v>0.359178751707077</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306241989136</v>
+        <v>0.357306271791458</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122654914856</v>
+        <v>0.362122625112534</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157960414886</v>
+        <v>0.379157990217209</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.39658984541893</v>
+        <v>0.396589815616608</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027393102646</v>
+        <v>0.370027363300323</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.368920415639877</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304054260254</v>
+        <v>0.351304084062576</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.350658357143402</v>
+        <v>0.35065832734108</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.409426003694534</v>
       </c>
       <c r="G108" t="n">
-        <v>0.377682000398636</v>
+        <v>0.377682030200958</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313888311386</v>
+        <v>0.358313918113708</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.385930001735687</v>
       </c>
       <c r="G114" t="n">
-        <v>0.356007754802704</v>
+        <v>0.356007725000381</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.373333007097244</v>
       </c>
       <c r="G117" t="n">
-        <v>0.34438744187355</v>
+        <v>0.344387412071228</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513133764267</v>
+        <v>0.359513103961945</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.353235989809036</v>
       </c>
       <c r="G126" t="n">
-        <v>0.325848609209061</v>
+        <v>0.325848579406738</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455947399139</v>
+        <v>0.317455977201462</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420865774155</v>
+        <v>0.359420835971832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.385930001735687</v>
       </c>
       <c r="G145" t="n">
-        <v>0.356007754802704</v>
+        <v>0.356007725000381</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163736104965</v>
+        <v>0.354163706302643</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.361434996128082</v>
       </c>
       <c r="G153" t="n">
-        <v>0.333411872386932</v>
+        <v>0.333411902189255</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843703985214</v>
+        <v>0.331843733787537</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212686538696</v>
+        <v>0.332212656736374</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.34213799238205</v>
       </c>
       <c r="G167" t="n">
-        <v>0.315611064434052</v>
+        <v>0.315611034631729</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3264020383358</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309829950333</v>
+        <v>0.326309859752655</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620868682861</v>
+        <v>0.322620838880539</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620868682861</v>
+        <v>0.322620838880539</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660098075867</v>
+        <v>0.312660068273544</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.31182986497879</v>
+        <v>0.311829835176468</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.351437002420425</v>
       </c>
       <c r="G203" t="n">
-        <v>0.324189096689224</v>
+        <v>0.324189066886902</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027339696884</v>
+        <v>0.351027369499207</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071468114853</v>
+        <v>0.354071438312531</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333532810211</v>
+        <v>0.353333503007889</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998814821243</v>
+        <v>0.348998785018921</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.338300079107285</v>
+        <v>0.338300049304962</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751435995102</v>
+        <v>0.331751465797424</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328246980905533</v>
+        <v>0.328247010707855</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.353635996580124</v>
       </c>
       <c r="G232" t="n">
-        <v>0.326217591762543</v>
+        <v>0.32621756196022</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344154119492</v>
+        <v>0.322344124317169</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183267593384</v>
+        <v>0.330183297395706</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.353235989809036</v>
       </c>
       <c r="G236" t="n">
-        <v>0.325848609209061</v>
+        <v>0.325848579406738</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.319116413593292</v>
+        <v>0.31911638379097</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.3264020383358</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.359135001897812</v>
       </c>
       <c r="G243" t="n">
-        <v>0.331290245056152</v>
+        <v>0.33129021525383</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018399715424</v>
+        <v>0.344018429517746</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.350473821163177</v>
+        <v>0.3504738509655</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.375653505325317</v>
+        <v>0.37565353512764</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609376907349</v>
+        <v>0.372609347105026</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.370949864387512</v>
+        <v>0.37094983458519</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370961666107</v>
+        <v>0.38137099146843</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>0.417724996805191</v>
       </c>
       <c r="G275" t="n">
-        <v>0.385337591171265</v>
+        <v>0.385337561368942</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.368920415639877</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085307121277</v>
+        <v>0.374085336923599</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531848192215</v>
+        <v>0.373531818389893</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744902849197</v>
+        <v>0.394744873046875</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714637041092</v>
+        <v>0.430714666843414</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340808868408</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321164369583</v>
+        <v>0.441321194171906</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145621776581</v>
+        <v>0.467145651578903</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.47544601559639</v>
+        <v>0.475445985794067</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839488267899</v>
+        <v>0.464839458465576</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099865436554</v>
+        <v>0.521099805831909</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774140834808</v>
+        <v>0.542774081230164</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345556735992</v>
+        <v>0.595345497131348</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495708942413</v>
+        <v>0.599495649337769</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267938613892</v>
+        <v>0.596267998218536</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.652882993221283</v>
       </c>
       <c r="G327" t="n">
-        <v>0.602263033390045</v>
+        <v>0.60226309299469</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634543001651764</v>
+        <v>0.634542942047119</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999317169189</v>
+        <v>0.640999376773834</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>0.702874004840851</v>
       </c>
       <c r="G338" t="n">
-        <v>0.648378193378448</v>
+        <v>0.648378133773804</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076875686646</v>
+        <v>0.640076816082001</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097331047058</v>
+        <v>0.616097271442413</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.628087520599365</v>
+        <v>0.62808758020401</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553706169128</v>
+        <v>0.622553646564484</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863821029663</v>
+        <v>0.618863761425018</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651660442352</v>
+        <v>0.597651720046997</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.634886026382446</v>
       </c>
       <c r="G353" t="n">
-        <v>0.585661470890045</v>
+        <v>0.5856614112854</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617480993270874</v>
+        <v>0.617481052875519</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.6243976354599</v>
+        <v>0.624397695064545</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465383529663</v>
+        <v>0.635465443134308</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019772529602</v>
+        <v>0.617019712924957</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -71672,7 +71672,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2743" t="n">
-        <v>428238</v>
+        <v>429813</v>
       </c>
       <c r="C2743" t="n">
         <v>0.75</v>
@@ -71690,6 +71690,32 @@
         <v>0.745000004768372</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>335648</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.759999990463257</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.376928627490997</v>
+        <v>0.37692865729332</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -485,7 +485,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984724283218</v>
+        <v>0.373984754085541</v>
       </c>
       <c r="H4" t="n">
         <v>28227</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920309305191</v>
+        <v>0.367920339107513</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -543,7 +543,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.36836639046669</v>
+        <v>0.368366360664368</v>
       </c>
       <c r="H6" t="n">
         <v>44447</v>
@@ -601,7 +601,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849839687347</v>
+        <v>0.366849809885025</v>
       </c>
       <c r="H8" t="n">
         <v>58014</v>
@@ -659,7 +659,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H10" t="n">
         <v>376498</v>
@@ -688,7 +688,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.36354997754097</v>
+        <v>0.363550007343292</v>
       </c>
       <c r="H11" t="n">
         <v>679980</v>
@@ -717,7 +717,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198344707489</v>
+        <v>0.358198314905167</v>
       </c>
       <c r="H12" t="n">
         <v>66923</v>
@@ -746,7 +746,7 @@
         <v>0.376531988382339</v>
       </c>
       <c r="G13" t="n">
-        <v>0.335899710655212</v>
+        <v>0.33589968085289</v>
       </c>
       <c r="H13" t="n">
         <v>687377</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671605825424</v>
+        <v>0.314671576023102</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1065,7 +1065,7 @@
         <v>0.348637014627457</v>
       </c>
       <c r="G24" t="n">
-        <v>0.311014950275421</v>
+        <v>0.311014920473099</v>
       </c>
       <c r="H24" t="n">
         <v>194987</v>
@@ -1123,7 +1123,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696389198303</v>
+        <v>0.308696359395981</v>
       </c>
       <c r="H26" t="n">
         <v>149000</v>
@@ -1152,7 +1152,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998313903809</v>
+        <v>0.292998284101486</v>
       </c>
       <c r="H27" t="n">
         <v>582541</v>
@@ -1210,7 +1210,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979585170746</v>
+        <v>0.293979614973068</v>
       </c>
       <c r="H29" t="n">
         <v>282359</v>
@@ -1326,7 +1326,7 @@
         <v>0.326041013002396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.290857285261154</v>
+        <v>0.290857315063477</v>
       </c>
       <c r="H33" t="n">
         <v>123285</v>
@@ -1384,7 +1384,7 @@
         <v>0.331440001726151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.295673698186874</v>
+        <v>0.295673668384552</v>
       </c>
       <c r="H35" t="n">
         <v>189584</v>
@@ -1413,7 +1413,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.291749358177185</v>
       </c>
       <c r="H36" t="n">
         <v>227448</v>
@@ -1471,7 +1471,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114499568939</v>
+        <v>0.301114529371262</v>
       </c>
       <c r="H38" t="n">
         <v>6327</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335544109344</v>
+        <v>0.294335573911667</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1529,7 +1529,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289875984191895</v>
+        <v>0.289876013994217</v>
       </c>
       <c r="H40" t="n">
         <v>857362</v>
@@ -1558,7 +1558,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.29005441069603</v>
+        <v>0.290054470300674</v>
       </c>
       <c r="H41" t="n">
         <v>53072</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500491857529</v>
+        <v>0.290500462055206</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1674,7 +1674,7 @@
         <v>0.340938001871109</v>
       </c>
       <c r="G45" t="n">
-        <v>0.304146766662598</v>
+        <v>0.304146736860275</v>
       </c>
       <c r="H45" t="n">
         <v>663295</v>
@@ -1732,7 +1732,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720278501511</v>
+        <v>0.302720248699188</v>
       </c>
       <c r="H47" t="n">
         <v>365880</v>
@@ -1877,7 +1877,7 @@
         <v>0.351437002420425</v>
       </c>
       <c r="G52" t="n">
-        <v>0.313512772321701</v>
+        <v>0.313512742519379</v>
       </c>
       <c r="H52" t="n">
         <v>862216</v>
@@ -1906,7 +1906,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229516744614</v>
+        <v>0.328229546546936</v>
       </c>
       <c r="H53" t="n">
         <v>274645</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007607936859</v>
+        <v>0.335007637739182</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1964,7 +1964,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="n">
         <v>361299</v>
@@ -2022,7 +2022,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736692428589</v>
+        <v>0.372736722230911</v>
       </c>
       <c r="H57" t="n">
         <v>389611</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993936538696</v>
+        <v>0.382993906736374</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.370149672031403</v>
+        <v>0.37014964222908</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2109,7 +2109,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.382904708385468</v>
+        <v>0.38290473818779</v>
       </c>
       <c r="H60" t="n">
         <v>377944</v>
@@ -2167,7 +2167,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350759744644</v>
+        <v>0.383350789546967</v>
       </c>
       <c r="H62" t="n">
         <v>181871</v>
@@ -2196,7 +2196,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063541889191</v>
+        <v>0.384063571691513</v>
       </c>
       <c r="H63" t="n">
         <v>163812</v>
@@ -2254,7 +2254,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.365690112113953</v>
+        <v>0.36569008231163</v>
       </c>
       <c r="H65" t="n">
         <v>332417</v>
@@ -2428,7 +2428,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G71" t="n">
-        <v>0.355432868003845</v>
+        <v>0.355432897806168</v>
       </c>
       <c r="H71" t="n">
         <v>267996</v>
@@ -2486,7 +2486,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579087018967</v>
+        <v>0.352579116821289</v>
       </c>
       <c r="H73" t="n">
         <v>623896</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183942079544</v>
+        <v>0.354183971881866</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2602,7 +2602,7 @@
         <v>0.395428985357285</v>
       </c>
       <c r="G77" t="n">
-        <v>0.352757483720779</v>
+        <v>0.352757513523102</v>
       </c>
       <c r="H77" t="n">
         <v>206044</v>
@@ -2689,7 +2689,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306271791458</v>
+        <v>0.357306301593781</v>
       </c>
       <c r="H80" t="n">
         <v>465916</v>
@@ -2747,7 +2747,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G82" t="n">
-        <v>0.355432868003845</v>
+        <v>0.355432897806168</v>
       </c>
       <c r="H82" t="n">
         <v>556716</v>
@@ -2776,7 +2776,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060443878174</v>
+        <v>0.370060473680496</v>
       </c>
       <c r="H83" t="n">
         <v>687485</v>
@@ -2834,7 +2834,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.39658984541893</v>
+        <v>0.396589815616608</v>
       </c>
       <c r="H85" t="n">
         <v>340192</v>
@@ -2892,7 +2892,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332632541656</v>
+        <v>0.372332602739334</v>
       </c>
       <c r="H87" t="n">
         <v>290844</v>
@@ -2921,7 +2921,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701615095139</v>
+        <v>0.372701585292816</v>
       </c>
       <c r="H88" t="n">
         <v>354215</v>
@@ -2950,7 +2950,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027393102646</v>
+        <v>0.370027363300323</v>
       </c>
       <c r="H89" t="n">
         <v>311938</v>
@@ -3066,7 +3066,7 @@
         <v>0.404626995325089</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3732550740242</v>
+        <v>0.373255103826523</v>
       </c>
       <c r="H93" t="n">
         <v>433441</v>
@@ -3124,7 +3124,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.368920385837555</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H95" t="n">
         <v>267568</v>
@@ -3269,7 +3269,7 @@
         <v>0.386929988861084</v>
       </c>
       <c r="G100" t="n">
-        <v>0.356930166482925</v>
+        <v>0.356930196285248</v>
       </c>
       <c r="H100" t="n">
         <v>922415</v>
@@ -3298,7 +3298,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304054260254</v>
+        <v>0.351304084062576</v>
       </c>
       <c r="H101" t="n">
         <v>1169299</v>
@@ -3385,7 +3385,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.350658357143402</v>
+        <v>0.35065832734108</v>
       </c>
       <c r="H104" t="n">
         <v>409447</v>
@@ -3414,7 +3414,7 @@
         <v>0.390929996967316</v>
       </c>
       <c r="G105" t="n">
-        <v>0.360620081424713</v>
+        <v>0.360620051622391</v>
       </c>
       <c r="H105" t="n">
         <v>196102</v>
@@ -3472,7 +3472,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H107" t="n">
         <v>1327868</v>
@@ -3617,7 +3617,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313888311386</v>
+        <v>0.358313918113708</v>
       </c>
       <c r="H112" t="n">
         <v>133757</v>
@@ -3704,7 +3704,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H115" t="n">
         <v>399670</v>
@@ -3733,7 +3733,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H116" t="n">
         <v>471777</v>
@@ -3791,7 +3791,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H118" t="n">
         <v>414717</v>
@@ -3820,7 +3820,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.337838798761368</v>
+        <v>0.33783882856369</v>
       </c>
       <c r="H119" t="n">
         <v>2519386</v>
@@ -3936,7 +3936,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513133764267</v>
+        <v>0.359513103961945</v>
       </c>
       <c r="H123" t="n">
         <v>361479</v>
@@ -3994,7 +3994,7 @@
         <v>0.344238013029099</v>
       </c>
       <c r="G125" t="n">
-        <v>0.317548215389252</v>
+        <v>0.317548245191574</v>
       </c>
       <c r="H125" t="n">
         <v>491917</v>
@@ -4052,7 +4052,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H127" t="n">
         <v>1255939</v>
@@ -4081,7 +4081,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455977201462</v>
+        <v>0.317455947399139</v>
       </c>
       <c r="H128" t="n">
         <v>1239642</v>
@@ -4139,7 +4139,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H130" t="n">
         <v>408863</v>
@@ -4168,7 +4168,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H131" t="n">
         <v>488386</v>
@@ -4197,7 +4197,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H132" t="n">
         <v>275307</v>
@@ -4226,7 +4226,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567830085754</v>
+        <v>0.312567800283432</v>
       </c>
       <c r="H133" t="n">
         <v>58287</v>
@@ -4255,7 +4255,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H134" t="n">
         <v>235517</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169422388077</v>
+        <v>0.329169452190399</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4429,7 +4429,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420865774155</v>
+        <v>0.359420835971832</v>
       </c>
       <c r="H140" t="n">
         <v>458480</v>
@@ -4516,7 +4516,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886961936951</v>
+        <v>0.353886932134628</v>
       </c>
       <c r="H143" t="n">
         <v>50099</v>
@@ -4632,7 +4632,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163736104965</v>
+        <v>0.354163706302643</v>
       </c>
       <c r="H147" t="n">
         <v>1381221</v>
@@ -4661,7 +4661,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.34475639462471</v>
+        <v>0.344756424427032</v>
       </c>
       <c r="H148" t="n">
         <v>760552</v>
@@ -4690,7 +4690,7 @@
         <v>0.381830990314484</v>
       </c>
       <c r="G149" t="n">
-        <v>0.352226495742798</v>
+        <v>0.35222652554512</v>
       </c>
       <c r="H149" t="n">
         <v>304342</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619968414307</v>
+        <v>0.341619998216629</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4777,7 +4777,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H152" t="n">
         <v>138916</v>
@@ -4951,7 +4951,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212686538696</v>
+        <v>0.332212656736374</v>
       </c>
       <c r="H158" t="n">
         <v>1508122</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5009,7 +5009,7 @@
         <v>0.356635987758636</v>
       </c>
       <c r="G160" t="n">
-        <v>0.328984946012497</v>
+        <v>0.328984975814819</v>
       </c>
       <c r="H160" t="n">
         <v>256812</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382483243942</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5067,7 +5067,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935942173004</v>
+        <v>0.331935912370682</v>
       </c>
       <c r="H162" t="n">
         <v>65792</v>
@@ -5154,7 +5154,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H165" t="n">
         <v>1547058</v>
@@ -5270,7 +5270,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417648077011</v>
+        <v>0.308417677879333</v>
       </c>
       <c r="H169" t="n">
         <v>480344</v>
@@ -5299,7 +5299,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H170" t="n">
         <v>262272</v>
@@ -5328,7 +5328,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H171" t="n">
         <v>260836</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309829950333</v>
+        <v>0.326309859752655</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5473,7 +5473,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H176" t="n">
         <v>198283</v>
@@ -5502,7 +5502,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H177" t="n">
         <v>167208</v>
@@ -5734,7 +5734,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305795192719</v>
+        <v>0.313305824995041</v>
       </c>
       <c r="H185" t="n">
         <v>269383</v>
@@ -5792,7 +5792,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H187" t="n">
         <v>969165</v>
@@ -5850,7 +5850,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H189" t="n">
         <v>96038</v>
@@ -5966,7 +5966,7 @@
         <v>0.33643901348114</v>
       </c>
       <c r="G193" t="n">
-        <v>0.310353934764862</v>
+        <v>0.31035390496254</v>
       </c>
       <c r="H193" t="n">
         <v>276707</v>
@@ -6053,7 +6053,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H196" t="n">
         <v>85046</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071497917175</v>
+        <v>0.354071468114853</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6575,7 +6575,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837958097458</v>
+        <v>0.356837928295135</v>
       </c>
       <c r="H214" t="n">
         <v>141958</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333532810211</v>
+        <v>0.353333503007889</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6633,7 +6633,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998814821243</v>
+        <v>0.348998785018921</v>
       </c>
       <c r="H216" t="n">
         <v>202870</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6749,7 +6749,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751435995102</v>
+        <v>0.331751465797424</v>
       </c>
       <c r="H220" t="n">
         <v>241870</v>
@@ -6778,7 +6778,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.326125353574753</v>
+        <v>0.32612532377243</v>
       </c>
       <c r="H221" t="n">
         <v>240850</v>
@@ -6807,7 +6807,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H222" t="n">
         <v>259436</v>
@@ -6836,7 +6836,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H223" t="n">
         <v>106739</v>
@@ -6865,7 +6865,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H224" t="n">
         <v>323877</v>
@@ -6952,7 +6952,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328246980905533</v>
+        <v>0.328247010707855</v>
       </c>
       <c r="H227" t="n">
         <v>176045</v>
@@ -6981,7 +6981,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H228" t="n">
         <v>10415</v>
@@ -7271,7 +7271,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H238" t="n">
         <v>60220</v>
@@ -7387,7 +7387,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397162914276</v>
+        <v>0.332397192716599</v>
       </c>
       <c r="H242" t="n">
         <v>278620</v>
@@ -7474,7 +7474,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H245" t="n">
         <v>783334</v>
@@ -7503,7 +7503,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H246" t="n">
         <v>332438</v>
@@ -7561,7 +7561,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018399715424</v>
+        <v>0.344018429517746</v>
       </c>
       <c r="H248" t="n">
         <v>335681</v>
@@ -7590,7 +7590,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H249" t="n">
         <v>515825</v>
@@ -7619,7 +7619,7 @@
         <v>0.377131998538971</v>
       </c>
       <c r="G250" t="n">
-        <v>0.34789189696312</v>
+        <v>0.347891867160797</v>
       </c>
       <c r="H250" t="n">
         <v>624870</v>
@@ -7648,7 +7648,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241264820099</v>
+        <v>0.353241235017776</v>
       </c>
       <c r="H251" t="n">
         <v>591930</v>
@@ -7677,7 +7677,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3504738509655</v>
+        <v>0.350473880767822</v>
       </c>
       <c r="H252" t="n">
         <v>190131</v>
@@ -7793,7 +7793,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105792284012</v>
+        <v>0.350105822086334</v>
       </c>
       <c r="H256" t="n">
         <v>175808</v>
@@ -7822,7 +7822,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396322250366</v>
+        <v>0.351396292448044</v>
       </c>
       <c r="H257" t="n">
         <v>191994</v>
@@ -7967,7 +7967,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429799556732</v>
+        <v>0.385429829359055</v>
       </c>
       <c r="H262" t="n">
         <v>463854</v>
@@ -8025,7 +8025,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H264" t="n">
         <v>828739</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609376907349</v>
+        <v>0.372609347105026</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8083,7 +8083,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.370949864387512</v>
+        <v>0.37094983458519</v>
       </c>
       <c r="H266" t="n">
         <v>191080</v>
@@ -8112,7 +8112,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G267" t="n">
-        <v>0.380910664796829</v>
+        <v>0.380910634994507</v>
       </c>
       <c r="H267" t="n">
         <v>111749</v>
@@ -8199,7 +8199,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342466592789</v>
+        <v>0.379342436790466</v>
       </c>
       <c r="H270" t="n">
         <v>170128</v>
@@ -8257,7 +8257,7 @@
         <v>0.412326008081436</v>
       </c>
       <c r="G272" t="n">
-        <v>0.380357146263123</v>
+        <v>0.380357176065445</v>
       </c>
       <c r="H272" t="n">
         <v>439414</v>
@@ -8315,7 +8315,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370931863785</v>
+        <v>0.381370961666107</v>
       </c>
       <c r="H274" t="n">
         <v>262282</v>
@@ -8431,7 +8431,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H278" t="n">
         <v>227740</v>
@@ -8460,7 +8460,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.368920385837555</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H279" t="n">
         <v>96256</v>
@@ -8489,7 +8489,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H280" t="n">
         <v>66227</v>
@@ -8518,7 +8518,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H281" t="n">
         <v>107938</v>
@@ -8576,7 +8576,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085307121277</v>
+        <v>0.374085336923599</v>
       </c>
       <c r="H283" t="n">
         <v>186709</v>
@@ -8634,7 +8634,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H285" t="n">
         <v>681169</v>
@@ -8750,7 +8750,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531848192215</v>
+        <v>0.373531818389893</v>
       </c>
       <c r="H289" t="n">
         <v>229876</v>
@@ -8866,7 +8866,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714637041092</v>
+        <v>0.430714666843414</v>
       </c>
       <c r="H293" t="n">
         <v>1274513</v>
@@ -8924,7 +8924,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927638292313</v>
+        <v>0.432927668094635</v>
       </c>
       <c r="H295" t="n">
         <v>547763</v>
@@ -8953,7 +8953,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757871389389</v>
+        <v>0.433757841587067</v>
       </c>
       <c r="H296" t="n">
         <v>764989</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340808868408</v>
+        <v>0.436340749263763</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9040,7 +9040,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321164369583</v>
+        <v>0.441321194171906</v>
       </c>
       <c r="H299" t="n">
         <v>731265</v>
@@ -9069,7 +9069,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403651714325</v>
+        <v>0.453403621912003</v>
       </c>
       <c r="H300" t="n">
         <v>1848152</v>
@@ -9098,7 +9098,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145621776581</v>
+        <v>0.467145651578903</v>
       </c>
       <c r="H301" t="n">
         <v>1481695</v>
@@ -9156,7 +9156,7 @@
         <v>0.524406015872955</v>
       </c>
       <c r="G303" t="n">
-        <v>0.483747273683548</v>
+        <v>0.48374730348587</v>
       </c>
       <c r="H303" t="n">
         <v>1152418</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.48881995677948</v>
+        <v>0.488819926977158</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9214,7 +9214,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265567779541</v>
+        <v>0.507265508174896</v>
       </c>
       <c r="H305" t="n">
         <v>2178115</v>
@@ -9301,7 +9301,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475446045398712</v>
+        <v>0.47544601559639</v>
       </c>
       <c r="H308" t="n">
         <v>1980457</v>
@@ -9359,7 +9359,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286082744598</v>
+        <v>0.483286052942276</v>
       </c>
       <c r="H310" t="n">
         <v>1188532</v>
@@ -9475,7 +9475,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511877000331879</v>
+        <v>0.511876940727234</v>
       </c>
       <c r="H314" t="n">
         <v>1905854</v>
@@ -9591,7 +9591,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774140834808</v>
+        <v>0.542774081230164</v>
       </c>
       <c r="H318" t="n">
         <v>750114</v>
@@ -9620,7 +9620,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841829299927</v>
+        <v>0.553841888904572</v>
       </c>
       <c r="H319" t="n">
         <v>1022491</v>
@@ -9794,7 +9794,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495708942413</v>
+        <v>0.599495649337769</v>
       </c>
       <c r="H325" t="n">
         <v>535825</v>
@@ -9823,7 +9823,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267938613892</v>
+        <v>0.596267998218536</v>
       </c>
       <c r="H326" t="n">
         <v>478574</v>
@@ -9881,7 +9881,7 @@
         <v>0.65488201379776</v>
       </c>
       <c r="G328" t="n">
-        <v>0.604107141494751</v>
+        <v>0.604107081890106</v>
       </c>
       <c r="H328" t="n">
         <v>930926</v>
@@ -9997,7 +9997,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718514442444</v>
+        <v>0.608718454837799</v>
       </c>
       <c r="H332" t="n">
         <v>2497649</v>
@@ -10084,7 +10084,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634543001651764</v>
+        <v>0.634542942047119</v>
       </c>
       <c r="H335" t="n">
         <v>2493902</v>
@@ -10229,7 +10229,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.64007693529129</v>
+        <v>0.640076875686646</v>
       </c>
       <c r="H340" t="n">
         <v>1222262</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097331047058</v>
+        <v>0.616097271442413</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10403,7 +10403,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.628087520599365</v>
+        <v>0.62808758020401</v>
       </c>
       <c r="H346" t="n">
         <v>1835882</v>
@@ -10461,7 +10461,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942273616791</v>
+        <v>0.617942214012146</v>
       </c>
       <c r="H348" t="n">
         <v>976577</v>
@@ -10548,7 +10548,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651660442352</v>
+        <v>0.597651720046997</v>
       </c>
       <c r="H351" t="n">
         <v>1472477</v>
@@ -10635,7 +10635,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607796967029572</v>
+        <v>0.607797026634216</v>
       </c>
       <c r="H354" t="n">
         <v>1281515</v>
@@ -10664,7 +10664,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617480993270874</v>
+        <v>0.617481052875519</v>
       </c>
       <c r="H355" t="n">
         <v>615646</v>
@@ -10751,7 +10751,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165138721466</v>
+        <v>0.627165079116821</v>
       </c>
       <c r="H358" t="n">
         <v>444207</v>
@@ -10954,7 +10954,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829319477081</v>
+        <v>0.608829379081726</v>
       </c>
       <c r="H365" t="n">
         <v>210377</v>
@@ -10983,7 +10983,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.613070249557495</v>
+        <v>0.61307030916214</v>
       </c>
       <c r="H366" t="n">
         <v>341904</v>
@@ -11273,7 +11273,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969141960144</v>
+        <v>0.581969201564789</v>
       </c>
       <c r="H376" t="n">
         <v>259131</v>
@@ -11389,7 +11389,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.573958694934845</v>
+        <v>0.57395875453949</v>
       </c>
       <c r="H380" t="n">
         <v>251076</v>
@@ -11418,7 +11418,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152659893036</v>
+        <v>0.587152719497681</v>
       </c>
       <c r="H381" t="n">
         <v>198695</v>
@@ -11447,7 +11447,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555200576782</v>
+        <v>0.580555260181427</v>
       </c>
       <c r="H382" t="n">
         <v>558855</v>
@@ -11505,7 +11505,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H384" t="n">
         <v>1352746</v>
@@ -11563,7 +11563,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H386" t="n">
         <v>141943</v>
@@ -11592,7 +11592,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H387" t="n">
         <v>349861</v>
@@ -11708,7 +11708,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H391" t="n">
         <v>289335</v>
@@ -11737,7 +11737,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741928577423</v>
+        <v>0.544741868972778</v>
       </c>
       <c r="H392" t="n">
         <v>329337</v>
@@ -11766,7 +11766,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396800041199</v>
+        <v>0.550396740436554</v>
       </c>
       <c r="H393" t="n">
         <v>280658</v>
@@ -11795,7 +11795,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H394" t="n">
         <v>290140</v>
@@ -11882,7 +11882,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H397" t="n">
         <v>459584</v>
@@ -11911,7 +11911,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H398" t="n">
         <v>210300</v>
@@ -12027,7 +12027,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H402" t="n">
         <v>228411</v>
@@ -12172,7 +12172,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H407" t="n">
         <v>288350</v>
@@ -12201,7 +12201,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H408" t="n">
         <v>253441</v>
@@ -12230,7 +12230,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H409" t="n">
         <v>269272</v>
@@ -12259,7 +12259,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H410" t="n">
         <v>183867</v>
@@ -12288,7 +12288,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040151596069</v>
+        <v>0.548040091991425</v>
       </c>
       <c r="H411" t="n">
         <v>89021</v>
@@ -12346,7 +12346,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H413" t="n">
         <v>291996</v>
@@ -12433,7 +12433,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731362342834</v>
+        <v>0.536731421947479</v>
       </c>
       <c r="H416" t="n">
         <v>473625</v>
@@ -12520,7 +12520,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H419" t="n">
         <v>180174</v>
@@ -12549,7 +12549,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454033374786</v>
+        <v>0.549454092979431</v>
       </c>
       <c r="H420" t="n">
         <v>451568</v>
@@ -12607,7 +12607,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.54238623380661</v>
+        <v>0.542386293411255</v>
       </c>
       <c r="H422" t="n">
         <v>215255</v>
@@ -12665,7 +12665,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H424" t="n">
         <v>209758</v>
@@ -12723,7 +12723,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H426" t="n">
         <v>156206</v>
@@ -12752,7 +12752,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.524479150772095</v>
+        <v>0.52447909116745</v>
       </c>
       <c r="H427" t="n">
         <v>232817</v>
@@ -12839,7 +12839,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H430" t="n">
         <v>130630</v>
@@ -12897,7 +12897,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180868148804</v>
+        <v>0.521180927753448</v>
       </c>
       <c r="H432" t="n">
         <v>387167</v>
@@ -12984,7 +12984,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720080852509</v>
+        <v>0.528720021247864</v>
       </c>
       <c r="H435" t="n">
         <v>816289</v>
@@ -13100,7 +13100,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H439" t="n">
         <v>699890</v>
@@ -13129,7 +13129,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H440" t="n">
         <v>444610</v>
@@ -13158,7 +13158,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H441" t="n">
         <v>292621</v>
@@ -13245,7 +13245,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H444" t="n">
         <v>1107250</v>
@@ -13274,7 +13274,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807471752167</v>
+        <v>0.592807531356812</v>
       </c>
       <c r="H445" t="n">
         <v>663729</v>
@@ -13332,7 +13332,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577107906342</v>
+        <v>0.596577048301697</v>
       </c>
       <c r="H447" t="n">
         <v>238428</v>
@@ -13361,7 +13361,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.59516316652298</v>
+        <v>0.595163106918335</v>
       </c>
       <c r="H448" t="n">
         <v>218066</v>
@@ -13390,7 +13390,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772086143494</v>
+        <v>0.609772026538849</v>
       </c>
       <c r="H449" t="n">
         <v>909618</v>
@@ -13448,7 +13448,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876284599304</v>
+        <v>0.599876224994659</v>
       </c>
       <c r="H451" t="n">
         <v>477138</v>
@@ -13738,7 +13738,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H461" t="n">
         <v>114187</v>
@@ -13767,7 +13767,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947234630585</v>
+        <v>0.565947294235229</v>
       </c>
       <c r="H462" t="n">
         <v>238863</v>
@@ -13883,7 +13883,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533293247223</v>
+        <v>0.564533352851868</v>
       </c>
       <c r="H466" t="n">
         <v>222204</v>
@@ -13970,7 +13970,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H469" t="n">
         <v>139232</v>
@@ -14115,7 +14115,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H474" t="n">
         <v>149208</v>
@@ -14144,7 +14144,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H475" t="n">
         <v>148025</v>
@@ -14202,7 +14202,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.537673115730286</v>
+        <v>0.53767317533493</v>
       </c>
       <c r="H477" t="n">
         <v>352368</v>
@@ -14405,7 +14405,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100654602051</v>
+        <v>0.506100714206696</v>
       </c>
       <c r="H484" t="n">
         <v>271973</v>
@@ -14695,7 +14695,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H494" t="n">
         <v>58278</v>
@@ -14724,7 +14724,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H495" t="n">
         <v>163569</v>
@@ -14840,7 +14840,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H499" t="n">
         <v>78535</v>
@@ -14869,7 +14869,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H500" t="n">
         <v>70687</v>
@@ -14927,7 +14927,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997409820557</v>
+        <v>0.515997350215912</v>
       </c>
       <c r="H502" t="n">
         <v>149092</v>
@@ -14956,7 +14956,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194495439529</v>
+        <v>0.488194525241852</v>
       </c>
       <c r="H503" t="n">
         <v>1026439</v>
@@ -14985,7 +14985,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H504" t="n">
         <v>196576</v>
@@ -15101,7 +15101,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.512226819992065</v>
+        <v>0.51222687959671</v>
       </c>
       <c r="H508" t="n">
         <v>41572</v>
@@ -15188,7 +15188,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H511" t="n">
         <v>235907</v>
@@ -15217,7 +15217,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H512" t="n">
         <v>80711</v>
@@ -15246,7 +15246,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H513" t="n">
         <v>68229</v>
@@ -15275,7 +15275,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H514" t="n">
         <v>429758</v>
@@ -15362,7 +15362,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H517" t="n">
         <v>143705</v>
@@ -15507,7 +15507,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H522" t="n">
         <v>79164</v>
@@ -15536,7 +15536,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H523" t="n">
         <v>97732</v>
@@ -15594,7 +15594,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H525" t="n">
         <v>53867</v>
@@ -15710,7 +15710,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H529" t="n">
         <v>118746</v>
@@ -15797,7 +15797,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H532" t="n">
         <v>205602</v>
@@ -15855,7 +15855,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H534" t="n">
         <v>98856</v>
@@ -15913,7 +15913,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.51835298538208</v>
+        <v>0.518352925777435</v>
       </c>
       <c r="H536" t="n">
         <v>79457</v>
@@ -15942,7 +15942,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.49384930729866</v>
+        <v>0.493849337100983</v>
       </c>
       <c r="H537" t="n">
         <v>518619</v>
@@ -16000,7 +16000,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H539" t="n">
         <v>178433</v>
@@ -16029,7 +16029,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539653778076</v>
+        <v>0.482539623975754</v>
       </c>
       <c r="H540" t="n">
         <v>175327</v>
@@ -16116,7 +16116,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770047426224</v>
+        <v>0.478770077228546</v>
       </c>
       <c r="H543" t="n">
         <v>269915</v>
@@ -16145,7 +16145,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H544" t="n">
         <v>168852</v>
@@ -16174,7 +16174,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H545" t="n">
         <v>96811</v>
@@ -16261,7 +16261,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H548" t="n">
         <v>145160</v>
@@ -16290,7 +16290,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H549" t="n">
         <v>92949</v>
@@ -16319,7 +16319,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H550" t="n">
         <v>133866</v>
@@ -16377,7 +16377,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.489137142896652</v>
+        <v>0.48913711309433</v>
       </c>
       <c r="H552" t="n">
         <v>240396</v>
@@ -16580,7 +16580,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H559" t="n">
         <v>314325</v>
@@ -16725,7 +16725,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H564" t="n">
         <v>355078</v>
@@ -16783,7 +16783,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H566" t="n">
         <v>370087</v>
@@ -16812,7 +16812,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H567" t="n">
         <v>425158</v>
@@ -16870,7 +16870,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931687831879</v>
+        <v>0.467931717634201</v>
       </c>
       <c r="H569" t="n">
         <v>298487</v>
@@ -17218,7 +17218,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909810304642</v>
+        <v>0.451909840106964</v>
       </c>
       <c r="H581" t="n">
         <v>283637</v>
@@ -17421,7 +17421,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469815999269485</v>
+        <v>0.469816029071808</v>
       </c>
       <c r="H588" t="n">
         <v>121246</v>
@@ -17537,7 +17537,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H592" t="n">
         <v>106747</v>
@@ -17624,7 +17624,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H595" t="n">
         <v>147417</v>
@@ -17682,7 +17682,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H597" t="n">
         <v>59239</v>
@@ -17711,7 +17711,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H598" t="n">
         <v>241824</v>
@@ -17827,7 +17827,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H602" t="n">
         <v>287903</v>
@@ -17885,7 +17885,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H604" t="n">
         <v>1272412</v>
@@ -17914,7 +17914,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H605" t="n">
         <v>1104869</v>
@@ -18001,7 +18001,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H608" t="n">
         <v>43571</v>
@@ -18030,7 +18030,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H609" t="n">
         <v>69465</v>
@@ -18088,7 +18088,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H611" t="n">
         <v>57385</v>
@@ -18117,7 +18117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H612" t="n">
         <v>209658</v>
@@ -18146,7 +18146,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H613" t="n">
         <v>10902</v>
@@ -18204,7 +18204,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H615" t="n">
         <v>157901</v>
@@ -18233,7 +18233,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H616" t="n">
         <v>192728</v>
@@ -18291,7 +18291,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H618" t="n">
         <v>74901</v>
@@ -18407,7 +18407,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H622" t="n">
         <v>442685</v>
@@ -79980,6 +79980,35 @@
         <v>553911</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.742999970912933</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.763000011444092</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.741999983787537</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.749000012874603</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.749000012874603</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>132328</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.405427008867264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.361676603555679</v>
+        <v>0.361676573753357</v>
       </c>
       <c r="H2" t="n">
         <v>90003</v>
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37692865729332</v>
+        <v>0.376928627490997</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -485,7 +485,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="n">
         <v>28227</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920339107513</v>
+        <v>0.367920309305191</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -543,7 +543,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.368366360664368</v>
+        <v>0.368366330862045</v>
       </c>
       <c r="H6" t="n">
         <v>44447</v>
@@ -659,7 +659,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H10" t="n">
         <v>376498</v>
@@ -717,7 +717,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198314905167</v>
+        <v>0.358198344707489</v>
       </c>
       <c r="H12" t="n">
         <v>66923</v>
@@ -862,7 +862,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012828111649</v>
+        <v>0.330012857913971</v>
       </c>
       <c r="H17" t="n">
         <v>26501</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272104978561</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -978,7 +978,7 @@
         <v>0.364533990621567</v>
       </c>
       <c r="G21" t="n">
-        <v>0.325196415185928</v>
+        <v>0.325196444988251</v>
       </c>
       <c r="H21" t="n">
         <v>42569</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1094,7 +1094,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358264923096</v>
+        <v>0.307358235120773</v>
       </c>
       <c r="H25" t="n">
         <v>217873</v>
@@ -1268,7 +1268,7 @@
         <v>0.323742002248764</v>
       </c>
       <c r="G31" t="n">
-        <v>0.288806408643723</v>
+        <v>0.2888063788414</v>
       </c>
       <c r="H31" t="n">
         <v>538832</v>
@@ -1297,7 +1297,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H32" t="n">
         <v>307119</v>
@@ -1413,7 +1413,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749358177185</v>
+        <v>0.291749387979507</v>
       </c>
       <c r="H36" t="n">
         <v>227448</v>
@@ -1442,7 +1442,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H37" t="n">
         <v>783105</v>
@@ -1471,7 +1471,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114529371262</v>
+        <v>0.301114499568939</v>
       </c>
       <c r="H38" t="n">
         <v>6327</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335573911667</v>
+        <v>0.294335514307022</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1529,7 +1529,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289876013994217</v>
+        <v>0.289875984191895</v>
       </c>
       <c r="H40" t="n">
         <v>857362</v>
@@ -1558,7 +1558,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.290054470300674</v>
+        <v>0.290054440498352</v>
       </c>
       <c r="H41" t="n">
         <v>53072</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500462055206</v>
+        <v>0.290500432252884</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1616,7 +1616,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H43" t="n">
         <v>236808</v>
@@ -1645,7 +1645,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311625003815</v>
+        <v>0.300311654806137</v>
       </c>
       <c r="H44" t="n">
         <v>929955</v>
@@ -1703,7 +1703,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.301203727722168</v>
+        <v>0.30120375752449</v>
       </c>
       <c r="H46" t="n">
         <v>245666</v>
@@ -1761,7 +1761,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166329860687</v>
+        <v>0.303166300058365</v>
       </c>
       <c r="H48" t="n">
         <v>159693</v>
@@ -1790,7 +1790,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560580730438</v>
+        <v>0.301560550928116</v>
       </c>
       <c r="H49" t="n">
         <v>194576</v>
@@ -1819,7 +1819,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471352577209</v>
+        <v>0.301471322774887</v>
       </c>
       <c r="H50" t="n">
         <v>368157</v>
@@ -1848,7 +1848,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869595527649</v>
+        <v>0.313869625329971</v>
       </c>
       <c r="H51" t="n">
         <v>251359</v>
@@ -1877,7 +1877,7 @@
         <v>0.351437002420425</v>
       </c>
       <c r="G52" t="n">
-        <v>0.313512742519379</v>
+        <v>0.313512772321701</v>
       </c>
       <c r="H52" t="n">
         <v>862216</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007637739182</v>
+        <v>0.335007667541504</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1964,7 +1964,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="n">
         <v>361299</v>
@@ -1993,7 +1993,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822822570801</v>
+        <v>0.358822792768478</v>
       </c>
       <c r="H56" t="n">
         <v>833937</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2109,7 +2109,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.38290473818779</v>
+        <v>0.382904767990112</v>
       </c>
       <c r="H60" t="n">
         <v>377944</v>
@@ -2138,7 +2138,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820700407028</v>
+        <v>0.377820670604706</v>
       </c>
       <c r="H61" t="n">
         <v>76617</v>
@@ -2196,7 +2196,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063571691513</v>
+        <v>0.384063541889191</v>
       </c>
       <c r="H63" t="n">
         <v>163812</v>
@@ -2254,7 +2254,7 @@
         <v>0.409925997257233</v>
       </c>
       <c r="G65" t="n">
-        <v>0.36569008231163</v>
+        <v>0.365690112113953</v>
       </c>
       <c r="H65" t="n">
         <v>332417</v>
@@ -2341,7 +2341,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G68" t="n">
-        <v>0.347851932048798</v>
+        <v>0.347851902246475</v>
       </c>
       <c r="H68" t="n">
         <v>53474</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3575738966465</v>
+        <v>0.357573866844177</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178721904755</v>
+        <v>0.359178751707077</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2428,7 +2428,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G71" t="n">
-        <v>0.355432897806168</v>
+        <v>0.355432868003845</v>
       </c>
       <c r="H71" t="n">
         <v>267996</v>
@@ -2660,7 +2660,7 @@
         <v>0.396028995513916</v>
       </c>
       <c r="G79" t="n">
-        <v>0.353292763233185</v>
+        <v>0.353292733430862</v>
       </c>
       <c r="H79" t="n">
         <v>82793</v>
@@ -2689,7 +2689,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306301593781</v>
+        <v>0.357306271791458</v>
       </c>
       <c r="H80" t="n">
         <v>465916</v>
@@ -2718,7 +2718,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122654914856</v>
+        <v>0.362122625112534</v>
       </c>
       <c r="H81" t="n">
         <v>732739</v>
@@ -2747,7 +2747,7 @@
         <v>0.398427993059158</v>
       </c>
       <c r="G82" t="n">
-        <v>0.355432897806168</v>
+        <v>0.355432868003845</v>
       </c>
       <c r="H82" t="n">
         <v>556716</v>
@@ -2776,7 +2776,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060473680496</v>
+        <v>0.370060443878174</v>
       </c>
       <c r="H83" t="n">
         <v>687485</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157960414886</v>
+        <v>0.379157990217209</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2892,7 +2892,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332602739334</v>
+        <v>0.372332632541656</v>
       </c>
       <c r="H87" t="n">
         <v>290844</v>
@@ -2921,7 +2921,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701585292816</v>
+        <v>0.372701615095139</v>
       </c>
       <c r="H88" t="n">
         <v>354215</v>
@@ -3008,7 +3008,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.371502429246902</v>
+        <v>0.37150239944458</v>
       </c>
       <c r="H91" t="n">
         <v>148553</v>
@@ -3240,7 +3240,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H99" t="n">
         <v>534781</v>
@@ -3356,7 +3356,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H103" t="n">
         <v>972529</v>
@@ -3530,7 +3530,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468945741653</v>
+        <v>0.356468975543976</v>
       </c>
       <c r="H109" t="n">
         <v>1359696</v>
@@ -3588,7 +3588,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36430898308754</v>
+        <v>0.364309012889862</v>
       </c>
       <c r="H111" t="n">
         <v>269379</v>
@@ -3791,7 +3791,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H118" t="n">
         <v>414717</v>
@@ -3820,7 +3820,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.33783882856369</v>
+        <v>0.337838798761368</v>
       </c>
       <c r="H119" t="n">
         <v>2519386</v>
@@ -3849,7 +3849,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H120" t="n">
         <v>660483</v>
@@ -3907,7 +3907,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H122" t="n">
         <v>582251</v>
@@ -3965,7 +3965,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H124" t="n">
         <v>418732</v>
@@ -4052,7 +4052,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H127" t="n">
         <v>1255939</v>
@@ -4081,7 +4081,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455947399139</v>
+        <v>0.317455977201462</v>
       </c>
       <c r="H128" t="n">
         <v>1239642</v>
@@ -4226,7 +4226,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567800283432</v>
+        <v>0.312567830085754</v>
       </c>
       <c r="H133" t="n">
         <v>58287</v>
@@ -4313,7 +4313,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328544378281</v>
+        <v>0.340328514575958</v>
       </c>
       <c r="H136" t="n">
         <v>146019</v>
@@ -4371,7 +4371,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H138" t="n">
         <v>190400</v>
@@ -4400,7 +4400,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367797374725</v>
+        <v>0.349367827177048</v>
       </c>
       <c r="H139" t="n">
         <v>108968</v>
@@ -4777,7 +4777,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H152" t="n">
         <v>138916</v>
@@ -4922,7 +4922,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843703985214</v>
+        <v>0.331843733787537</v>
       </c>
       <c r="H157" t="n">
         <v>1100576</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5067,7 +5067,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935912370682</v>
+        <v>0.331935942173004</v>
       </c>
       <c r="H162" t="n">
         <v>65792</v>
@@ -5270,7 +5270,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417677879333</v>
+        <v>0.308417648077011</v>
       </c>
       <c r="H169" t="n">
         <v>480344</v>
@@ -5299,7 +5299,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H170" t="n">
         <v>262272</v>
@@ -5328,7 +5328,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H171" t="n">
         <v>260836</v>
@@ -5473,7 +5473,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H176" t="n">
         <v>198283</v>
@@ -5502,7 +5502,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H177" t="n">
         <v>167208</v>
@@ -5676,7 +5676,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761246442795</v>
+        <v>0.319761216640472</v>
       </c>
       <c r="H183" t="n">
         <v>499322</v>
@@ -5705,7 +5705,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660098075867</v>
+        <v>0.312660068273544</v>
       </c>
       <c r="H184" t="n">
         <v>501296</v>
@@ -5734,7 +5734,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305824995041</v>
+        <v>0.313305795192719</v>
       </c>
       <c r="H185" t="n">
         <v>269383</v>
@@ -5763,7 +5763,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.31182986497879</v>
+        <v>0.311829835176468</v>
       </c>
       <c r="H186" t="n">
         <v>107625</v>
@@ -5908,7 +5908,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H191" t="n">
         <v>53571</v>
@@ -5937,7 +5937,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.31219881772995</v>
+        <v>0.312198847532272</v>
       </c>
       <c r="H192" t="n">
         <v>79208</v>
@@ -6227,7 +6227,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.323543339967728</v>
+        <v>0.32354336977005</v>
       </c>
       <c r="H202" t="n">
         <v>232428</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6314,7 +6314,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484555482864</v>
+        <v>0.338484525680542</v>
       </c>
       <c r="H205" t="n">
         <v>279724</v>
@@ -6343,7 +6343,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G206" t="n">
-        <v>0.340605288743973</v>
+        <v>0.340605318546295</v>
       </c>
       <c r="H206" t="n">
         <v>152266</v>
@@ -6372,7 +6372,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G207" t="n">
-        <v>0.340605288743973</v>
+        <v>0.340605318546295</v>
       </c>
       <c r="H207" t="n">
         <v>160709</v>
@@ -6459,7 +6459,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027339696884</v>
+        <v>0.351027369499207</v>
       </c>
       <c r="H210" t="n">
         <v>537773</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071468114853</v>
+        <v>0.354071438312531</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6575,7 +6575,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837928295135</v>
+        <v>0.356837958097458</v>
       </c>
       <c r="H214" t="n">
         <v>141958</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6865,7 +6865,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H224" t="n">
         <v>323877</v>
@@ -6894,7 +6894,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="n">
         <v>81571</v>
@@ -6981,7 +6981,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H228" t="n">
         <v>10415</v>
@@ -7068,7 +7068,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558049440384</v>
+        <v>0.324558079242706</v>
       </c>
       <c r="H231" t="n">
         <v>85940</v>
@@ -7126,7 +7126,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344154119492</v>
+        <v>0.322344124317169</v>
       </c>
       <c r="H233" t="n">
         <v>60253</v>
@@ -7184,7 +7184,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183267593384</v>
+        <v>0.330183297395706</v>
       </c>
       <c r="H235" t="n">
         <v>95241</v>
@@ -7300,7 +7300,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.319116413593292</v>
+        <v>0.31911638379097</v>
       </c>
       <c r="H239" t="n">
         <v>206647</v>
@@ -7387,7 +7387,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397192716599</v>
+        <v>0.332397162914276</v>
       </c>
       <c r="H242" t="n">
         <v>278620</v>
@@ -7474,7 +7474,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712236404419</v>
       </c>
       <c r="H245" t="n">
         <v>783334</v>
@@ -7677,7 +7677,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.350473880767822</v>
+        <v>0.3504738509655</v>
       </c>
       <c r="H252" t="n">
         <v>190131</v>
@@ -7735,7 +7735,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595537900925</v>
+        <v>0.352595508098602</v>
       </c>
       <c r="H254" t="n">
         <v>213674</v>
@@ -7793,7 +7793,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105822086334</v>
+        <v>0.350105792284012</v>
       </c>
       <c r="H256" t="n">
         <v>175808</v>
@@ -7822,7 +7822,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396292448044</v>
+        <v>0.351396322250366</v>
       </c>
       <c r="H257" t="n">
         <v>191994</v>
@@ -8199,7 +8199,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342436790466</v>
+        <v>0.379342466592789</v>
       </c>
       <c r="H270" t="n">
         <v>170128</v>
@@ -8286,7 +8286,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H273" t="n">
         <v>229996</v>
@@ -8315,7 +8315,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370961666107</v>
+        <v>0.38137099146843</v>
       </c>
       <c r="H274" t="n">
         <v>262282</v>
@@ -8373,7 +8373,7 @@
         <v>0.410425990819931</v>
       </c>
       <c r="G276" t="n">
-        <v>0.378604471683502</v>
+        <v>0.37860444188118</v>
       </c>
       <c r="H276" t="n">
         <v>278198</v>
@@ -8402,7 +8402,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895955324173</v>
+        <v>0.379895925521851</v>
       </c>
       <c r="H277" t="n">
         <v>215538</v>
@@ -8547,7 +8547,7 @@
         <v>0.407326996326447</v>
       </c>
       <c r="G282" t="n">
-        <v>0.375745743513107</v>
+        <v>0.37574577331543</v>
       </c>
       <c r="H282" t="n">
         <v>260882</v>
@@ -8808,7 +8808,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744902849197</v>
+        <v>0.394744873046875</v>
       </c>
       <c r="H291" t="n">
         <v>911786</v>
@@ -8924,7 +8924,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927668094635</v>
+        <v>0.432927638292313</v>
       </c>
       <c r="H295" t="n">
         <v>547763</v>
@@ -8953,7 +8953,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757841587067</v>
+        <v>0.433757871389389</v>
       </c>
       <c r="H296" t="n">
         <v>764989</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340749263763</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9069,7 +9069,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403621912003</v>
+        <v>0.453403651714325</v>
       </c>
       <c r="H300" t="n">
         <v>1848152</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.488819926977158</v>
+        <v>0.48881995677948</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9214,7 +9214,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265508174896</v>
+        <v>0.507265567779541</v>
       </c>
       <c r="H305" t="n">
         <v>2178115</v>
@@ -9301,7 +9301,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.47544601559639</v>
+        <v>0.475445985794067</v>
       </c>
       <c r="H308" t="n">
         <v>1980457</v>
@@ -9359,7 +9359,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286052942276</v>
+        <v>0.483286023139954</v>
       </c>
       <c r="H310" t="n">
         <v>1188532</v>
@@ -9475,7 +9475,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511876940727234</v>
+        <v>0.511877000331879</v>
       </c>
       <c r="H314" t="n">
         <v>1905854</v>
@@ -9620,7 +9620,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841888904572</v>
+        <v>0.553841829299927</v>
       </c>
       <c r="H319" t="n">
         <v>1022491</v>
@@ -9997,7 +9997,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718454837799</v>
+        <v>0.608718514442444</v>
       </c>
       <c r="H332" t="n">
         <v>2497649</v>
@@ -10055,7 +10055,7 @@
         <v>0.690375983715057</v>
       </c>
       <c r="G334" t="n">
-        <v>0.636849105358124</v>
+        <v>0.636849164962769</v>
       </c>
       <c r="H334" t="n">
         <v>3228462</v>
@@ -10113,7 +10113,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999317169189</v>
+        <v>0.640999376773834</v>
       </c>
       <c r="H336" t="n">
         <v>1092710</v>
@@ -10229,7 +10229,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076875686646</v>
+        <v>0.640076816082001</v>
       </c>
       <c r="H340" t="n">
         <v>1222262</v>
@@ -10432,7 +10432,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553706169128</v>
+        <v>0.622553646564484</v>
       </c>
       <c r="H347" t="n">
         <v>1501004</v>
@@ -10461,7 +10461,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942214012146</v>
+        <v>0.617942273616791</v>
       </c>
       <c r="H348" t="n">
         <v>976577</v>
@@ -10490,7 +10490,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863821029663</v>
+        <v>0.618863761425018</v>
       </c>
       <c r="H349" t="n">
         <v>716788</v>
@@ -10635,7 +10635,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607797026634216</v>
+        <v>0.607796967029572</v>
       </c>
       <c r="H354" t="n">
         <v>1281515</v>
@@ -10693,7 +10693,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.6243976354599</v>
+        <v>0.624397695064545</v>
       </c>
       <c r="H356" t="n">
         <v>591723</v>
@@ -10722,7 +10722,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465383529663</v>
+        <v>0.635465443134308</v>
       </c>
       <c r="H357" t="n">
         <v>654445</v>
@@ -10780,7 +10780,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019772529602</v>
+        <v>0.617019712924957</v>
       </c>
       <c r="H359" t="n">
         <v>534811</v>
@@ -10838,7 +10838,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179735183716</v>
+        <v>0.609179794788361</v>
       </c>
       <c r="H361" t="n">
         <v>498433</v>
@@ -10867,7 +10867,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G362" t="n">
-        <v>0.612408339977264</v>
+        <v>0.612408399581909</v>
       </c>
       <c r="H362" t="n">
         <v>510897</v>
@@ -10896,7 +10896,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G363" t="n">
-        <v>0.612408339977264</v>
+        <v>0.612408399581909</v>
       </c>
       <c r="H363" t="n">
         <v>588330</v>
@@ -10925,7 +10925,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H364" t="n">
         <v>375033</v>
@@ -10954,7 +10954,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829379081726</v>
+        <v>0.608829319477081</v>
       </c>
       <c r="H365" t="n">
         <v>210377</v>
@@ -10983,7 +10983,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.61307030916214</v>
+        <v>0.613070249557495</v>
       </c>
       <c r="H366" t="n">
         <v>341904</v>
@@ -11273,7 +11273,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969201564789</v>
+        <v>0.581969141960144</v>
       </c>
       <c r="H376" t="n">
         <v>259131</v>
@@ -11389,7 +11389,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.57395875453949</v>
+        <v>0.573958694934845</v>
       </c>
       <c r="H380" t="n">
         <v>251076</v>
@@ -11418,7 +11418,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152719497681</v>
+        <v>0.587152659893036</v>
       </c>
       <c r="H381" t="n">
         <v>198695</v>
@@ -11447,7 +11447,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555260181427</v>
+        <v>0.580555200576782</v>
       </c>
       <c r="H382" t="n">
         <v>558855</v>
@@ -11505,7 +11505,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H384" t="n">
         <v>1352746</v>
@@ -11563,7 +11563,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H386" t="n">
         <v>141943</v>
@@ -11592,7 +11592,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H387" t="n">
         <v>349861</v>
@@ -11708,7 +11708,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H391" t="n">
         <v>289335</v>
@@ -11737,7 +11737,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741868972778</v>
+        <v>0.544741928577423</v>
       </c>
       <c r="H392" t="n">
         <v>329337</v>
@@ -11766,7 +11766,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396740436554</v>
+        <v>0.550396800041199</v>
       </c>
       <c r="H393" t="n">
         <v>280658</v>
@@ -11795,7 +11795,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H394" t="n">
         <v>290140</v>
@@ -11882,7 +11882,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H397" t="n">
         <v>459584</v>
@@ -11911,7 +11911,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H398" t="n">
         <v>210300</v>
@@ -12027,7 +12027,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H402" t="n">
         <v>228411</v>
@@ -12172,7 +12172,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H407" t="n">
         <v>288350</v>
@@ -12201,7 +12201,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H408" t="n">
         <v>253441</v>
@@ -12230,7 +12230,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H409" t="n">
         <v>269272</v>
@@ -12259,7 +12259,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H410" t="n">
         <v>183867</v>
@@ -12288,7 +12288,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040091991425</v>
+        <v>0.548040151596069</v>
       </c>
       <c r="H411" t="n">
         <v>89021</v>
@@ -12346,7 +12346,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H413" t="n">
         <v>291996</v>
@@ -12433,7 +12433,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731421947479</v>
+        <v>0.536731362342834</v>
       </c>
       <c r="H416" t="n">
         <v>473625</v>
@@ -12520,7 +12520,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H419" t="n">
         <v>180174</v>
@@ -12549,7 +12549,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454092979431</v>
+        <v>0.549454033374786</v>
       </c>
       <c r="H420" t="n">
         <v>451568</v>
@@ -12607,7 +12607,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.542386293411255</v>
+        <v>0.54238623380661</v>
       </c>
       <c r="H422" t="n">
         <v>215255</v>
@@ -12665,7 +12665,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H424" t="n">
         <v>209758</v>
@@ -12723,7 +12723,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H426" t="n">
         <v>156206</v>
@@ -12752,7 +12752,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.52447909116745</v>
+        <v>0.524479150772095</v>
       </c>
       <c r="H427" t="n">
         <v>232817</v>
@@ -12839,7 +12839,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H430" t="n">
         <v>130630</v>
@@ -12897,7 +12897,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180927753448</v>
+        <v>0.521180868148804</v>
       </c>
       <c r="H432" t="n">
         <v>387167</v>
@@ -12984,7 +12984,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720021247864</v>
+        <v>0.528720080852509</v>
       </c>
       <c r="H435" t="n">
         <v>816289</v>
@@ -13100,7 +13100,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H439" t="n">
         <v>699890</v>
@@ -13129,7 +13129,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H440" t="n">
         <v>444610</v>
@@ -13158,7 +13158,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H441" t="n">
         <v>292621</v>
@@ -13245,7 +13245,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645861148834</v>
+        <v>0.603645801544189</v>
       </c>
       <c r="H444" t="n">
         <v>1107250</v>
@@ -13274,7 +13274,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807531356812</v>
+        <v>0.592807471752167</v>
       </c>
       <c r="H445" t="n">
         <v>663729</v>
@@ -13332,7 +13332,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577048301697</v>
+        <v>0.596577107906342</v>
       </c>
       <c r="H447" t="n">
         <v>238428</v>
@@ -13361,7 +13361,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.595163106918335</v>
+        <v>0.59516316652298</v>
       </c>
       <c r="H448" t="n">
         <v>218066</v>
@@ -13390,7 +13390,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772026538849</v>
+        <v>0.609772086143494</v>
       </c>
       <c r="H449" t="n">
         <v>909618</v>
@@ -13448,7 +13448,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876224994659</v>
+        <v>0.599876284599304</v>
       </c>
       <c r="H451" t="n">
         <v>477138</v>
@@ -13738,7 +13738,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H461" t="n">
         <v>114187</v>
@@ -13767,7 +13767,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947294235229</v>
+        <v>0.565947234630585</v>
       </c>
       <c r="H462" t="n">
         <v>238863</v>
@@ -13883,7 +13883,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533352851868</v>
+        <v>0.564533293247223</v>
       </c>
       <c r="H466" t="n">
         <v>222204</v>
@@ -13970,7 +13970,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H469" t="n">
         <v>139232</v>
@@ -14115,7 +14115,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H474" t="n">
         <v>149208</v>
@@ -14144,7 +14144,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H475" t="n">
         <v>148025</v>
@@ -14202,7 +14202,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.53767317533493</v>
+        <v>0.537673115730286</v>
       </c>
       <c r="H477" t="n">
         <v>352368</v>
@@ -14405,7 +14405,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100714206696</v>
+        <v>0.506100654602051</v>
       </c>
       <c r="H484" t="n">
         <v>271973</v>
@@ -14695,7 +14695,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H494" t="n">
         <v>58278</v>
@@ -14724,7 +14724,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H495" t="n">
         <v>163569</v>
@@ -14840,7 +14840,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H499" t="n">
         <v>78535</v>
@@ -14869,7 +14869,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H500" t="n">
         <v>70687</v>
@@ -14927,7 +14927,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997350215912</v>
+        <v>0.515997409820557</v>
       </c>
       <c r="H502" t="n">
         <v>149092</v>
@@ -14956,7 +14956,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194525241852</v>
+        <v>0.488194495439529</v>
       </c>
       <c r="H503" t="n">
         <v>1026439</v>
@@ -14985,7 +14985,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H504" t="n">
         <v>196576</v>
@@ -15101,7 +15101,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.51222687959671</v>
+        <v>0.512226819992065</v>
       </c>
       <c r="H508" t="n">
         <v>41572</v>
@@ -15188,7 +15188,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H511" t="n">
         <v>235907</v>
@@ -15217,7 +15217,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H512" t="n">
         <v>80711</v>
@@ -15246,7 +15246,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H513" t="n">
         <v>68229</v>
@@ -15275,7 +15275,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H514" t="n">
         <v>429758</v>
@@ -15362,7 +15362,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H517" t="n">
         <v>143705</v>
@@ -15507,7 +15507,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H522" t="n">
         <v>79164</v>
@@ -15536,7 +15536,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H523" t="n">
         <v>97732</v>
@@ -15594,7 +15594,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H525" t="n">
         <v>53867</v>
@@ -15710,7 +15710,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H529" t="n">
         <v>118746</v>
@@ -15797,7 +15797,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H532" t="n">
         <v>205602</v>
@@ -15855,7 +15855,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H534" t="n">
         <v>98856</v>
@@ -15913,7 +15913,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.518352925777435</v>
+        <v>0.51835298538208</v>
       </c>
       <c r="H536" t="n">
         <v>79457</v>
@@ -15942,7 +15942,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.493849337100983</v>
+        <v>0.49384930729866</v>
       </c>
       <c r="H537" t="n">
         <v>518619</v>
@@ -16000,7 +16000,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H539" t="n">
         <v>178433</v>
@@ -16029,7 +16029,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539623975754</v>
+        <v>0.482539653778076</v>
       </c>
       <c r="H540" t="n">
         <v>175327</v>
@@ -16116,7 +16116,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770077228546</v>
+        <v>0.478770047426224</v>
       </c>
       <c r="H543" t="n">
         <v>269915</v>
@@ -16145,7 +16145,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H544" t="n">
         <v>168852</v>
@@ -16174,7 +16174,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H545" t="n">
         <v>96811</v>
@@ -16261,7 +16261,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H548" t="n">
         <v>145160</v>
@@ -16290,7 +16290,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H549" t="n">
         <v>92949</v>
@@ -16319,7 +16319,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H550" t="n">
         <v>133866</v>
@@ -16377,7 +16377,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.48913711309433</v>
+        <v>0.489137142896652</v>
       </c>
       <c r="H552" t="n">
         <v>240396</v>
@@ -16580,7 +16580,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H559" t="n">
         <v>314325</v>
@@ -16725,7 +16725,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H564" t="n">
         <v>355078</v>
@@ -16783,7 +16783,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H566" t="n">
         <v>370087</v>
@@ -16812,7 +16812,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H567" t="n">
         <v>425158</v>
@@ -16870,7 +16870,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931717634201</v>
+        <v>0.467931687831879</v>
       </c>
       <c r="H569" t="n">
         <v>298487</v>
@@ -17218,7 +17218,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909840106964</v>
+        <v>0.451909810304642</v>
       </c>
       <c r="H581" t="n">
         <v>283637</v>
@@ -17421,7 +17421,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469816029071808</v>
+        <v>0.469815999269485</v>
       </c>
       <c r="H588" t="n">
         <v>121246</v>
@@ -17537,7 +17537,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H592" t="n">
         <v>106747</v>
@@ -17624,7 +17624,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H595" t="n">
         <v>147417</v>
@@ -17682,7 +17682,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H597" t="n">
         <v>59239</v>
@@ -17711,7 +17711,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H598" t="n">
         <v>241824</v>
@@ -17827,7 +17827,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H602" t="n">
         <v>287903</v>
@@ -17885,7 +17885,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H604" t="n">
         <v>1272412</v>
@@ -17914,7 +17914,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H605" t="n">
         <v>1104869</v>
@@ -18001,7 +18001,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H608" t="n">
         <v>43571</v>
@@ -18030,7 +18030,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H609" t="n">
         <v>69465</v>
@@ -18088,7 +18088,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H611" t="n">
         <v>57385</v>
@@ -18117,7 +18117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H612" t="n">
         <v>209658</v>
@@ -18146,7 +18146,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H613" t="n">
         <v>10902</v>
@@ -18204,7 +18204,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H615" t="n">
         <v>157901</v>
@@ -18233,7 +18233,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H616" t="n">
         <v>192728</v>
@@ -18291,7 +18291,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H618" t="n">
         <v>74901</v>
@@ -18407,7 +18407,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H622" t="n">
         <v>442685</v>
@@ -80009,6 +80009,35 @@
         <v>132328</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.742999970912933</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.753000020980835</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.753000020980835</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>191351</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.405427008867264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.361676573753357</v>
+        <v>0.361676603555679</v>
       </c>
       <c r="H2" t="n">
         <v>90003</v>
@@ -485,7 +485,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984724283218</v>
+        <v>0.373984754085541</v>
       </c>
       <c r="H4" t="n">
         <v>28227</v>
@@ -543,7 +543,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.368366330862045</v>
+        <v>0.368366360664368</v>
       </c>
       <c r="H6" t="n">
         <v>44447</v>
@@ -572,7 +572,7 @@
         <v>0.410126000642776</v>
       </c>
       <c r="G7" t="n">
-        <v>0.365868508815765</v>
+        <v>0.365868479013443</v>
       </c>
       <c r="H7" t="n">
         <v>71244</v>
@@ -601,7 +601,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849809885025</v>
+        <v>0.366849839687347</v>
       </c>
       <c r="H8" t="n">
         <v>58014</v>
@@ -630,7 +630,7 @@
         <v>0.406127005815506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.362301051616669</v>
+        <v>0.362301081418991</v>
       </c>
       <c r="H9" t="n">
         <v>183012</v>
@@ -688,7 +688,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="n">
         <v>679980</v>
@@ -746,7 +746,7 @@
         <v>0.376531988382339</v>
       </c>
       <c r="G13" t="n">
-        <v>0.33589968085289</v>
+        <v>0.335899710655212</v>
       </c>
       <c r="H13" t="n">
         <v>687377</v>
@@ -862,7 +862,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012857913971</v>
+        <v>0.330012828111649</v>
       </c>
       <c r="H17" t="n">
         <v>26501</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272104978561</v>
+        <v>0.321272164583206</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -920,7 +920,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450531482697</v>
+        <v>0.321450561285019</v>
       </c>
       <c r="H19" t="n">
         <v>460284</v>
@@ -978,7 +978,7 @@
         <v>0.364533990621567</v>
       </c>
       <c r="G21" t="n">
-        <v>0.325196444988251</v>
+        <v>0.325196415185928</v>
       </c>
       <c r="H21" t="n">
         <v>42569</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671605825424</v>
+        <v>0.314671576023102</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1094,7 +1094,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358235120773</v>
+        <v>0.307358264923096</v>
       </c>
       <c r="H25" t="n">
         <v>217873</v>
@@ -1152,7 +1152,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998284101486</v>
+        <v>0.292998313903809</v>
       </c>
       <c r="H27" t="n">
         <v>582541</v>
@@ -1210,7 +1210,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979614973068</v>
+        <v>0.293979585170746</v>
       </c>
       <c r="H29" t="n">
         <v>282359</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28283029794693</v>
+        <v>0.282830327749252</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1326,7 +1326,7 @@
         <v>0.326041013002396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.290857315063477</v>
+        <v>0.290857285261154</v>
       </c>
       <c r="H33" t="n">
         <v>123285</v>
@@ -1413,7 +1413,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.291749358177185</v>
       </c>
       <c r="H36" t="n">
         <v>227448</v>
@@ -1529,7 +1529,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289875984191895</v>
+        <v>0.289876013994217</v>
       </c>
       <c r="H40" t="n">
         <v>857362</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500432252884</v>
+        <v>0.290500491857529</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1645,7 +1645,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311654806137</v>
+        <v>0.300311625003815</v>
       </c>
       <c r="H44" t="n">
         <v>929955</v>
@@ -1703,7 +1703,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.30120375752449</v>
+        <v>0.301203697919846</v>
       </c>
       <c r="H46" t="n">
         <v>245666</v>
@@ -1732,7 +1732,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720248699188</v>
+        <v>0.302720278501511</v>
       </c>
       <c r="H47" t="n">
         <v>365880</v>
@@ -1848,7 +1848,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869625329971</v>
+        <v>0.313869595527649</v>
       </c>
       <c r="H51" t="n">
         <v>251359</v>
@@ -1906,7 +1906,7 @@
         <v>0.367933988571167</v>
       </c>
       <c r="G53" t="n">
-        <v>0.328229546546936</v>
+        <v>0.328229516744614</v>
       </c>
       <c r="H53" t="n">
         <v>274645</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007667541504</v>
+        <v>0.335007637739182</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1993,7 +1993,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822792768478</v>
+        <v>0.358822822570801</v>
       </c>
       <c r="H56" t="n">
         <v>833937</v>
@@ -2022,7 +2022,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736722230911</v>
+        <v>0.372736692428589</v>
       </c>
       <c r="H57" t="n">
         <v>389611</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993936538696</v>
+        <v>0.382993906736374</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37014964222908</v>
+        <v>0.370149672031403</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2109,7 +2109,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.382904767990112</v>
+        <v>0.38290473818779</v>
       </c>
       <c r="H60" t="n">
         <v>377944</v>
@@ -2138,7 +2138,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820670604706</v>
+        <v>0.377820730209351</v>
       </c>
       <c r="H61" t="n">
         <v>76617</v>
@@ -2167,7 +2167,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350789546967</v>
+        <v>0.383350759744644</v>
       </c>
       <c r="H62" t="n">
         <v>181871</v>
@@ -2225,7 +2225,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806297779083</v>
+        <v>0.373806327581406</v>
       </c>
       <c r="H64" t="n">
         <v>172614</v>
@@ -2283,7 +2283,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203564882278</v>
+        <v>0.353203594684601</v>
       </c>
       <c r="H66" t="n">
         <v>34491</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573866844177</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178751707077</v>
+        <v>0.359178721904755</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2486,7 +2486,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579116821289</v>
+        <v>0.352579087018967</v>
       </c>
       <c r="H73" t="n">
         <v>623896</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183971881866</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2573,7 +2573,7 @@
         <v>0.386629998683929</v>
       </c>
       <c r="G76" t="n">
-        <v>0.344908028841019</v>
+        <v>0.344908058643341</v>
       </c>
       <c r="H76" t="n">
         <v>402900</v>
@@ -2602,7 +2602,7 @@
         <v>0.395428985357285</v>
       </c>
       <c r="G77" t="n">
-        <v>0.352757513523102</v>
+        <v>0.352757483720779</v>
       </c>
       <c r="H77" t="n">
         <v>206044</v>
@@ -2631,7 +2631,7 @@
         <v>0.401827991008759</v>
       </c>
       <c r="G78" t="n">
-        <v>0.358465969562531</v>
+        <v>0.358465999364853</v>
       </c>
       <c r="H78" t="n">
         <v>145425</v>
@@ -2660,7 +2660,7 @@
         <v>0.396028995513916</v>
       </c>
       <c r="G79" t="n">
-        <v>0.353292733430862</v>
+        <v>0.353292763233185</v>
       </c>
       <c r="H79" t="n">
         <v>82793</v>
@@ -2776,7 +2776,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060443878174</v>
+        <v>0.370060473680496</v>
       </c>
       <c r="H83" t="n">
         <v>687485</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157990217209</v>
+        <v>0.379157930612564</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -3008,7 +3008,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.37150239944458</v>
+        <v>0.371502429246902</v>
       </c>
       <c r="H91" t="n">
         <v>148553</v>
@@ -3124,7 +3124,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H95" t="n">
         <v>267568</v>
@@ -3211,7 +3211,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H98" t="n">
         <v>149597</v>
@@ -3240,7 +3240,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G99" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H99" t="n">
         <v>534781</v>
@@ -3385,7 +3385,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.35065832734108</v>
+        <v>0.350658357143402</v>
       </c>
       <c r="H104" t="n">
         <v>409447</v>
@@ -3443,7 +3443,7 @@
         <v>0.40022799372673</v>
       </c>
       <c r="G106" t="n">
-        <v>0.369197160005569</v>
+        <v>0.369197130203247</v>
       </c>
       <c r="H106" t="n">
         <v>3752445</v>
@@ -3472,7 +3472,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H107" t="n">
         <v>1327868</v>
@@ -3530,7 +3530,7 @@
         <v>0.386429995298386</v>
       </c>
       <c r="G109" t="n">
-        <v>0.356468975543976</v>
+        <v>0.356468945741653</v>
       </c>
       <c r="H109" t="n">
         <v>1359696</v>
@@ -3588,7 +3588,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.364309012889862</v>
+        <v>0.36430898308754</v>
       </c>
       <c r="H111" t="n">
         <v>269379</v>
@@ -3617,7 +3617,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313918113708</v>
+        <v>0.358313888311386</v>
       </c>
       <c r="H112" t="n">
         <v>133757</v>
@@ -3646,7 +3646,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H113" t="n">
         <v>105892</v>
@@ -3704,7 +3704,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H115" t="n">
         <v>399670</v>
@@ -3733,7 +3733,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H116" t="n">
         <v>471777</v>
@@ -3820,7 +3820,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.337838798761368</v>
+        <v>0.33783882856369</v>
       </c>
       <c r="H119" t="n">
         <v>2519386</v>
@@ -3849,7 +3849,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G120" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H120" t="n">
         <v>660483</v>
@@ -3936,7 +3936,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513103961945</v>
+        <v>0.359513133764267</v>
       </c>
       <c r="H123" t="n">
         <v>361479</v>
@@ -3965,7 +3965,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G124" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H124" t="n">
         <v>418732</v>
@@ -4197,7 +4197,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H132" t="n">
         <v>275307</v>
@@ -4226,7 +4226,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567830085754</v>
+        <v>0.312567800283432</v>
       </c>
       <c r="H133" t="n">
         <v>58287</v>
@@ -4313,7 +4313,7 @@
         <v>0.368932992219925</v>
       </c>
       <c r="G136" t="n">
-        <v>0.340328514575958</v>
+        <v>0.340328544378281</v>
       </c>
       <c r="H136" t="n">
         <v>146019</v>
@@ -4371,7 +4371,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H138" t="n">
         <v>190400</v>
@@ -4400,7 +4400,7 @@
         <v>0.378731995820999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.349367827177048</v>
+        <v>0.349367797374725</v>
       </c>
       <c r="H139" t="n">
         <v>108968</v>
@@ -4487,7 +4487,7 @@
         <v>0.380430996417999</v>
       </c>
       <c r="G142" t="n">
-        <v>0.350935071706772</v>
+        <v>0.350935101509094</v>
       </c>
       <c r="H142" t="n">
         <v>244048</v>
@@ -4516,7 +4516,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886932134628</v>
+        <v>0.353886961936951</v>
       </c>
       <c r="H143" t="n">
         <v>50099</v>
@@ -4603,7 +4603,7 @@
         <v>0.381931006908417</v>
       </c>
       <c r="G146" t="n">
-        <v>0.352318793535233</v>
+        <v>0.35231876373291</v>
       </c>
       <c r="H146" t="n">
         <v>86953</v>
@@ -4632,7 +4632,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163706302643</v>
+        <v>0.354163736104965</v>
       </c>
       <c r="H147" t="n">
         <v>1381221</v>
@@ -4661,7 +4661,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.344756424427032</v>
+        <v>0.34475639462471</v>
       </c>
       <c r="H148" t="n">
         <v>760552</v>
@@ -4719,7 +4719,7 @@
         <v>0.38782998919487</v>
       </c>
       <c r="G150" t="n">
-        <v>0.357760399580002</v>
+        <v>0.357760369777679</v>
       </c>
       <c r="H150" t="n">
         <v>73463</v>
@@ -4777,7 +4777,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H152" t="n">
         <v>138916</v>
@@ -4951,7 +4951,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212656736374</v>
+        <v>0.332212686538696</v>
       </c>
       <c r="H158" t="n">
         <v>1508122</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382423639297</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5154,7 +5154,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H165" t="n">
         <v>1547058</v>
@@ -5241,7 +5241,7 @@
         <v>0.342938005924225</v>
       </c>
       <c r="G168" t="n">
-        <v>0.316349029541016</v>
+        <v>0.316348999738693</v>
       </c>
       <c r="H168" t="n">
         <v>570779</v>
@@ -5357,7 +5357,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.326402068138123</v>
+        <v>0.326402097940445</v>
       </c>
       <c r="H172" t="n">
         <v>220072</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309859752655</v>
+        <v>0.32630980014801</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5415,7 +5415,7 @@
         <v>0.341937988996506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.315426558256149</v>
+        <v>0.315426528453827</v>
       </c>
       <c r="H174" t="n">
         <v>1029741</v>
@@ -5560,7 +5560,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G179" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H179" t="n">
         <v>231414</v>
@@ -5589,7 +5589,7 @@
         <v>0.342038005590439</v>
       </c>
       <c r="G180" t="n">
-        <v>0.315518796443939</v>
+        <v>0.315518826246262</v>
       </c>
       <c r="H180" t="n">
         <v>97882</v>
@@ -5705,7 +5705,7 @@
         <v>0.338939011096954</v>
       </c>
       <c r="G184" t="n">
-        <v>0.312660068273544</v>
+        <v>0.312660098075867</v>
       </c>
       <c r="H184" t="n">
         <v>501296</v>
@@ -5734,7 +5734,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305795192719</v>
+        <v>0.313305824995041</v>
       </c>
       <c r="H185" t="n">
         <v>269383</v>
@@ -5763,7 +5763,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G186" t="n">
-        <v>0.311829835176468</v>
+        <v>0.31182986497879</v>
       </c>
       <c r="H186" t="n">
         <v>107625</v>
@@ -5792,7 +5792,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H187" t="n">
         <v>969165</v>
@@ -5850,7 +5850,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H189" t="n">
         <v>96038</v>
@@ -5908,7 +5908,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G191" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H191" t="n">
         <v>53571</v>
@@ -5937,7 +5937,7 @@
         <v>0.338438987731934</v>
       </c>
       <c r="G192" t="n">
-        <v>0.312198847532272</v>
+        <v>0.31219881772995</v>
       </c>
       <c r="H192" t="n">
         <v>79208</v>
@@ -5995,7 +5995,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H194" t="n">
         <v>209554</v>
@@ -6024,7 +6024,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H195" t="n">
         <v>35089</v>
@@ -6053,7 +6053,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H196" t="n">
         <v>85046</v>
@@ -6082,7 +6082,7 @@
         <v>0.336838990449905</v>
       </c>
       <c r="G197" t="n">
-        <v>0.310722887516022</v>
+        <v>0.310722917318344</v>
       </c>
       <c r="H197" t="n">
         <v>191857</v>
@@ -6111,7 +6111,7 @@
         <v>0.337038993835449</v>
       </c>
       <c r="G198" t="n">
-        <v>0.310907393693924</v>
+        <v>0.310907363891602</v>
       </c>
       <c r="H198" t="n">
         <v>482576</v>
@@ -6140,7 +6140,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H199" t="n">
         <v>29451</v>
@@ -6198,7 +6198,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G201" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H201" t="n">
         <v>234454</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6314,7 +6314,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484525680542</v>
+        <v>0.338484555482864</v>
       </c>
       <c r="H205" t="n">
         <v>279724</v>
@@ -6343,7 +6343,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G206" t="n">
-        <v>0.340605318546295</v>
+        <v>0.340605288743973</v>
       </c>
       <c r="H206" t="n">
         <v>152266</v>
@@ -6372,7 +6372,7 @@
         <v>0.369233012199402</v>
       </c>
       <c r="G207" t="n">
-        <v>0.340605318546295</v>
+        <v>0.340605288743973</v>
       </c>
       <c r="H207" t="n">
         <v>160709</v>
@@ -6401,7 +6401,7 @@
         <v>0.372732996940613</v>
       </c>
       <c r="G208" t="n">
-        <v>0.343833923339844</v>
+        <v>0.343833953142166</v>
       </c>
       <c r="H208" t="n">
         <v>21151</v>
@@ -6459,7 +6459,7 @@
         <v>0.380531013011932</v>
       </c>
       <c r="G210" t="n">
-        <v>0.351027369499207</v>
+        <v>0.351027339696884</v>
       </c>
       <c r="H210" t="n">
         <v>537773</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071438312531</v>
+        <v>0.354071497917175</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6575,7 +6575,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837958097458</v>
+        <v>0.356837928295135</v>
       </c>
       <c r="H214" t="n">
         <v>141958</v>
@@ -6633,7 +6633,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998785018921</v>
+        <v>0.348998814821243</v>
       </c>
       <c r="H216" t="n">
         <v>202870</v>
@@ -6662,7 +6662,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.338300049304962</v>
+        <v>0.33830001950264</v>
       </c>
       <c r="H217" t="n">
         <v>1242085</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6749,7 +6749,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751465797424</v>
+        <v>0.331751435995102</v>
       </c>
       <c r="H220" t="n">
         <v>241870</v>
@@ -6778,7 +6778,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.32612532377243</v>
+        <v>0.326125353574753</v>
       </c>
       <c r="H221" t="n">
         <v>240850</v>
@@ -6894,7 +6894,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897642850876</v>
+        <v>0.322897613048553</v>
       </c>
       <c r="H225" t="n">
         <v>81571</v>
@@ -7068,7 +7068,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558079242706</v>
+        <v>0.324558049440384</v>
       </c>
       <c r="H231" t="n">
         <v>85940</v>
@@ -7300,7 +7300,7 @@
         <v>0.345937997102737</v>
       </c>
       <c r="G239" t="n">
-        <v>0.31911638379097</v>
+        <v>0.319116413593292</v>
       </c>
       <c r="H239" t="n">
         <v>206647</v>
@@ -7329,7 +7329,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.326402068138123</v>
+        <v>0.326402097940445</v>
       </c>
       <c r="H240" t="n">
         <v>211099</v>
@@ -7387,7 +7387,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397162914276</v>
+        <v>0.332397192716599</v>
       </c>
       <c r="H242" t="n">
         <v>278620</v>
@@ -7474,7 +7474,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712236404419</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H245" t="n">
         <v>783334</v>
@@ -7503,7 +7503,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H246" t="n">
         <v>332438</v>
@@ -7561,7 +7561,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018429517746</v>
+        <v>0.344018399715424</v>
       </c>
       <c r="H248" t="n">
         <v>335681</v>
@@ -7590,7 +7590,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H249" t="n">
         <v>515825</v>
@@ -7648,7 +7648,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241235017776</v>
+        <v>0.353241264820099</v>
       </c>
       <c r="H251" t="n">
         <v>591930</v>
@@ -7822,7 +7822,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396322250366</v>
+        <v>0.351396292448044</v>
       </c>
       <c r="H257" t="n">
         <v>191994</v>
@@ -7880,7 +7880,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H259" t="n">
         <v>372572</v>
@@ -7938,7 +7938,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.37565353512764</v>
+        <v>0.375653505325317</v>
       </c>
       <c r="H261" t="n">
         <v>685961</v>
@@ -7967,7 +7967,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429829359055</v>
+        <v>0.385429799556732</v>
       </c>
       <c r="H262" t="n">
         <v>463854</v>
@@ -8025,7 +8025,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H264" t="n">
         <v>828739</v>
@@ -8083,7 +8083,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.37094983458519</v>
+        <v>0.370949864387512</v>
       </c>
       <c r="H266" t="n">
         <v>191080</v>
@@ -8141,7 +8141,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G268" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H268" t="n">
         <v>145464</v>
@@ -8228,7 +8228,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G271" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H271" t="n">
         <v>143383</v>
@@ -8286,7 +8286,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G273" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H273" t="n">
         <v>229996</v>
@@ -8315,7 +8315,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.38137099146843</v>
+        <v>0.381370931863785</v>
       </c>
       <c r="H274" t="n">
         <v>262282</v>
@@ -8373,7 +8373,7 @@
         <v>0.410425990819931</v>
       </c>
       <c r="G276" t="n">
-        <v>0.37860444188118</v>
+        <v>0.378604471683502</v>
       </c>
       <c r="H276" t="n">
         <v>278198</v>
@@ -8402,7 +8402,7 @@
         <v>0.411826014518738</v>
       </c>
       <c r="G277" t="n">
-        <v>0.379895925521851</v>
+        <v>0.379895955324173</v>
       </c>
       <c r="H277" t="n">
         <v>215538</v>
@@ -8460,7 +8460,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H279" t="n">
         <v>96256</v>
@@ -8518,7 +8518,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H281" t="n">
         <v>107938</v>
@@ -8547,7 +8547,7 @@
         <v>0.407326996326447</v>
       </c>
       <c r="G282" t="n">
-        <v>0.37574577331543</v>
+        <v>0.375745743513107</v>
       </c>
       <c r="H282" t="n">
         <v>260882</v>
@@ -8634,7 +8634,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H285" t="n">
         <v>681169</v>
@@ -8692,7 +8692,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G287" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H287" t="n">
         <v>280249</v>
@@ -8721,7 +8721,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G288" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H288" t="n">
         <v>218241</v>
@@ -8750,7 +8750,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531818389893</v>
+        <v>0.373531848192215</v>
       </c>
       <c r="H289" t="n">
         <v>229876</v>
@@ -8866,7 +8866,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714666843414</v>
+        <v>0.430714637041092</v>
       </c>
       <c r="H293" t="n">
         <v>1274513</v>
@@ -8953,7 +8953,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757871389389</v>
+        <v>0.433757841587067</v>
       </c>
       <c r="H296" t="n">
         <v>764989</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340779066086</v>
+        <v>0.436340808868408</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9098,7 +9098,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145651578903</v>
+        <v>0.467145621776581</v>
       </c>
       <c r="H301" t="n">
         <v>1481695</v>
@@ -9301,7 +9301,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475445985794067</v>
+        <v>0.475446045398712</v>
       </c>
       <c r="H308" t="n">
         <v>1980457</v>
@@ -9330,7 +9330,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839458465576</v>
+        <v>0.464839428663254</v>
       </c>
       <c r="H309" t="n">
         <v>2438508</v>
@@ -9359,7 +9359,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286023139954</v>
+        <v>0.483286052942276</v>
       </c>
       <c r="H310" t="n">
         <v>1188532</v>
@@ -9388,7 +9388,7 @@
         <v>0.558399975299835</v>
       </c>
       <c r="G311" t="n">
-        <v>0.515105545520782</v>
+        <v>0.515105605125427</v>
       </c>
       <c r="H311" t="n">
         <v>2223034</v>
@@ -9446,7 +9446,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G313" t="n">
-        <v>0.531245112419128</v>
+        <v>0.531245172023773</v>
       </c>
       <c r="H313" t="n">
         <v>1840311</v>
@@ -9591,7 +9591,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774081230164</v>
+        <v>0.542774140834808</v>
       </c>
       <c r="H318" t="n">
         <v>750114</v>
@@ -9649,7 +9649,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G320" t="n">
-        <v>0.557992041110992</v>
+        <v>0.557991981506348</v>
       </c>
       <c r="H320" t="n">
         <v>846974</v>
@@ -9678,7 +9678,7 @@
         <v>0.601891994476318</v>
       </c>
       <c r="G321" t="n">
-        <v>0.555225551128387</v>
+        <v>0.555225610733032</v>
       </c>
       <c r="H321" t="n">
         <v>722821</v>
@@ -9765,7 +9765,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345497131348</v>
+        <v>0.595345556735992</v>
       </c>
       <c r="H324" t="n">
         <v>1537366</v>
@@ -9794,7 +9794,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495649337769</v>
+        <v>0.599495708942413</v>
       </c>
       <c r="H325" t="n">
         <v>535825</v>
@@ -9823,7 +9823,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267998218536</v>
+        <v>0.596267938613892</v>
       </c>
       <c r="H326" t="n">
         <v>478574</v>
@@ -9910,7 +9910,7 @@
         <v>0.661381006240845</v>
       </c>
       <c r="G329" t="n">
-        <v>0.610102236270905</v>
+        <v>0.61010217666626</v>
       </c>
       <c r="H329" t="n">
         <v>1371286</v>
@@ -10055,7 +10055,7 @@
         <v>0.690375983715057</v>
       </c>
       <c r="G334" t="n">
-        <v>0.636849164962769</v>
+        <v>0.636849105358124</v>
       </c>
       <c r="H334" t="n">
         <v>3228462</v>
@@ -10084,7 +10084,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634542942047119</v>
+        <v>0.634543001651764</v>
       </c>
       <c r="H335" t="n">
         <v>2493902</v>
@@ -10113,7 +10113,7 @@
         <v>0.694875001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>0.640999376773834</v>
+        <v>0.640999317169189</v>
       </c>
       <c r="H336" t="n">
         <v>1092710</v>
@@ -10200,7 +10200,7 @@
         <v>0.696874976158142</v>
       </c>
       <c r="G339" t="n">
-        <v>0.642844200134277</v>
+        <v>0.642844259738922</v>
       </c>
       <c r="H339" t="n">
         <v>725692</v>
@@ -10229,7 +10229,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076816082001</v>
+        <v>0.640076875686646</v>
       </c>
       <c r="H340" t="n">
         <v>1222262</v>
@@ -10316,7 +10316,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G343" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H343" t="n">
         <v>1199670</v>
@@ -10345,7 +10345,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G344" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H344" t="n">
         <v>1226901</v>
@@ -10374,7 +10374,7 @@
         <v>0.653383016586304</v>
       </c>
       <c r="G345" t="n">
-        <v>0.602724313735962</v>
+        <v>0.602724373340607</v>
       </c>
       <c r="H345" t="n">
         <v>1424542</v>
@@ -10403,7 +10403,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.62808758020401</v>
+        <v>0.628087520599365</v>
       </c>
       <c r="H346" t="n">
         <v>1835882</v>
@@ -10432,7 +10432,7 @@
         <v>0.674879014492035</v>
       </c>
       <c r="G347" t="n">
-        <v>0.622553646564484</v>
+        <v>0.622553706169128</v>
       </c>
       <c r="H347" t="n">
         <v>1501004</v>
@@ -10490,7 +10490,7 @@
         <v>0.670879006385803</v>
       </c>
       <c r="G349" t="n">
-        <v>0.618863761425018</v>
+        <v>0.618863821029663</v>
       </c>
       <c r="H349" t="n">
         <v>716788</v>
@@ -10548,7 +10548,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651720046997</v>
+        <v>0.597651660442352</v>
       </c>
       <c r="H351" t="n">
         <v>1472477</v>
@@ -10664,7 +10664,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617481052875519</v>
+        <v>0.617480993270874</v>
       </c>
       <c r="H355" t="n">
         <v>615646</v>
@@ -10693,7 +10693,7 @@
         <v>0.676877975463867</v>
       </c>
       <c r="G356" t="n">
-        <v>0.624397695064545</v>
+        <v>0.6243976354599</v>
       </c>
       <c r="H356" t="n">
         <v>591723</v>
@@ -10751,7 +10751,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165079116821</v>
+        <v>0.627165138721466</v>
       </c>
       <c r="H358" t="n">
         <v>444207</v>
@@ -10780,7 +10780,7 @@
         <v>0.668879985809326</v>
       </c>
       <c r="G359" t="n">
-        <v>0.617019712924957</v>
+        <v>0.617019772529602</v>
       </c>
       <c r="H359" t="n">
         <v>534811</v>
@@ -10809,7 +10809,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G360" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H360" t="n">
         <v>434952</v>
@@ -10838,7 +10838,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179794788361</v>
+        <v>0.609179735183716</v>
       </c>
       <c r="H361" t="n">
         <v>498433</v>
@@ -10867,7 +10867,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G362" t="n">
-        <v>0.612408399581909</v>
+        <v>0.612408339977264</v>
       </c>
       <c r="H362" t="n">
         <v>510897</v>
@@ -10896,7 +10896,7 @@
         <v>0.663881003856659</v>
       </c>
       <c r="G363" t="n">
-        <v>0.612408399581909</v>
+        <v>0.612408339977264</v>
       </c>
       <c r="H363" t="n">
         <v>588330</v>
@@ -10954,7 +10954,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829319477081</v>
+        <v>0.608829379081726</v>
       </c>
       <c r="H365" t="n">
         <v>210377</v>
@@ -10983,7 +10983,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.613070249557495</v>
+        <v>0.61307030916214</v>
       </c>
       <c r="H366" t="n">
         <v>341904</v>
@@ -11273,7 +11273,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969141960144</v>
+        <v>0.581969201564789</v>
       </c>
       <c r="H376" t="n">
         <v>259131</v>
@@ -11389,7 +11389,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.573958694934845</v>
+        <v>0.57395875453949</v>
       </c>
       <c r="H380" t="n">
         <v>251076</v>
@@ -11418,7 +11418,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152659893036</v>
+        <v>0.587152719497681</v>
       </c>
       <c r="H381" t="n">
         <v>198695</v>
@@ -11447,7 +11447,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555200576782</v>
+        <v>0.580555260181427</v>
       </c>
       <c r="H382" t="n">
         <v>558855</v>
@@ -11505,7 +11505,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H384" t="n">
         <v>1352746</v>
@@ -11563,7 +11563,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H386" t="n">
         <v>141943</v>
@@ -11592,7 +11592,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H387" t="n">
         <v>349861</v>
@@ -11708,7 +11708,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H391" t="n">
         <v>289335</v>
@@ -11737,7 +11737,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741928577423</v>
+        <v>0.544741868972778</v>
       </c>
       <c r="H392" t="n">
         <v>329337</v>
@@ -11766,7 +11766,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396800041199</v>
+        <v>0.550396740436554</v>
       </c>
       <c r="H393" t="n">
         <v>280658</v>
@@ -11795,7 +11795,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H394" t="n">
         <v>290140</v>
@@ -11882,7 +11882,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H397" t="n">
         <v>459584</v>
@@ -11911,7 +11911,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H398" t="n">
         <v>210300</v>
@@ -12027,7 +12027,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H402" t="n">
         <v>228411</v>
@@ -12172,7 +12172,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H407" t="n">
         <v>288350</v>
@@ -12201,7 +12201,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H408" t="n">
         <v>253441</v>
@@ -12230,7 +12230,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H409" t="n">
         <v>269272</v>
@@ -12259,7 +12259,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H410" t="n">
         <v>183867</v>
@@ -12288,7 +12288,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040151596069</v>
+        <v>0.548040091991425</v>
       </c>
       <c r="H411" t="n">
         <v>89021</v>
@@ -12346,7 +12346,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H413" t="n">
         <v>291996</v>
@@ -12433,7 +12433,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731362342834</v>
+        <v>0.536731421947479</v>
       </c>
       <c r="H416" t="n">
         <v>473625</v>
@@ -12520,7 +12520,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H419" t="n">
         <v>180174</v>
@@ -12549,7 +12549,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454033374786</v>
+        <v>0.549454092979431</v>
       </c>
       <c r="H420" t="n">
         <v>451568</v>
@@ -12607,7 +12607,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.54238623380661</v>
+        <v>0.542386293411255</v>
       </c>
       <c r="H422" t="n">
         <v>215255</v>
@@ -12665,7 +12665,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H424" t="n">
         <v>209758</v>
@@ -12723,7 +12723,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H426" t="n">
         <v>156206</v>
@@ -12752,7 +12752,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.524479150772095</v>
+        <v>0.52447909116745</v>
       </c>
       <c r="H427" t="n">
         <v>232817</v>
@@ -12839,7 +12839,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H430" t="n">
         <v>130630</v>
@@ -12897,7 +12897,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180868148804</v>
+        <v>0.521180927753448</v>
       </c>
       <c r="H432" t="n">
         <v>387167</v>
@@ -12984,7 +12984,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720080852509</v>
+        <v>0.528720021247864</v>
       </c>
       <c r="H435" t="n">
         <v>816289</v>
@@ -13100,7 +13100,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H439" t="n">
         <v>699890</v>
@@ -13129,7 +13129,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H440" t="n">
         <v>444610</v>
@@ -13158,7 +13158,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H441" t="n">
         <v>292621</v>
@@ -13245,7 +13245,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H444" t="n">
         <v>1107250</v>
@@ -13274,7 +13274,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807471752167</v>
+        <v>0.592807531356812</v>
       </c>
       <c r="H445" t="n">
         <v>663729</v>
@@ -13332,7 +13332,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577107906342</v>
+        <v>0.596577048301697</v>
       </c>
       <c r="H447" t="n">
         <v>238428</v>
@@ -13361,7 +13361,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.59516316652298</v>
+        <v>0.595163106918335</v>
       </c>
       <c r="H448" t="n">
         <v>218066</v>
@@ -13390,7 +13390,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772086143494</v>
+        <v>0.609772026538849</v>
       </c>
       <c r="H449" t="n">
         <v>909618</v>
@@ -13448,7 +13448,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876284599304</v>
+        <v>0.599876224994659</v>
       </c>
       <c r="H451" t="n">
         <v>477138</v>
@@ -13738,7 +13738,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H461" t="n">
         <v>114187</v>
@@ -13767,7 +13767,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947234630585</v>
+        <v>0.565947294235229</v>
       </c>
       <c r="H462" t="n">
         <v>238863</v>
@@ -13883,7 +13883,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533293247223</v>
+        <v>0.564533352851868</v>
       </c>
       <c r="H466" t="n">
         <v>222204</v>
@@ -13970,7 +13970,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H469" t="n">
         <v>139232</v>
@@ -14115,7 +14115,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H474" t="n">
         <v>149208</v>
@@ -14144,7 +14144,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H475" t="n">
         <v>148025</v>
@@ -14202,7 +14202,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.537673115730286</v>
+        <v>0.53767317533493</v>
       </c>
       <c r="H477" t="n">
         <v>352368</v>
@@ -14405,7 +14405,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100654602051</v>
+        <v>0.506100714206696</v>
       </c>
       <c r="H484" t="n">
         <v>271973</v>
@@ -14695,7 +14695,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H494" t="n">
         <v>58278</v>
@@ -14724,7 +14724,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H495" t="n">
         <v>163569</v>
@@ -14840,7 +14840,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H499" t="n">
         <v>78535</v>
@@ -14869,7 +14869,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H500" t="n">
         <v>70687</v>
@@ -14927,7 +14927,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997409820557</v>
+        <v>0.515997350215912</v>
       </c>
       <c r="H502" t="n">
         <v>149092</v>
@@ -14956,7 +14956,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194495439529</v>
+        <v>0.488194525241852</v>
       </c>
       <c r="H503" t="n">
         <v>1026439</v>
@@ -14985,7 +14985,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H504" t="n">
         <v>196576</v>
@@ -15101,7 +15101,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.512226819992065</v>
+        <v>0.51222687959671</v>
       </c>
       <c r="H508" t="n">
         <v>41572</v>
@@ -15188,7 +15188,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H511" t="n">
         <v>235907</v>
@@ -15217,7 +15217,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H512" t="n">
         <v>80711</v>
@@ -15246,7 +15246,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H513" t="n">
         <v>68229</v>
@@ -15275,7 +15275,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H514" t="n">
         <v>429758</v>
@@ -15362,7 +15362,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H517" t="n">
         <v>143705</v>
@@ -15507,7 +15507,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H522" t="n">
         <v>79164</v>
@@ -15536,7 +15536,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H523" t="n">
         <v>97732</v>
@@ -15594,7 +15594,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H525" t="n">
         <v>53867</v>
@@ -15710,7 +15710,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H529" t="n">
         <v>118746</v>
@@ -15797,7 +15797,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H532" t="n">
         <v>205602</v>
@@ -15855,7 +15855,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H534" t="n">
         <v>98856</v>
@@ -15913,7 +15913,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.51835298538208</v>
+        <v>0.518352925777435</v>
       </c>
       <c r="H536" t="n">
         <v>79457</v>
@@ -15942,7 +15942,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.49384930729866</v>
+        <v>0.493849337100983</v>
       </c>
       <c r="H537" t="n">
         <v>518619</v>
@@ -16000,7 +16000,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H539" t="n">
         <v>178433</v>
@@ -16029,7 +16029,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539653778076</v>
+        <v>0.482539623975754</v>
       </c>
       <c r="H540" t="n">
         <v>175327</v>
@@ -16116,7 +16116,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770047426224</v>
+        <v>0.478770077228546</v>
       </c>
       <c r="H543" t="n">
         <v>269915</v>
@@ -16145,7 +16145,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H544" t="n">
         <v>168852</v>
@@ -16174,7 +16174,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H545" t="n">
         <v>96811</v>
@@ -16261,7 +16261,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H548" t="n">
         <v>145160</v>
@@ -16290,7 +16290,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H549" t="n">
         <v>92949</v>
@@ -16319,7 +16319,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H550" t="n">
         <v>133866</v>
@@ -16377,7 +16377,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.489137142896652</v>
+        <v>0.48913711309433</v>
       </c>
       <c r="H552" t="n">
         <v>240396</v>
@@ -16580,7 +16580,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H559" t="n">
         <v>314325</v>
@@ -16725,7 +16725,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H564" t="n">
         <v>355078</v>
@@ -16783,7 +16783,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H566" t="n">
         <v>370087</v>
@@ -16812,7 +16812,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H567" t="n">
         <v>425158</v>
@@ -16870,7 +16870,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931687831879</v>
+        <v>0.467931717634201</v>
       </c>
       <c r="H569" t="n">
         <v>298487</v>
@@ -17218,7 +17218,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909810304642</v>
+        <v>0.451909840106964</v>
       </c>
       <c r="H581" t="n">
         <v>283637</v>
@@ -17421,7 +17421,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469815999269485</v>
+        <v>0.469816029071808</v>
       </c>
       <c r="H588" t="n">
         <v>121246</v>
@@ -17537,7 +17537,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H592" t="n">
         <v>106747</v>
@@ -17624,7 +17624,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H595" t="n">
         <v>147417</v>
@@ -17682,7 +17682,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H597" t="n">
         <v>59239</v>
@@ -17711,7 +17711,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H598" t="n">
         <v>241824</v>
@@ -17827,7 +17827,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H602" t="n">
         <v>287903</v>
@@ -17885,7 +17885,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H604" t="n">
         <v>1272412</v>
@@ -17914,7 +17914,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H605" t="n">
         <v>1104869</v>
@@ -18001,7 +18001,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H608" t="n">
         <v>43571</v>
@@ -18030,7 +18030,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H609" t="n">
         <v>69465</v>
@@ -18088,7 +18088,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H611" t="n">
         <v>57385</v>
@@ -18117,7 +18117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H612" t="n">
         <v>209658</v>
@@ -18146,7 +18146,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H613" t="n">
         <v>10902</v>
@@ -18204,7 +18204,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H615" t="n">
         <v>157901</v>
@@ -18233,7 +18233,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H616" t="n">
         <v>192728</v>
@@ -18291,7 +18291,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H618" t="n">
         <v>74901</v>
@@ -18407,7 +18407,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H622" t="n">
         <v>442685</v>
@@ -80038,6 +80038,35 @@
         <v>191351</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.746999979019165</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.73199999332428</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>342203</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.376928627490997</v>
+        <v>0.37692865729332</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920309305191</v>
+        <v>0.367920339107513</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -572,7 +572,7 @@
         <v>0.410126000642776</v>
       </c>
       <c r="G7" t="n">
-        <v>0.365868479013443</v>
+        <v>0.365868508815765</v>
       </c>
       <c r="H7" t="n">
         <v>71244</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272164583206</v>
+        <v>0.321272134780884</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -920,7 +920,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450561285019</v>
+        <v>0.321450531482697</v>
       </c>
       <c r="H19" t="n">
         <v>460284</v>
@@ -1123,7 +1123,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696359395981</v>
+        <v>0.308696389198303</v>
       </c>
       <c r="H26" t="n">
         <v>149000</v>
@@ -1181,7 +1181,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205849885941</v>
+        <v>0.282205820083618</v>
       </c>
       <c r="H28" t="n">
         <v>388643</v>
@@ -1210,7 +1210,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979585170746</v>
+        <v>0.293979614973068</v>
       </c>
       <c r="H29" t="n">
         <v>282359</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830327749252</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1471,7 +1471,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114499568939</v>
+        <v>0.301114529371262</v>
       </c>
       <c r="H38" t="n">
         <v>6327</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335514307022</v>
+        <v>0.294335544109344</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500491857529</v>
+        <v>0.290500462055206</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1703,7 +1703,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.301203697919846</v>
+        <v>0.301203727722168</v>
       </c>
       <c r="H46" t="n">
         <v>245666</v>
@@ -1761,7 +1761,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166300058365</v>
+        <v>0.303166329860687</v>
       </c>
       <c r="H48" t="n">
         <v>159693</v>
@@ -1819,7 +1819,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471322774887</v>
+        <v>0.301471352577209</v>
       </c>
       <c r="H50" t="n">
         <v>368157</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007637739182</v>
+        <v>0.335007607936859</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1964,7 +1964,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="n">
         <v>361299</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.370149672031403</v>
+        <v>0.37014964222908</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2138,7 +2138,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820730209351</v>
+        <v>0.377820700407028</v>
       </c>
       <c r="H61" t="n">
         <v>76617</v>
@@ -2283,7 +2283,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203594684601</v>
+        <v>0.353203564882278</v>
       </c>
       <c r="H66" t="n">
         <v>34491</v>
@@ -2341,7 +2341,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G68" t="n">
-        <v>0.347851902246475</v>
+        <v>0.347851932048798</v>
       </c>
       <c r="H68" t="n">
         <v>53474</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178721904755</v>
+        <v>0.359178751707077</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2457,7 +2457,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376771211624</v>
+        <v>0.358376741409302</v>
       </c>
       <c r="H72" t="n">
         <v>393696</v>
@@ -2573,7 +2573,7 @@
         <v>0.386629998683929</v>
       </c>
       <c r="G76" t="n">
-        <v>0.344908058643341</v>
+        <v>0.344908028841019</v>
       </c>
       <c r="H76" t="n">
         <v>402900</v>
@@ -2689,7 +2689,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306271791458</v>
+        <v>0.357306301593781</v>
       </c>
       <c r="H80" t="n">
         <v>465916</v>
@@ -2776,7 +2776,7 @@
         <v>0.414824992418289</v>
       </c>
       <c r="G83" t="n">
-        <v>0.370060473680496</v>
+        <v>0.370060443878174</v>
       </c>
       <c r="H83" t="n">
         <v>687485</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157960414886</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2921,7 +2921,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701615095139</v>
+        <v>0.372701585292816</v>
       </c>
       <c r="H88" t="n">
         <v>354215</v>
@@ -3008,7 +3008,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.371502429246902</v>
+        <v>0.37150239944458</v>
       </c>
       <c r="H91" t="n">
         <v>148553</v>
@@ -3153,7 +3153,7 @@
         <v>0.399827986955643</v>
       </c>
       <c r="G96" t="n">
-        <v>0.368828147649765</v>
+        <v>0.368828177452087</v>
       </c>
       <c r="H96" t="n">
         <v>378647</v>
@@ -3182,7 +3182,7 @@
         <v>0.393429011106491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.362925320863724</v>
+        <v>0.362925291061401</v>
       </c>
       <c r="H97" t="n">
         <v>371654</v>
@@ -3211,7 +3211,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H98" t="n">
         <v>149597</v>
@@ -3356,7 +3356,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H103" t="n">
         <v>972529</v>
@@ -3472,7 +3472,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H107" t="n">
         <v>1327868</v>
@@ -3588,7 +3588,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36430898308754</v>
+        <v>0.364309012889862</v>
       </c>
       <c r="H111" t="n">
         <v>269379</v>
@@ -3617,7 +3617,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313888311386</v>
+        <v>0.358313918113708</v>
       </c>
       <c r="H112" t="n">
         <v>133757</v>
@@ -3646,7 +3646,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H113" t="n">
         <v>105892</v>
@@ -3733,7 +3733,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H116" t="n">
         <v>471777</v>
@@ -3907,7 +3907,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H122" t="n">
         <v>582251</v>
@@ -3936,7 +3936,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513133764267</v>
+        <v>0.359513103961945</v>
       </c>
       <c r="H123" t="n">
         <v>361479</v>
@@ -4110,7 +4110,7 @@
         <v>0.350237011909485</v>
       </c>
       <c r="G129" t="n">
-        <v>0.323082119226456</v>
+        <v>0.323082089424133</v>
       </c>
       <c r="H129" t="n">
         <v>128422</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169452190399</v>
+        <v>0.329169481992722</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4342,7 +4342,7 @@
         <v>0.374033004045486</v>
       </c>
       <c r="G137" t="n">
-        <v>0.345033138990402</v>
+        <v>0.34503310918808</v>
       </c>
       <c r="H137" t="n">
         <v>55292</v>
@@ -4603,7 +4603,7 @@
         <v>0.381931006908417</v>
       </c>
       <c r="G146" t="n">
-        <v>0.35231876373291</v>
+        <v>0.352318793535233</v>
       </c>
       <c r="H146" t="n">
         <v>86953</v>
@@ -4719,7 +4719,7 @@
         <v>0.38782998919487</v>
       </c>
       <c r="G150" t="n">
-        <v>0.357760369777679</v>
+        <v>0.357760399580002</v>
       </c>
       <c r="H150" t="n">
         <v>73463</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619998216629</v>
+        <v>0.341620028018951</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4922,7 +4922,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843733787537</v>
+        <v>0.331843703985214</v>
       </c>
       <c r="H157" t="n">
         <v>1100576</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5154,7 +5154,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H165" t="n">
         <v>1547058</v>
@@ -5241,7 +5241,7 @@
         <v>0.342938005924225</v>
       </c>
       <c r="G168" t="n">
-        <v>0.316348999738693</v>
+        <v>0.316349029541016</v>
       </c>
       <c r="H168" t="n">
         <v>570779</v>
@@ -5357,7 +5357,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.326402097940445</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H172" t="n">
         <v>220072</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.32630980014801</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5444,7 +5444,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H175" t="n">
         <v>311100</v>
@@ -5473,7 +5473,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H176" t="n">
         <v>198283</v>
@@ -5502,7 +5502,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H177" t="n">
         <v>167208</v>
@@ -5531,7 +5531,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H178" t="n">
         <v>68182</v>
@@ -5676,7 +5676,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761216640472</v>
+        <v>0.319761246442795</v>
       </c>
       <c r="H183" t="n">
         <v>499322</v>
@@ -5792,7 +5792,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H187" t="n">
         <v>969165</v>
@@ -5850,7 +5850,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H189" t="n">
         <v>96038</v>
@@ -5995,7 +5995,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H194" t="n">
         <v>209554</v>
@@ -6024,7 +6024,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H195" t="n">
         <v>35089</v>
@@ -6082,7 +6082,7 @@
         <v>0.336838990449905</v>
       </c>
       <c r="G197" t="n">
-        <v>0.310722917318344</v>
+        <v>0.310722887516022</v>
       </c>
       <c r="H197" t="n">
         <v>191857</v>
@@ -6111,7 +6111,7 @@
         <v>0.337038993835449</v>
       </c>
       <c r="G198" t="n">
-        <v>0.310907363891602</v>
+        <v>0.310907393693924</v>
       </c>
       <c r="H198" t="n">
         <v>482576</v>
@@ -6140,7 +6140,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H199" t="n">
         <v>29451</v>
@@ -6227,7 +6227,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.32354336977005</v>
+        <v>0.323543339967728</v>
       </c>
       <c r="H202" t="n">
         <v>232428</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6314,7 +6314,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484555482864</v>
+        <v>0.338484525680542</v>
       </c>
       <c r="H205" t="n">
         <v>279724</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071497917175</v>
+        <v>0.354071468114853</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6517,7 +6517,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G212" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H212" t="n">
         <v>184112</v>
@@ -6546,7 +6546,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G213" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H213" t="n">
         <v>256167</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333473205566</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6662,7 +6662,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.33830001950264</v>
+        <v>0.338300049304962</v>
       </c>
       <c r="H217" t="n">
         <v>1242085</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6749,7 +6749,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751435995102</v>
+        <v>0.331751465797424</v>
       </c>
       <c r="H220" t="n">
         <v>241870</v>
@@ -6778,7 +6778,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.326125353574753</v>
+        <v>0.32612532377243</v>
       </c>
       <c r="H221" t="n">
         <v>240850</v>
@@ -6894,7 +6894,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="n">
         <v>81571</v>
@@ -6923,7 +6923,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G226" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H226" t="n">
         <v>90191</v>
@@ -7010,7 +7010,7 @@
         <v>0.352436006069183</v>
       </c>
       <c r="G229" t="n">
-        <v>0.325110614299774</v>
+        <v>0.325110644102097</v>
       </c>
       <c r="H229" t="n">
         <v>52752</v>
@@ -7068,7 +7068,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558049440384</v>
+        <v>0.324558079242706</v>
       </c>
       <c r="H231" t="n">
         <v>85940</v>
@@ -7126,7 +7126,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344124317169</v>
+        <v>0.322344154119492</v>
       </c>
       <c r="H233" t="n">
         <v>60253</v>
@@ -7155,7 +7155,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G234" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H234" t="n">
         <v>61950</v>
@@ -7184,7 +7184,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183297395706</v>
+        <v>0.330183267593384</v>
       </c>
       <c r="H235" t="n">
         <v>95241</v>
@@ -7329,7 +7329,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.326402097940445</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H240" t="n">
         <v>211099</v>
@@ -7561,7 +7561,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018399715424</v>
+        <v>0.344018429517746</v>
       </c>
       <c r="H248" t="n">
         <v>335681</v>
@@ -7648,7 +7648,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241264820099</v>
+        <v>0.353241235017776</v>
       </c>
       <c r="H251" t="n">
         <v>591930</v>
@@ -7735,7 +7735,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595508098602</v>
+        <v>0.352595537900925</v>
       </c>
       <c r="H254" t="n">
         <v>213674</v>
@@ -7880,7 +7880,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H259" t="n">
         <v>372572</v>
@@ -8025,7 +8025,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H264" t="n">
         <v>828739</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8199,7 +8199,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342466592789</v>
+        <v>0.379342436790466</v>
       </c>
       <c r="H270" t="n">
         <v>170128</v>
@@ -8750,7 +8750,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531848192215</v>
+        <v>0.373531818389893</v>
       </c>
       <c r="H289" t="n">
         <v>229876</v>
@@ -8895,7 +8895,7 @@
         <v>0.469814985990524</v>
       </c>
       <c r="G294" t="n">
-        <v>0.433388859033585</v>
+        <v>0.433388888835907</v>
       </c>
       <c r="H294" t="n">
         <v>517174</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340808868408</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9098,7 +9098,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145621776581</v>
+        <v>0.467145651578903</v>
       </c>
       <c r="H301" t="n">
         <v>1481695</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.48881995677948</v>
+        <v>0.488819897174835</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9446,7 +9446,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G313" t="n">
-        <v>0.531245172023773</v>
+        <v>0.531245112419128</v>
       </c>
       <c r="H313" t="n">
         <v>1840311</v>
@@ -9504,7 +9504,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099805831909</v>
+        <v>0.521099865436554</v>
       </c>
       <c r="H315" t="n">
         <v>1732441</v>
@@ -9562,7 +9562,7 @@
         <v>0.593892991542816</v>
       </c>
       <c r="G317" t="n">
-        <v>0.547846734523773</v>
+        <v>0.547846794128418</v>
       </c>
       <c r="H317" t="n">
         <v>846434</v>
@@ -9591,7 +9591,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774140834808</v>
+        <v>0.542774081230164</v>
       </c>
       <c r="H318" t="n">
         <v>750114</v>
@@ -9823,7 +9823,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267938613892</v>
+        <v>0.596267998218536</v>
       </c>
       <c r="H326" t="n">
         <v>478574</v>
@@ -10084,7 +10084,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634543001651764</v>
+        <v>0.634542942047119</v>
       </c>
       <c r="H335" t="n">
         <v>2493902</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10316,7 +10316,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G343" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H343" t="n">
         <v>1199670</v>
@@ -10345,7 +10345,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G344" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H344" t="n">
         <v>1226901</v>
@@ -10403,7 +10403,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.628087520599365</v>
+        <v>0.62808758020401</v>
       </c>
       <c r="H346" t="n">
         <v>1835882</v>
@@ -10461,7 +10461,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942273616791</v>
+        <v>0.617942214012146</v>
       </c>
       <c r="H348" t="n">
         <v>976577</v>
@@ -10635,7 +10635,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607796967029572</v>
+        <v>0.607797026634216</v>
       </c>
       <c r="H354" t="n">
         <v>1281515</v>
@@ -10809,7 +10809,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G360" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H360" t="n">
         <v>434952</v>
@@ -10838,7 +10838,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179735183716</v>
+        <v>0.609179794788361</v>
       </c>
       <c r="H361" t="n">
         <v>498433</v>
@@ -80055,7 +80055,7 @@
         <v>0.75</v>
       </c>
       <c r="E2748" t="n">
-        <v>0.73199999332428</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="F2748" t="n">
         <v>0.730000019073486</v>
@@ -80064,9 +80064,38 @@
         <v>0.730000019073486</v>
       </c>
       <c r="H2748" t="n">
-        <v>342203</v>
+        <v>345696</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.721000015735626</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.731000006198883</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.731000006198883</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>339222</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.405427008867264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.361676603555679</v>
+        <v>0.361676573753357</v>
       </c>
       <c r="H2" t="n">
         <v>90003</v>
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37692865729332</v>
+        <v>0.376928627490997</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920339107513</v>
+        <v>0.367920309305191</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -601,7 +601,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849839687347</v>
+        <v>0.366849809885025</v>
       </c>
       <c r="H8" t="n">
         <v>58014</v>
@@ -630,7 +630,7 @@
         <v>0.406127005815506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.362301081418991</v>
+        <v>0.362301051616669</v>
       </c>
       <c r="H9" t="n">
         <v>183012</v>
@@ -688,7 +688,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.36354997754097</v>
+        <v>0.363550007343292</v>
       </c>
       <c r="H11" t="n">
         <v>679980</v>
@@ -717,7 +717,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198344707489</v>
+        <v>0.358198314905167</v>
       </c>
       <c r="H12" t="n">
         <v>66923</v>
@@ -775,7 +775,7 @@
         <v>0.360035002231598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.321182936429977</v>
+        <v>0.3211829662323</v>
       </c>
       <c r="H14" t="n">
         <v>427660</v>
@@ -862,7 +862,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012828111649</v>
+        <v>0.330012857913971</v>
       </c>
       <c r="H17" t="n">
         <v>26501</v>
@@ -920,7 +920,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450531482697</v>
+        <v>0.321450561285019</v>
       </c>
       <c r="H19" t="n">
         <v>460284</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1123,7 +1123,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696389198303</v>
+        <v>0.308696359395981</v>
       </c>
       <c r="H26" t="n">
         <v>149000</v>
@@ -1152,7 +1152,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998313903809</v>
+        <v>0.292998284101486</v>
       </c>
       <c r="H27" t="n">
         <v>582541</v>
@@ -1181,7 +1181,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205820083618</v>
+        <v>0.282205849885941</v>
       </c>
       <c r="H28" t="n">
         <v>388643</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28283029794693</v>
+        <v>0.282830268144608</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1268,7 +1268,7 @@
         <v>0.323742002248764</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2888063788414</v>
+        <v>0.288806408643723</v>
       </c>
       <c r="H31" t="n">
         <v>538832</v>
@@ -1297,7 +1297,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H32" t="n">
         <v>307119</v>
@@ -1326,7 +1326,7 @@
         <v>0.326041013002396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.290857285261154</v>
+        <v>0.290857315063477</v>
       </c>
       <c r="H33" t="n">
         <v>123285</v>
@@ -1413,7 +1413,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749358177185</v>
+        <v>0.291749387979507</v>
       </c>
       <c r="H36" t="n">
         <v>227448</v>
@@ -1442,7 +1442,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H37" t="n">
         <v>783105</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335544109344</v>
+        <v>0.294335573911667</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1558,7 +1558,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.290054440498352</v>
+        <v>0.29005441069603</v>
       </c>
       <c r="H41" t="n">
         <v>53072</v>
@@ -1616,7 +1616,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424772262573</v>
+        <v>0.294424742460251</v>
       </c>
       <c r="H43" t="n">
         <v>236808</v>
@@ -1645,7 +1645,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311625003815</v>
+        <v>0.300311654806137</v>
       </c>
       <c r="H44" t="n">
         <v>929955</v>
@@ -1703,7 +1703,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.301203727722168</v>
+        <v>0.30120375752449</v>
       </c>
       <c r="H46" t="n">
         <v>245666</v>
@@ -1732,7 +1732,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720278501511</v>
+        <v>0.302720248699188</v>
       </c>
       <c r="H47" t="n">
         <v>365880</v>
@@ -1761,7 +1761,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166329860687</v>
+        <v>0.303166300058365</v>
       </c>
       <c r="H48" t="n">
         <v>159693</v>
@@ -1790,7 +1790,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560550928116</v>
+        <v>0.301560580730438</v>
       </c>
       <c r="H49" t="n">
         <v>194576</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007607936859</v>
+        <v>0.335007637739182</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1964,7 +1964,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.33349198102951</v>
+        <v>0.333491951227188</v>
       </c>
       <c r="H55" t="n">
         <v>361299</v>
@@ -1993,7 +1993,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822822570801</v>
+        <v>0.358822792768478</v>
       </c>
       <c r="H56" t="n">
         <v>833937</v>
@@ -2022,7 +2022,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736692428589</v>
+        <v>0.372736722230911</v>
       </c>
       <c r="H57" t="n">
         <v>389611</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37014964222908</v>
+        <v>0.370149672031403</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2109,7 +2109,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.38290473818779</v>
+        <v>0.382904708385468</v>
       </c>
       <c r="H60" t="n">
         <v>377944</v>
@@ -2167,7 +2167,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350759744644</v>
+        <v>0.383350789546967</v>
       </c>
       <c r="H62" t="n">
         <v>181871</v>
@@ -2225,7 +2225,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806327581406</v>
+        <v>0.373806297779083</v>
       </c>
       <c r="H64" t="n">
         <v>172614</v>
@@ -2283,7 +2283,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203564882278</v>
+        <v>0.353203535079956</v>
       </c>
       <c r="H66" t="n">
         <v>34491</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3575738966465</v>
+        <v>0.357573866844177</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178751707077</v>
+        <v>0.359178721904755</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2457,7 +2457,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376741409302</v>
+        <v>0.358376801013947</v>
       </c>
       <c r="H72" t="n">
         <v>393696</v>
@@ -2486,7 +2486,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579087018967</v>
+        <v>0.352579116821289</v>
       </c>
       <c r="H73" t="n">
         <v>623896</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183942079544</v>
+        <v>0.354183971881866</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2544,7 +2544,7 @@
         <v>0.393929004669189</v>
       </c>
       <c r="G75" t="n">
-        <v>0.351419359445572</v>
+        <v>0.351419389247894</v>
       </c>
       <c r="H75" t="n">
         <v>330426</v>
@@ -2631,7 +2631,7 @@
         <v>0.401827991008759</v>
       </c>
       <c r="G78" t="n">
-        <v>0.358465999364853</v>
+        <v>0.358465969562531</v>
       </c>
       <c r="H78" t="n">
         <v>145425</v>
@@ -2689,7 +2689,7 @@
         <v>0.400528013706207</v>
       </c>
       <c r="G80" t="n">
-        <v>0.357306301593781</v>
+        <v>0.357306271791458</v>
       </c>
       <c r="H80" t="n">
         <v>465916</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157960414886</v>
+        <v>0.379157930612564</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2892,7 +2892,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332632541656</v>
+        <v>0.372332602739334</v>
       </c>
       <c r="H87" t="n">
         <v>290844</v>
@@ -3008,7 +3008,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.37150239944458</v>
+        <v>0.371502429246902</v>
       </c>
       <c r="H91" t="n">
         <v>148553</v>
@@ -3124,7 +3124,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.368920415639877</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H95" t="n">
         <v>267568</v>
@@ -3153,7 +3153,7 @@
         <v>0.399827986955643</v>
       </c>
       <c r="G96" t="n">
-        <v>0.368828177452087</v>
+        <v>0.368828147649765</v>
       </c>
       <c r="H96" t="n">
         <v>378647</v>
@@ -3182,7 +3182,7 @@
         <v>0.393429011106491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.362925291061401</v>
+        <v>0.362925320863724</v>
       </c>
       <c r="H97" t="n">
         <v>371654</v>
@@ -3385,7 +3385,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.350658357143402</v>
+        <v>0.35065832734108</v>
       </c>
       <c r="H104" t="n">
         <v>409447</v>
@@ -3443,7 +3443,7 @@
         <v>0.40022799372673</v>
       </c>
       <c r="G106" t="n">
-        <v>0.369197130203247</v>
+        <v>0.369197160005569</v>
       </c>
       <c r="H106" t="n">
         <v>3752445</v>
@@ -3588,7 +3588,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.364309012889862</v>
+        <v>0.36430898308754</v>
       </c>
       <c r="H111" t="n">
         <v>269379</v>
@@ -3704,7 +3704,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H115" t="n">
         <v>399670</v>
@@ -3791,7 +3791,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H118" t="n">
         <v>414717</v>
@@ -4052,7 +4052,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H127" t="n">
         <v>1255939</v>
@@ -4081,7 +4081,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455977201462</v>
+        <v>0.317455947399139</v>
       </c>
       <c r="H128" t="n">
         <v>1239642</v>
@@ -4110,7 +4110,7 @@
         <v>0.350237011909485</v>
       </c>
       <c r="G129" t="n">
-        <v>0.323082089424133</v>
+        <v>0.323082119226456</v>
       </c>
       <c r="H129" t="n">
         <v>128422</v>
@@ -4197,7 +4197,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H132" t="n">
         <v>275307</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169481992722</v>
+        <v>0.329169452190399</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4342,7 +4342,7 @@
         <v>0.374033004045486</v>
       </c>
       <c r="G137" t="n">
-        <v>0.34503310918808</v>
+        <v>0.345033138990402</v>
       </c>
       <c r="H137" t="n">
         <v>55292</v>
@@ -4487,7 +4487,7 @@
         <v>0.380430996417999</v>
       </c>
       <c r="G142" t="n">
-        <v>0.350935101509094</v>
+        <v>0.350935071706772</v>
       </c>
       <c r="H142" t="n">
         <v>244048</v>
@@ -4516,7 +4516,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886961936951</v>
+        <v>0.353886932134628</v>
       </c>
       <c r="H143" t="n">
         <v>50099</v>
@@ -4632,7 +4632,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163736104965</v>
+        <v>0.354163706302643</v>
       </c>
       <c r="H147" t="n">
         <v>1381221</v>
@@ -4661,7 +4661,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.34475639462471</v>
+        <v>0.344756424427032</v>
       </c>
       <c r="H148" t="n">
         <v>760552</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341620028018951</v>
+        <v>0.341619998216629</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4951,7 +4951,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212686538696</v>
+        <v>0.332212656736374</v>
       </c>
       <c r="H158" t="n">
         <v>1508122</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382423639297</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5067,7 +5067,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935942173004</v>
+        <v>0.331935912370682</v>
       </c>
       <c r="H162" t="n">
         <v>65792</v>
@@ -5270,7 +5270,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417648077011</v>
+        <v>0.308417677879333</v>
       </c>
       <c r="H169" t="n">
         <v>480344</v>
@@ -5299,7 +5299,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H170" t="n">
         <v>262272</v>
@@ -5328,7 +5328,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130199193954</v>
+        <v>0.320130228996277</v>
       </c>
       <c r="H171" t="n">
         <v>260836</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309829950333</v>
+        <v>0.326309859752655</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5415,7 +5415,7 @@
         <v>0.341937988996506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.315426528453827</v>
+        <v>0.315426558256149</v>
       </c>
       <c r="H174" t="n">
         <v>1029741</v>
@@ -5444,7 +5444,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620868682861</v>
+        <v>0.322620838880539</v>
       </c>
       <c r="H175" t="n">
         <v>311100</v>
@@ -5531,7 +5531,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620868682861</v>
+        <v>0.322620838880539</v>
       </c>
       <c r="H178" t="n">
         <v>68182</v>
@@ -5560,7 +5560,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G179" t="n">
-        <v>0.320960432291031</v>
+        <v>0.320960402488708</v>
       </c>
       <c r="H179" t="n">
         <v>231414</v>
@@ -5589,7 +5589,7 @@
         <v>0.342038005590439</v>
       </c>
       <c r="G180" t="n">
-        <v>0.315518826246262</v>
+        <v>0.315518796443939</v>
       </c>
       <c r="H180" t="n">
         <v>97882</v>
@@ -6053,7 +6053,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582569360733</v>
+        <v>0.313582539558411</v>
       </c>
       <c r="H196" t="n">
         <v>85046</v>
@@ -6198,7 +6198,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G201" t="n">
-        <v>0.320960432291031</v>
+        <v>0.320960402488708</v>
       </c>
       <c r="H201" t="n">
         <v>234454</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6314,7 +6314,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484525680542</v>
+        <v>0.338484555482864</v>
       </c>
       <c r="H205" t="n">
         <v>279724</v>
@@ -6401,7 +6401,7 @@
         <v>0.372732996940613</v>
       </c>
       <c r="G208" t="n">
-        <v>0.343833953142166</v>
+        <v>0.343833923339844</v>
       </c>
       <c r="H208" t="n">
         <v>21151</v>
@@ -6517,7 +6517,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G212" t="n">
-        <v>0.354440480470657</v>
+        <v>0.354440450668335</v>
       </c>
       <c r="H212" t="n">
         <v>184112</v>
@@ -6546,7 +6546,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G213" t="n">
-        <v>0.354440480470657</v>
+        <v>0.354440450668335</v>
       </c>
       <c r="H213" t="n">
         <v>256167</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333473205566</v>
+        <v>0.353333503007889</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6633,7 +6633,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998814821243</v>
+        <v>0.348998785018921</v>
       </c>
       <c r="H216" t="n">
         <v>202870</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028210163116</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6865,7 +6865,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H224" t="n">
         <v>323877</v>
@@ -6894,7 +6894,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897642850876</v>
+        <v>0.322897613048553</v>
       </c>
       <c r="H225" t="n">
         <v>81571</v>
@@ -6923,7 +6923,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G226" t="n">
-        <v>0.325387388467789</v>
+        <v>0.325387358665466</v>
       </c>
       <c r="H226" t="n">
         <v>90191</v>
@@ -6981,7 +6981,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571835041046</v>
+        <v>0.325571864843369</v>
       </c>
       <c r="H228" t="n">
         <v>10415</v>
@@ -7010,7 +7010,7 @@
         <v>0.352436006069183</v>
       </c>
       <c r="G229" t="n">
-        <v>0.325110644102097</v>
+        <v>0.325110614299774</v>
       </c>
       <c r="H229" t="n">
         <v>52752</v>
@@ -7068,7 +7068,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558079242706</v>
+        <v>0.324558049440384</v>
       </c>
       <c r="H231" t="n">
         <v>85940</v>
@@ -7155,7 +7155,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G234" t="n">
-        <v>0.325387388467789</v>
+        <v>0.325387358665466</v>
       </c>
       <c r="H234" t="n">
         <v>61950</v>
@@ -7503,7 +7503,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H246" t="n">
         <v>332438</v>
@@ -7590,7 +7590,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251015663147</v>
+        <v>0.341251045465469</v>
       </c>
       <c r="H249" t="n">
         <v>515825</v>
@@ -7677,7 +7677,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3504738509655</v>
+        <v>0.350473880767822</v>
       </c>
       <c r="H252" t="n">
         <v>190131</v>
@@ -7793,7 +7793,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105792284012</v>
+        <v>0.350105822086334</v>
       </c>
       <c r="H256" t="n">
         <v>175808</v>
@@ -7938,7 +7938,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.375653505325317</v>
+        <v>0.37565353512764</v>
       </c>
       <c r="H261" t="n">
         <v>685961</v>
@@ -7967,7 +7967,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429799556732</v>
+        <v>0.385429829359055</v>
       </c>
       <c r="H262" t="n">
         <v>463854</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609376907349</v>
+        <v>0.372609347105026</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8083,7 +8083,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.370949864387512</v>
+        <v>0.37094983458519</v>
       </c>
       <c r="H266" t="n">
         <v>191080</v>
@@ -8141,7 +8141,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G268" t="n">
-        <v>0.380449414253235</v>
+        <v>0.380449384450912</v>
       </c>
       <c r="H268" t="n">
         <v>145464</v>
@@ -8228,7 +8228,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G271" t="n">
-        <v>0.380449414253235</v>
+        <v>0.380449384450912</v>
       </c>
       <c r="H271" t="n">
         <v>143383</v>
@@ -8315,7 +8315,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370931863785</v>
+        <v>0.381370961666107</v>
       </c>
       <c r="H274" t="n">
         <v>262282</v>
@@ -8460,7 +8460,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.368920415639877</v>
+        <v>0.3689204454422</v>
       </c>
       <c r="H279" t="n">
         <v>96256</v>
@@ -8518,7 +8518,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H281" t="n">
         <v>107938</v>
@@ -8634,7 +8634,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162865638733</v>
+        <v>0.373162835836411</v>
       </c>
       <c r="H285" t="n">
         <v>681169</v>
@@ -8692,7 +8692,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G287" t="n">
-        <v>0.369935125112534</v>
+        <v>0.369935154914856</v>
       </c>
       <c r="H287" t="n">
         <v>280249</v>
@@ -8721,7 +8721,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G288" t="n">
-        <v>0.369935125112534</v>
+        <v>0.369935154914856</v>
       </c>
       <c r="H288" t="n">
         <v>218241</v>
@@ -8808,7 +8808,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744873046875</v>
+        <v>0.394744902849197</v>
       </c>
       <c r="H291" t="n">
         <v>911786</v>
@@ -8866,7 +8866,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714637041092</v>
+        <v>0.430714666843414</v>
       </c>
       <c r="H293" t="n">
         <v>1274513</v>
@@ -8895,7 +8895,7 @@
         <v>0.469814985990524</v>
       </c>
       <c r="G294" t="n">
-        <v>0.433388888835907</v>
+        <v>0.433388859033585</v>
       </c>
       <c r="H294" t="n">
         <v>517174</v>
@@ -8924,7 +8924,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927638292313</v>
+        <v>0.432927668094635</v>
       </c>
       <c r="H295" t="n">
         <v>547763</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340779066086</v>
+        <v>0.436340749263763</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9069,7 +9069,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403651714325</v>
+        <v>0.453403621912003</v>
       </c>
       <c r="H300" t="n">
         <v>1848152</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.488819897174835</v>
+        <v>0.488819926977158</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9214,7 +9214,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265567779541</v>
+        <v>0.507265508174896</v>
       </c>
       <c r="H305" t="n">
         <v>2178115</v>
@@ -9301,7 +9301,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.475446045398712</v>
+        <v>0.47544601559639</v>
       </c>
       <c r="H308" t="n">
         <v>1980457</v>
@@ -9330,7 +9330,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839428663254</v>
+        <v>0.464839458465576</v>
       </c>
       <c r="H309" t="n">
         <v>2438508</v>
@@ -9388,7 +9388,7 @@
         <v>0.558399975299835</v>
       </c>
       <c r="G311" t="n">
-        <v>0.515105605125427</v>
+        <v>0.515105545520782</v>
       </c>
       <c r="H311" t="n">
         <v>2223034</v>
@@ -9475,7 +9475,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511877000331879</v>
+        <v>0.511876940727234</v>
       </c>
       <c r="H314" t="n">
         <v>1905854</v>
@@ -9504,7 +9504,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099865436554</v>
+        <v>0.521099805831909</v>
       </c>
       <c r="H315" t="n">
         <v>1732441</v>
@@ -9562,7 +9562,7 @@
         <v>0.593892991542816</v>
       </c>
       <c r="G317" t="n">
-        <v>0.547846794128418</v>
+        <v>0.547846734523773</v>
       </c>
       <c r="H317" t="n">
         <v>846434</v>
@@ -9620,7 +9620,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841829299927</v>
+        <v>0.553841888904572</v>
       </c>
       <c r="H319" t="n">
         <v>1022491</v>
@@ -9649,7 +9649,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G320" t="n">
-        <v>0.557991981506348</v>
+        <v>0.557992041110992</v>
       </c>
       <c r="H320" t="n">
         <v>846974</v>
@@ -9678,7 +9678,7 @@
         <v>0.601891994476318</v>
       </c>
       <c r="G321" t="n">
-        <v>0.555225610733032</v>
+        <v>0.555225551128387</v>
       </c>
       <c r="H321" t="n">
         <v>722821</v>
@@ -9765,7 +9765,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345556735992</v>
+        <v>0.595345497131348</v>
       </c>
       <c r="H324" t="n">
         <v>1537366</v>
@@ -9794,7 +9794,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495708942413</v>
+        <v>0.599495649337769</v>
       </c>
       <c r="H325" t="n">
         <v>535825</v>
@@ -9910,7 +9910,7 @@
         <v>0.661381006240845</v>
       </c>
       <c r="G329" t="n">
-        <v>0.61010217666626</v>
+        <v>0.610102236270905</v>
       </c>
       <c r="H329" t="n">
         <v>1371286</v>
@@ -9997,7 +9997,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718514442444</v>
+        <v>0.608718454837799</v>
       </c>
       <c r="H332" t="n">
         <v>2497649</v>
@@ -10200,7 +10200,7 @@
         <v>0.696874976158142</v>
       </c>
       <c r="G339" t="n">
-        <v>0.642844259738922</v>
+        <v>0.642844200134277</v>
       </c>
       <c r="H339" t="n">
         <v>725692</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097331047058</v>
+        <v>0.616097271442413</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10374,7 +10374,7 @@
         <v>0.653383016586304</v>
       </c>
       <c r="G345" t="n">
-        <v>0.602724373340607</v>
+        <v>0.602724313735962</v>
       </c>
       <c r="H345" t="n">
         <v>1424542</v>
@@ -10548,7 +10548,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651660442352</v>
+        <v>0.597651720046997</v>
       </c>
       <c r="H351" t="n">
         <v>1472477</v>
@@ -10664,7 +10664,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617480993270874</v>
+        <v>0.617481052875519</v>
       </c>
       <c r="H355" t="n">
         <v>615646</v>
@@ -10722,7 +10722,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465443134308</v>
+        <v>0.635465383529663</v>
       </c>
       <c r="H357" t="n">
         <v>654445</v>
@@ -10751,7 +10751,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165138721466</v>
+        <v>0.627165079116821</v>
       </c>
       <c r="H358" t="n">
         <v>444207</v>
@@ -10838,7 +10838,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179794788361</v>
+        <v>0.609179735183716</v>
       </c>
       <c r="H361" t="n">
         <v>498433</v>
@@ -10925,7 +10925,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645861148834</v>
+        <v>0.603645801544189</v>
       </c>
       <c r="H364" t="n">
         <v>375033</v>
@@ -80096,6 +80096,35 @@
         <v>339222</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>173465</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.405427008867264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.361676573753357</v>
+        <v>0.361676603555679</v>
       </c>
       <c r="H2" t="n">
         <v>90003</v>
@@ -485,7 +485,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984754085541</v>
+        <v>0.373984724283218</v>
       </c>
       <c r="H4" t="n">
         <v>28227</v>
@@ -543,7 +543,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.368366360664368</v>
+        <v>0.36836639046669</v>
       </c>
       <c r="H6" t="n">
         <v>44447</v>
@@ -601,7 +601,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849809885025</v>
+        <v>0.366849839687347</v>
       </c>
       <c r="H8" t="n">
         <v>58014</v>
@@ -688,7 +688,7 @@
         <v>0.40752699971199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.363550007343292</v>
+        <v>0.36354997754097</v>
       </c>
       <c r="H11" t="n">
         <v>679980</v>
@@ -717,7 +717,7 @@
         <v>0.401528000831604</v>
       </c>
       <c r="G12" t="n">
-        <v>0.358198314905167</v>
+        <v>0.358198344707489</v>
       </c>
       <c r="H12" t="n">
         <v>66923</v>
@@ -775,7 +775,7 @@
         <v>0.360035002231598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3211829662323</v>
+        <v>0.321182936429977</v>
       </c>
       <c r="H14" t="n">
         <v>427660</v>
@@ -862,7 +862,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G17" t="n">
-        <v>0.330012857913971</v>
+        <v>0.330012828111649</v>
       </c>
       <c r="H17" t="n">
         <v>26501</v>
@@ -920,7 +920,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450561285019</v>
+        <v>0.321450531482697</v>
       </c>
       <c r="H19" t="n">
         <v>460284</v>
@@ -1065,7 +1065,7 @@
         <v>0.348637014627457</v>
       </c>
       <c r="G24" t="n">
-        <v>0.311014920473099</v>
+        <v>0.311014950275421</v>
       </c>
       <c r="H24" t="n">
         <v>194987</v>
@@ -1123,7 +1123,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696359395981</v>
+        <v>0.308696389198303</v>
       </c>
       <c r="H26" t="n">
         <v>149000</v>
@@ -1152,7 +1152,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998284101486</v>
+        <v>0.292998313903809</v>
       </c>
       <c r="H27" t="n">
         <v>582541</v>
@@ -1210,7 +1210,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979614973068</v>
+        <v>0.293979585170746</v>
       </c>
       <c r="H29" t="n">
         <v>282359</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830268144608</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1326,7 +1326,7 @@
         <v>0.326041013002396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.290857315063477</v>
+        <v>0.290857285261154</v>
       </c>
       <c r="H33" t="n">
         <v>123285</v>
@@ -1384,7 +1384,7 @@
         <v>0.331440001726151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.295673668384552</v>
+        <v>0.295673698186874</v>
       </c>
       <c r="H35" t="n">
         <v>189584</v>
@@ -1471,7 +1471,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114529371262</v>
+        <v>0.301114499568939</v>
       </c>
       <c r="H38" t="n">
         <v>6327</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335573911667</v>
+        <v>0.294335544109344</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1529,7 +1529,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289876013994217</v>
+        <v>0.289875984191895</v>
       </c>
       <c r="H40" t="n">
         <v>857362</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500462055206</v>
+        <v>0.290500491857529</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1645,7 +1645,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311654806137</v>
+        <v>0.300311625003815</v>
       </c>
       <c r="H44" t="n">
         <v>929955</v>
@@ -1674,7 +1674,7 @@
         <v>0.340938001871109</v>
       </c>
       <c r="G45" t="n">
-        <v>0.304146736860275</v>
+        <v>0.304146766662598</v>
       </c>
       <c r="H45" t="n">
         <v>663295</v>
@@ -1703,7 +1703,7 @@
         <v>0.337639003992081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.30120375752449</v>
+        <v>0.301203727722168</v>
       </c>
       <c r="H46" t="n">
         <v>245666</v>
@@ -1732,7 +1732,7 @@
         <v>0.33933898806572</v>
       </c>
       <c r="G47" t="n">
-        <v>0.302720248699188</v>
+        <v>0.302720278501511</v>
       </c>
       <c r="H47" t="n">
         <v>365880</v>
@@ -1761,7 +1761,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166300058365</v>
+        <v>0.303166329860687</v>
       </c>
       <c r="H48" t="n">
         <v>159693</v>
@@ -1935,7 +1935,7 @@
         <v>0.375532001256943</v>
       </c>
       <c r="G54" t="n">
-        <v>0.335007637739182</v>
+        <v>0.335007607936859</v>
       </c>
       <c r="H54" t="n">
         <v>323205</v>
@@ -1993,7 +1993,7 @@
         <v>0.402227997779846</v>
       </c>
       <c r="G56" t="n">
-        <v>0.358822792768478</v>
+        <v>0.358822822570801</v>
       </c>
       <c r="H56" t="n">
         <v>833937</v>
@@ -2022,7 +2022,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G57" t="n">
-        <v>0.372736722230911</v>
+        <v>0.372736692428589</v>
       </c>
       <c r="H57" t="n">
         <v>389611</v>
@@ -2167,7 +2167,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350789546967</v>
+        <v>0.383350759744644</v>
       </c>
       <c r="H62" t="n">
         <v>181871</v>
@@ -2283,7 +2283,7 @@
         <v>0.395929008722305</v>
       </c>
       <c r="G66" t="n">
-        <v>0.353203535079956</v>
+        <v>0.353203564882278</v>
       </c>
       <c r="H66" t="n">
         <v>34491</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573866844177</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2457,7 +2457,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376801013947</v>
+        <v>0.358376771211624</v>
       </c>
       <c r="H72" t="n">
         <v>393696</v>
@@ -2486,7 +2486,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579116821289</v>
+        <v>0.352579087018967</v>
       </c>
       <c r="H73" t="n">
         <v>623896</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183971881866</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2544,7 +2544,7 @@
         <v>0.393929004669189</v>
       </c>
       <c r="G75" t="n">
-        <v>0.351419389247894</v>
+        <v>0.351419359445572</v>
       </c>
       <c r="H75" t="n">
         <v>330426</v>
@@ -2718,7 +2718,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122625112534</v>
+        <v>0.362122654914856</v>
       </c>
       <c r="H81" t="n">
         <v>732739</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157960414886</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2834,7 +2834,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.396589815616608</v>
+        <v>0.39658984541893</v>
       </c>
       <c r="H85" t="n">
         <v>340192</v>
@@ -2892,7 +2892,7 @@
         <v>0.403627008199692</v>
       </c>
       <c r="G87" t="n">
-        <v>0.372332602739334</v>
+        <v>0.372332632541656</v>
       </c>
       <c r="H87" t="n">
         <v>290844</v>
@@ -2921,7 +2921,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701585292816</v>
+        <v>0.372701615095139</v>
       </c>
       <c r="H88" t="n">
         <v>354215</v>
@@ -2950,7 +2950,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027363300323</v>
+        <v>0.370027393102646</v>
       </c>
       <c r="H89" t="n">
         <v>311938</v>
@@ -3066,7 +3066,7 @@
         <v>0.404626995325089</v>
       </c>
       <c r="G93" t="n">
-        <v>0.373255103826523</v>
+        <v>0.3732550740242</v>
       </c>
       <c r="H93" t="n">
         <v>433441</v>
@@ -3124,7 +3124,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920385837555</v>
       </c>
       <c r="H95" t="n">
         <v>267568</v>
@@ -3269,7 +3269,7 @@
         <v>0.386929988861084</v>
       </c>
       <c r="G100" t="n">
-        <v>0.356930196285248</v>
+        <v>0.356930166482925</v>
       </c>
       <c r="H100" t="n">
         <v>922415</v>
@@ -3298,7 +3298,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304084062576</v>
+        <v>0.351304054260254</v>
       </c>
       <c r="H101" t="n">
         <v>1169299</v>
@@ -3385,7 +3385,7 @@
         <v>0.380131006240845</v>
       </c>
       <c r="G104" t="n">
-        <v>0.35065832734108</v>
+        <v>0.350658357143402</v>
       </c>
       <c r="H104" t="n">
         <v>409447</v>
@@ -3414,7 +3414,7 @@
         <v>0.390929996967316</v>
       </c>
       <c r="G105" t="n">
-        <v>0.360620051622391</v>
+        <v>0.360620081424713</v>
       </c>
       <c r="H105" t="n">
         <v>196102</v>
@@ -3472,7 +3472,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H107" t="n">
         <v>1327868</v>
@@ -3617,7 +3617,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313918113708</v>
+        <v>0.358313888311386</v>
       </c>
       <c r="H112" t="n">
         <v>133757</v>
@@ -3704,7 +3704,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G115" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H115" t="n">
         <v>399670</v>
@@ -3733,7 +3733,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H116" t="n">
         <v>471777</v>
@@ -3791,7 +3791,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G118" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H118" t="n">
         <v>414717</v>
@@ -3820,7 +3820,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.33783882856369</v>
+        <v>0.337838798761368</v>
       </c>
       <c r="H119" t="n">
         <v>2519386</v>
@@ -3936,7 +3936,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513103961945</v>
+        <v>0.359513133764267</v>
       </c>
       <c r="H123" t="n">
         <v>361479</v>
@@ -3994,7 +3994,7 @@
         <v>0.344238013029099</v>
       </c>
       <c r="G125" t="n">
-        <v>0.317548245191574</v>
+        <v>0.317548215389252</v>
       </c>
       <c r="H125" t="n">
         <v>491917</v>
@@ -4052,7 +4052,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G127" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H127" t="n">
         <v>1255939</v>
@@ -4081,7 +4081,7 @@
         <v>0.344137996435165</v>
       </c>
       <c r="G128" t="n">
-        <v>0.317455947399139</v>
+        <v>0.317455977201462</v>
       </c>
       <c r="H128" t="n">
         <v>1239642</v>
@@ -4139,7 +4139,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H130" t="n">
         <v>408863</v>
@@ -4168,7 +4168,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H131" t="n">
         <v>488386</v>
@@ -4197,7 +4197,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G132" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H132" t="n">
         <v>275307</v>
@@ -4226,7 +4226,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567800283432</v>
+        <v>0.312567830085754</v>
       </c>
       <c r="H133" t="n">
         <v>58287</v>
@@ -4255,7 +4255,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H134" t="n">
         <v>235517</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169452190399</v>
+        <v>0.329169422388077</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4429,7 +4429,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420835971832</v>
+        <v>0.359420865774155</v>
       </c>
       <c r="H140" t="n">
         <v>458480</v>
@@ -4516,7 +4516,7 @@
         <v>0.383630990982056</v>
       </c>
       <c r="G143" t="n">
-        <v>0.353886932134628</v>
+        <v>0.353886961936951</v>
       </c>
       <c r="H143" t="n">
         <v>50099</v>
@@ -4632,7 +4632,7 @@
         <v>0.383931010961533</v>
       </c>
       <c r="G147" t="n">
-        <v>0.354163706302643</v>
+        <v>0.354163736104965</v>
       </c>
       <c r="H147" t="n">
         <v>1381221</v>
@@ -4661,7 +4661,7 @@
         <v>0.373733013868332</v>
       </c>
       <c r="G148" t="n">
-        <v>0.344756424427032</v>
+        <v>0.34475639462471</v>
       </c>
       <c r="H148" t="n">
         <v>760552</v>
@@ -4690,7 +4690,7 @@
         <v>0.381830990314484</v>
       </c>
       <c r="G149" t="n">
-        <v>0.35222652554512</v>
+        <v>0.352226495742798</v>
       </c>
       <c r="H149" t="n">
         <v>304342</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619998216629</v>
+        <v>0.341619968414307</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4777,7 +4777,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712296009064</v>
       </c>
       <c r="H152" t="n">
         <v>138916</v>
@@ -4951,7 +4951,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G158" t="n">
-        <v>0.332212656736374</v>
+        <v>0.332212686538696</v>
       </c>
       <c r="H158" t="n">
         <v>1508122</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5009,7 +5009,7 @@
         <v>0.356635987758636</v>
       </c>
       <c r="G160" t="n">
-        <v>0.328984975814819</v>
+        <v>0.328984946012497</v>
       </c>
       <c r="H160" t="n">
         <v>256812</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382483243942</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5067,7 +5067,7 @@
         <v>0.359834998846054</v>
       </c>
       <c r="G162" t="n">
-        <v>0.331935912370682</v>
+        <v>0.331935942173004</v>
       </c>
       <c r="H162" t="n">
         <v>65792</v>
@@ -5154,7 +5154,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.32372784614563</v>
+        <v>0.323727816343307</v>
       </c>
       <c r="H165" t="n">
         <v>1547058</v>
@@ -5270,7 +5270,7 @@
         <v>0.334340006113052</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308417677879333</v>
+        <v>0.308417648077011</v>
       </c>
       <c r="H169" t="n">
         <v>480344</v>
@@ -5299,7 +5299,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G170" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H170" t="n">
         <v>262272</v>
@@ -5328,7 +5328,7 @@
         <v>0.347036987543106</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320130228996277</v>
+        <v>0.320130199193954</v>
       </c>
       <c r="H171" t="n">
         <v>260836</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309859752655</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5473,7 +5473,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H176" t="n">
         <v>198283</v>
@@ -5502,7 +5502,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.31847071647644</v>
+        <v>0.318470686674118</v>
       </c>
       <c r="H177" t="n">
         <v>167208</v>
@@ -5734,7 +5734,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305824995041</v>
+        <v>0.313305795192719</v>
       </c>
       <c r="H185" t="n">
         <v>269383</v>
@@ -5792,7 +5792,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H187" t="n">
         <v>969165</v>
@@ -5850,7 +5850,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892654418945</v>
+        <v>0.309892684221268</v>
       </c>
       <c r="H189" t="n">
         <v>96038</v>
@@ -5966,7 +5966,7 @@
         <v>0.33643901348114</v>
       </c>
       <c r="G193" t="n">
-        <v>0.31035390496254</v>
+        <v>0.310353934764862</v>
       </c>
       <c r="H193" t="n">
         <v>276707</v>
@@ -6053,7 +6053,7 @@
         <v>0.339938998222351</v>
       </c>
       <c r="G196" t="n">
-        <v>0.313582539558411</v>
+        <v>0.313582569360733</v>
       </c>
       <c r="H196" t="n">
         <v>85046</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071468114853</v>
+        <v>0.354071497917175</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6575,7 +6575,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837928295135</v>
+        <v>0.356837958097458</v>
       </c>
       <c r="H214" t="n">
         <v>141958</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333532810211</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6633,7 +6633,7 @@
         <v>0.378331989049911</v>
       </c>
       <c r="G216" t="n">
-        <v>0.348998785018921</v>
+        <v>0.348998814821243</v>
       </c>
       <c r="H216" t="n">
         <v>202870</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028210163116</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6749,7 +6749,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751465797424</v>
+        <v>0.331751435995102</v>
       </c>
       <c r="H220" t="n">
         <v>241870</v>
@@ -6778,7 +6778,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.32612532377243</v>
+        <v>0.326125353574753</v>
       </c>
       <c r="H221" t="n">
         <v>240850</v>
@@ -6807,7 +6807,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H222" t="n">
         <v>259436</v>
@@ -6836,7 +6836,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004560709</v>
+        <v>0.324004590511322</v>
       </c>
       <c r="H223" t="n">
         <v>106739</v>
@@ -6865,7 +6865,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G224" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H224" t="n">
         <v>323877</v>
@@ -6952,7 +6952,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328247010707855</v>
+        <v>0.328246980905533</v>
       </c>
       <c r="H227" t="n">
         <v>176045</v>
@@ -6981,7 +6981,7 @@
         <v>0.352935999631882</v>
       </c>
       <c r="G228" t="n">
-        <v>0.325571864843369</v>
+        <v>0.325571835041046</v>
       </c>
       <c r="H228" t="n">
         <v>10415</v>
@@ -7271,7 +7271,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805374860764</v>
+        <v>0.322805345058441</v>
       </c>
       <c r="H238" t="n">
         <v>60220</v>
@@ -7387,7 +7387,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397192716599</v>
+        <v>0.332397162914276</v>
       </c>
       <c r="H242" t="n">
         <v>278620</v>
@@ -7474,7 +7474,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712266206741</v>
+        <v>0.341712296009064</v>
       </c>
       <c r="H245" t="n">
         <v>783334</v>
@@ -7503,7 +7503,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G246" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H246" t="n">
         <v>332438</v>
@@ -7561,7 +7561,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018429517746</v>
+        <v>0.344018399715424</v>
       </c>
       <c r="H248" t="n">
         <v>335681</v>
@@ -7590,7 +7590,7 @@
         <v>0.369933009147644</v>
       </c>
       <c r="G249" t="n">
-        <v>0.341251045465469</v>
+        <v>0.341251015663147</v>
       </c>
       <c r="H249" t="n">
         <v>515825</v>
@@ -7619,7 +7619,7 @@
         <v>0.377131998538971</v>
       </c>
       <c r="G250" t="n">
-        <v>0.347891867160797</v>
+        <v>0.34789189696312</v>
       </c>
       <c r="H250" t="n">
         <v>624870</v>
@@ -7648,7 +7648,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241235017776</v>
+        <v>0.353241264820099</v>
       </c>
       <c r="H251" t="n">
         <v>591930</v>
@@ -7677,7 +7677,7 @@
         <v>0.379931002855301</v>
       </c>
       <c r="G252" t="n">
-        <v>0.350473880767822</v>
+        <v>0.3504738509655</v>
       </c>
       <c r="H252" t="n">
         <v>190131</v>
@@ -7793,7 +7793,7 @@
         <v>0.379532009363174</v>
       </c>
       <c r="G256" t="n">
-        <v>0.350105822086334</v>
+        <v>0.350105792284012</v>
       </c>
       <c r="H256" t="n">
         <v>175808</v>
@@ -7822,7 +7822,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396292448044</v>
+        <v>0.351396322250366</v>
       </c>
       <c r="H257" t="n">
         <v>191994</v>
@@ -7967,7 +7967,7 @@
         <v>0.417825013399124</v>
       </c>
       <c r="G262" t="n">
-        <v>0.385429829359055</v>
+        <v>0.385429799556732</v>
       </c>
       <c r="H262" t="n">
         <v>463854</v>
@@ -8025,7 +8025,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633890628815</v>
+        <v>0.380633920431137</v>
       </c>
       <c r="H264" t="n">
         <v>828739</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8083,7 +8083,7 @@
         <v>0.402128010988235</v>
       </c>
       <c r="G266" t="n">
-        <v>0.37094983458519</v>
+        <v>0.370949864387512</v>
       </c>
       <c r="H266" t="n">
         <v>191080</v>
@@ -8112,7 +8112,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G267" t="n">
-        <v>0.380910634994507</v>
+        <v>0.380910664796829</v>
       </c>
       <c r="H267" t="n">
         <v>111749</v>
@@ -8199,7 +8199,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342436790466</v>
+        <v>0.379342466592789</v>
       </c>
       <c r="H270" t="n">
         <v>170128</v>
@@ -8257,7 +8257,7 @@
         <v>0.412326008081436</v>
       </c>
       <c r="G272" t="n">
-        <v>0.380357176065445</v>
+        <v>0.380357146263123</v>
       </c>
       <c r="H272" t="n">
         <v>439414</v>
@@ -8315,7 +8315,7 @@
         <v>0.413424998521805</v>
       </c>
       <c r="G274" t="n">
-        <v>0.381370961666107</v>
+        <v>0.381370931863785</v>
       </c>
       <c r="H274" t="n">
         <v>262282</v>
@@ -8431,7 +8431,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H278" t="n">
         <v>227740</v>
@@ -8460,7 +8460,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3689204454422</v>
+        <v>0.368920385837555</v>
       </c>
       <c r="H279" t="n">
         <v>96256</v>
@@ -8489,7 +8489,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517138719559</v>
+        <v>0.372517108917236</v>
       </c>
       <c r="H280" t="n">
         <v>66227</v>
@@ -8518,7 +8518,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G281" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H281" t="n">
         <v>107938</v>
@@ -8576,7 +8576,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085336923599</v>
+        <v>0.374085307121277</v>
       </c>
       <c r="H283" t="n">
         <v>186709</v>
@@ -8634,7 +8634,7 @@
         <v>0.404527008533478</v>
       </c>
       <c r="G285" t="n">
-        <v>0.373162835836411</v>
+        <v>0.373162865638733</v>
       </c>
       <c r="H285" t="n">
         <v>681169</v>
@@ -8750,7 +8750,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531818389893</v>
+        <v>0.373531848192215</v>
       </c>
       <c r="H289" t="n">
         <v>229876</v>
@@ -8866,7 +8866,7 @@
         <v>0.466915994882584</v>
       </c>
       <c r="G293" t="n">
-        <v>0.430714666843414</v>
+        <v>0.430714637041092</v>
       </c>
       <c r="H293" t="n">
         <v>1274513</v>
@@ -8924,7 +8924,7 @@
         <v>0.469314992427826</v>
       </c>
       <c r="G295" t="n">
-        <v>0.432927668094635</v>
+        <v>0.432927638292313</v>
       </c>
       <c r="H295" t="n">
         <v>547763</v>
@@ -8953,7 +8953,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757841587067</v>
+        <v>0.433757871389389</v>
       </c>
       <c r="H296" t="n">
         <v>764989</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340749263763</v>
+        <v>0.436340808868408</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9040,7 +9040,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321194171906</v>
+        <v>0.441321164369583</v>
       </c>
       <c r="H299" t="n">
         <v>731265</v>
@@ -9069,7 +9069,7 @@
         <v>0.49151200056076</v>
       </c>
       <c r="G300" t="n">
-        <v>0.453403621912003</v>
+        <v>0.453403651714325</v>
       </c>
       <c r="H300" t="n">
         <v>1848152</v>
@@ -9098,7 +9098,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145651578903</v>
+        <v>0.467145621776581</v>
       </c>
       <c r="H301" t="n">
         <v>1481695</v>
@@ -9156,7 +9156,7 @@
         <v>0.524406015872955</v>
       </c>
       <c r="G303" t="n">
-        <v>0.48374730348587</v>
+        <v>0.483747273683548</v>
       </c>
       <c r="H303" t="n">
         <v>1152418</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.488819926977158</v>
+        <v>0.48881995677948</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9214,7 +9214,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G305" t="n">
-        <v>0.507265508174896</v>
+        <v>0.507265567779541</v>
       </c>
       <c r="H305" t="n">
         <v>2178115</v>
@@ -9301,7 +9301,7 @@
         <v>0.515407025814056</v>
       </c>
       <c r="G308" t="n">
-        <v>0.47544601559639</v>
+        <v>0.475446045398712</v>
       </c>
       <c r="H308" t="n">
         <v>1980457</v>
@@ -9359,7 +9359,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286052942276</v>
+        <v>0.483286082744598</v>
       </c>
       <c r="H310" t="n">
         <v>1188532</v>
@@ -9475,7 +9475,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G314" t="n">
-        <v>0.511876940727234</v>
+        <v>0.511877000331879</v>
       </c>
       <c r="H314" t="n">
         <v>1905854</v>
@@ -9591,7 +9591,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774081230164</v>
+        <v>0.542774140834808</v>
       </c>
       <c r="H318" t="n">
         <v>750114</v>
@@ -9620,7 +9620,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G319" t="n">
-        <v>0.553841888904572</v>
+        <v>0.553841829299927</v>
       </c>
       <c r="H319" t="n">
         <v>1022491</v>
@@ -9794,7 +9794,7 @@
         <v>0.649882972240448</v>
       </c>
       <c r="G325" t="n">
-        <v>0.599495649337769</v>
+        <v>0.599495708942413</v>
       </c>
       <c r="H325" t="n">
         <v>535825</v>
@@ -9823,7 +9823,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267998218536</v>
+        <v>0.596267938613892</v>
       </c>
       <c r="H326" t="n">
         <v>478574</v>
@@ -9881,7 +9881,7 @@
         <v>0.65488201379776</v>
       </c>
       <c r="G328" t="n">
-        <v>0.604107081890106</v>
+        <v>0.604107141494751</v>
       </c>
       <c r="H328" t="n">
         <v>930926</v>
@@ -9997,7 +9997,7 @@
         <v>0.659880995750427</v>
       </c>
       <c r="G332" t="n">
-        <v>0.608718454837799</v>
+        <v>0.608718514442444</v>
       </c>
       <c r="H332" t="n">
         <v>2497649</v>
@@ -10084,7 +10084,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634542942047119</v>
+        <v>0.634543001651764</v>
       </c>
       <c r="H335" t="n">
         <v>2493902</v>
@@ -10229,7 +10229,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.640076875686646</v>
+        <v>0.64007693529129</v>
       </c>
       <c r="H340" t="n">
         <v>1222262</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10403,7 +10403,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.62808758020401</v>
+        <v>0.628087520599365</v>
       </c>
       <c r="H346" t="n">
         <v>1835882</v>
@@ -10461,7 +10461,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942214012146</v>
+        <v>0.617942273616791</v>
       </c>
       <c r="H348" t="n">
         <v>976577</v>
@@ -10548,7 +10548,7 @@
         <v>0.647884011268616</v>
       </c>
       <c r="G351" t="n">
-        <v>0.597651720046997</v>
+        <v>0.597651660442352</v>
       </c>
       <c r="H351" t="n">
         <v>1472477</v>
@@ -10635,7 +10635,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607797026634216</v>
+        <v>0.607796967029572</v>
       </c>
       <c r="H354" t="n">
         <v>1281515</v>
@@ -10664,7 +10664,7 @@
         <v>0.669380009174347</v>
       </c>
       <c r="G355" t="n">
-        <v>0.617481052875519</v>
+        <v>0.617480993270874</v>
       </c>
       <c r="H355" t="n">
         <v>615646</v>
@@ -10751,7 +10751,7 @@
         <v>0.679877996444702</v>
       </c>
       <c r="G358" t="n">
-        <v>0.627165079116821</v>
+        <v>0.627165138721466</v>
       </c>
       <c r="H358" t="n">
         <v>444207</v>
@@ -10954,7 +10954,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829379081726</v>
+        <v>0.608829319477081</v>
       </c>
       <c r="H365" t="n">
         <v>210377</v>
@@ -10983,7 +10983,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.61307030916214</v>
+        <v>0.613070249557495</v>
       </c>
       <c r="H366" t="n">
         <v>341904</v>
@@ -11273,7 +11273,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969201564789</v>
+        <v>0.581969141960144</v>
       </c>
       <c r="H376" t="n">
         <v>259131</v>
@@ -11389,7 +11389,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.57395875453949</v>
+        <v>0.573958694934845</v>
       </c>
       <c r="H380" t="n">
         <v>251076</v>
@@ -11418,7 +11418,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152719497681</v>
+        <v>0.587152659893036</v>
       </c>
       <c r="H381" t="n">
         <v>198695</v>
@@ -11447,7 +11447,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555260181427</v>
+        <v>0.580555200576782</v>
       </c>
       <c r="H382" t="n">
         <v>558855</v>
@@ -11505,7 +11505,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H384" t="n">
         <v>1352746</v>
@@ -11563,7 +11563,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H386" t="n">
         <v>141943</v>
@@ -11592,7 +11592,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H387" t="n">
         <v>349861</v>
@@ -11708,7 +11708,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H391" t="n">
         <v>289335</v>
@@ -11737,7 +11737,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741868972778</v>
+        <v>0.544741928577423</v>
       </c>
       <c r="H392" t="n">
         <v>329337</v>
@@ -11766,7 +11766,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396740436554</v>
+        <v>0.550396800041199</v>
       </c>
       <c r="H393" t="n">
         <v>280658</v>
@@ -11795,7 +11795,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H394" t="n">
         <v>290140</v>
@@ -11882,7 +11882,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432245254517</v>
+        <v>0.533432185649872</v>
       </c>
       <c r="H397" t="n">
         <v>459584</v>
@@ -11911,7 +11911,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H398" t="n">
         <v>210300</v>
@@ -12027,7 +12027,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H402" t="n">
         <v>228411</v>
@@ -12172,7 +12172,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569811344147</v>
+        <v>0.547569751739502</v>
       </c>
       <c r="H407" t="n">
         <v>288350</v>
@@ -12201,7 +12201,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H408" t="n">
         <v>253441</v>
@@ -12230,7 +12230,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H409" t="n">
         <v>269272</v>
@@ -12259,7 +12259,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H410" t="n">
         <v>183867</v>
@@ -12288,7 +12288,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040091991425</v>
+        <v>0.548040151596069</v>
       </c>
       <c r="H411" t="n">
         <v>89021</v>
@@ -12346,7 +12346,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580198764801</v>
+        <v>0.555580258369446</v>
       </c>
       <c r="H413" t="n">
         <v>291996</v>
@@ -12433,7 +12433,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731421947479</v>
+        <v>0.536731362342834</v>
       </c>
       <c r="H416" t="n">
         <v>473625</v>
@@ -12520,7 +12520,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H419" t="n">
         <v>180174</v>
@@ -12549,7 +12549,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454092979431</v>
+        <v>0.549454033374786</v>
       </c>
       <c r="H420" t="n">
         <v>451568</v>
@@ -12607,7 +12607,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.542386293411255</v>
+        <v>0.54238623380661</v>
       </c>
       <c r="H422" t="n">
         <v>215255</v>
@@ -12665,7 +12665,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615763187408</v>
+        <v>0.538615703582764</v>
       </c>
       <c r="H424" t="n">
         <v>209758</v>
@@ -12723,7 +12723,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H426" t="n">
         <v>156206</v>
@@ -12752,7 +12752,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.52447909116745</v>
+        <v>0.524479150772095</v>
       </c>
       <c r="H427" t="n">
         <v>232817</v>
@@ -12839,7 +12839,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H430" t="n">
         <v>130630</v>
@@ -12897,7 +12897,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180927753448</v>
+        <v>0.521180868148804</v>
       </c>
       <c r="H432" t="n">
         <v>387167</v>
@@ -12984,7 +12984,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720021247864</v>
+        <v>0.528720080852509</v>
       </c>
       <c r="H435" t="n">
         <v>816289</v>
@@ -13100,7 +13100,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349894523621</v>
+        <v>0.559349834918976</v>
       </c>
       <c r="H439" t="n">
         <v>699890</v>
@@ -13129,7 +13129,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H440" t="n">
         <v>444610</v>
@@ -13158,7 +13158,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H441" t="n">
         <v>292621</v>
@@ -13245,7 +13245,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645861148834</v>
+        <v>0.603645801544189</v>
       </c>
       <c r="H444" t="n">
         <v>1107250</v>
@@ -13274,7 +13274,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807531356812</v>
+        <v>0.592807471752167</v>
       </c>
       <c r="H445" t="n">
         <v>663729</v>
@@ -13332,7 +13332,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577048301697</v>
+        <v>0.596577107906342</v>
       </c>
       <c r="H447" t="n">
         <v>238428</v>
@@ -13361,7 +13361,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.595163106918335</v>
+        <v>0.59516316652298</v>
       </c>
       <c r="H448" t="n">
         <v>218066</v>
@@ -13390,7 +13390,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772026538849</v>
+        <v>0.609772086143494</v>
       </c>
       <c r="H449" t="n">
         <v>909618</v>
@@ -13448,7 +13448,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876224994659</v>
+        <v>0.599876284599304</v>
       </c>
       <c r="H451" t="n">
         <v>477138</v>
@@ -13738,7 +13738,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H461" t="n">
         <v>114187</v>
@@ -13767,7 +13767,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947294235229</v>
+        <v>0.565947234630585</v>
       </c>
       <c r="H462" t="n">
         <v>238863</v>
@@ -13883,7 +13883,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533352851868</v>
+        <v>0.564533293247223</v>
       </c>
       <c r="H466" t="n">
         <v>222204</v>
@@ -13970,7 +13970,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670859336853</v>
+        <v>0.578670918941498</v>
       </c>
       <c r="H469" t="n">
         <v>139232</v>
@@ -14115,7 +14115,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292482376099</v>
+        <v>0.560292422771454</v>
       </c>
       <c r="H474" t="n">
         <v>149208</v>
@@ -14144,7 +14144,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108964443207</v>
+        <v>0.555108904838562</v>
       </c>
       <c r="H475" t="n">
         <v>148025</v>
@@ -14202,7 +14202,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.53767317533493</v>
+        <v>0.537673115730286</v>
       </c>
       <c r="H477" t="n">
         <v>352368</v>
@@ -14405,7 +14405,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100714206696</v>
+        <v>0.506100654602051</v>
       </c>
       <c r="H484" t="n">
         <v>271973</v>
@@ -14695,7 +14695,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H494" t="n">
         <v>58278</v>
@@ -14724,7 +14724,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H495" t="n">
         <v>163569</v>
@@ -14840,7 +14840,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H499" t="n">
         <v>78535</v>
@@ -14869,7 +14869,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972352027893</v>
+        <v>0.540972292423248</v>
       </c>
       <c r="H500" t="n">
         <v>70687</v>
@@ -14927,7 +14927,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997350215912</v>
+        <v>0.515997409820557</v>
       </c>
       <c r="H502" t="n">
         <v>149092</v>
@@ -14956,7 +14956,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194525241852</v>
+        <v>0.488194495439529</v>
       </c>
       <c r="H503" t="n">
         <v>1026439</v>
@@ -14985,7 +14985,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H504" t="n">
         <v>196576</v>
@@ -15101,7 +15101,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.51222687959671</v>
+        <v>0.512226819992065</v>
       </c>
       <c r="H508" t="n">
         <v>41572</v>
@@ -15188,7 +15188,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H511" t="n">
         <v>235907</v>
@@ -15217,7 +15217,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.533903539180756</v>
+        <v>0.5339035987854</v>
       </c>
       <c r="H512" t="n">
         <v>80711</v>
@@ -15246,7 +15246,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H513" t="n">
         <v>68229</v>
@@ -15275,7 +15275,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H514" t="n">
         <v>429758</v>
@@ -15362,7 +15362,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H517" t="n">
         <v>143705</v>
@@ -15507,7 +15507,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H522" t="n">
         <v>79164</v>
@@ -15536,7 +15536,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627163887024</v>
+        <v>0.546627104282379</v>
       </c>
       <c r="H523" t="n">
         <v>97732</v>
@@ -15594,7 +15594,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.543799221515656</v>
+        <v>0.5437992811203</v>
       </c>
       <c r="H525" t="n">
         <v>53867</v>
@@ -15710,7 +15710,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994140148163</v>
+        <v>0.556994199752808</v>
       </c>
       <c r="H529" t="n">
         <v>118746</v>
@@ -15797,7 +15797,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684456825256</v>
+        <v>0.545684516429901</v>
       </c>
       <c r="H532" t="n">
         <v>205602</v>
@@ -15855,7 +15855,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539087057113647</v>
+        <v>0.539086997509003</v>
       </c>
       <c r="H534" t="n">
         <v>98856</v>
@@ -15913,7 +15913,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.518352925777435</v>
+        <v>0.51835298538208</v>
       </c>
       <c r="H536" t="n">
         <v>79457</v>
@@ -15942,7 +15942,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.493849337100983</v>
+        <v>0.49384930729866</v>
       </c>
       <c r="H537" t="n">
         <v>518619</v>
@@ -16000,7 +16000,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H539" t="n">
         <v>178433</v>
@@ -16029,7 +16029,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539623975754</v>
+        <v>0.482539653778076</v>
       </c>
       <c r="H540" t="n">
         <v>175327</v>
@@ -16116,7 +16116,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770077228546</v>
+        <v>0.478770047426224</v>
       </c>
       <c r="H543" t="n">
         <v>269915</v>
@@ -16145,7 +16145,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H544" t="n">
         <v>168852</v>
@@ -16174,7 +16174,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.492906719446182</v>
+        <v>0.49290668964386</v>
       </c>
       <c r="H545" t="n">
         <v>96811</v>
@@ -16261,7 +16261,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078747272491</v>
+        <v>0.490078777074814</v>
       </c>
       <c r="H548" t="n">
         <v>145160</v>
@@ -16290,7 +16290,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H549" t="n">
         <v>92949</v>
@@ -16319,7 +16319,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H550" t="n">
         <v>133866</v>
@@ -16377,7 +16377,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.48913711309433</v>
+        <v>0.489137142896652</v>
       </c>
       <c r="H552" t="n">
         <v>240396</v>
@@ -16580,7 +16580,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777373790741</v>
+        <v>0.527777314186096</v>
       </c>
       <c r="H559" t="n">
         <v>314325</v>
@@ -16725,7 +16725,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065149784088</v>
+        <v>0.523065209388733</v>
       </c>
       <c r="H564" t="n">
         <v>355078</v>
@@ -16783,7 +16783,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021424531937</v>
+        <v>0.491021364927292</v>
       </c>
       <c r="H566" t="n">
         <v>370087</v>
@@ -16812,7 +16812,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251847982407</v>
+        <v>0.487251818180084</v>
       </c>
       <c r="H567" t="n">
         <v>425158</v>
@@ -16870,7 +16870,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931717634201</v>
+        <v>0.467931687831879</v>
       </c>
       <c r="H569" t="n">
         <v>298487</v>
@@ -17218,7 +17218,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909840106964</v>
+        <v>0.451909810304642</v>
       </c>
       <c r="H581" t="n">
         <v>283637</v>
@@ -17421,7 +17421,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469816029071808</v>
+        <v>0.469815999269485</v>
       </c>
       <c r="H588" t="n">
         <v>121246</v>
@@ -17537,7 +17537,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H592" t="n">
         <v>106747</v>
@@ -17624,7 +17624,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H595" t="n">
         <v>147417</v>
@@ -17682,7 +17682,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H597" t="n">
         <v>59239</v>
@@ -17711,7 +17711,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H598" t="n">
         <v>241824</v>
@@ -17827,7 +17827,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H602" t="n">
         <v>287903</v>
@@ -17885,7 +17885,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H604" t="n">
         <v>1272412</v>
@@ -17914,7 +17914,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H605" t="n">
         <v>1104869</v>
@@ -18001,7 +18001,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H608" t="n">
         <v>43571</v>
@@ -18030,7 +18030,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H609" t="n">
         <v>69465</v>
@@ -18088,7 +18088,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977699279785</v>
+        <v>0.458977669477463</v>
       </c>
       <c r="H611" t="n">
         <v>57385</v>
@@ -18117,7 +18117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H612" t="n">
         <v>209658</v>
@@ -18146,7 +18146,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H613" t="n">
         <v>10902</v>
@@ -18204,7 +18204,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458035975694656</v>
+        <v>0.458036005496979</v>
       </c>
       <c r="H615" t="n">
         <v>157901</v>
@@ -18233,7 +18233,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H616" t="n">
         <v>192728</v>
@@ -18291,7 +18291,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517746448517</v>
+        <v>0.466517776250839</v>
       </c>
       <c r="H618" t="n">
         <v>74901</v>
@@ -18407,7 +18407,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506375551224</v>
+        <v>0.458506345748901</v>
       </c>
       <c r="H622" t="n">
         <v>442685</v>
@@ -80125,6 +80125,35 @@
         <v>173465</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.737999975681305</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.737999975681305</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>129826</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.376928627490997</v>
+        <v>0.37692865729332</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920309305191</v>
+        <v>0.367920339107513</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -543,7 +543,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.36836639046669</v>
+        <v>0.368366360664368</v>
       </c>
       <c r="H6" t="n">
         <v>44447</v>
@@ -804,7 +804,7 @@
         <v>0.354936003684998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316634178161621</v>
+        <v>0.316634207963943</v>
       </c>
       <c r="H15" t="n">
         <v>315990</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272164583206</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -1007,7 +1007,7 @@
         <v>0.370133012533188</v>
       </c>
       <c r="G22" t="n">
-        <v>0.330191254615784</v>
+        <v>0.330191284418106</v>
       </c>
       <c r="H22" t="n">
         <v>1594825</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671605825424</v>
+        <v>0.314671576023102</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1065,7 +1065,7 @@
         <v>0.348637014627457</v>
       </c>
       <c r="G24" t="n">
-        <v>0.311014950275421</v>
+        <v>0.311014920473099</v>
       </c>
       <c r="H24" t="n">
         <v>194987</v>
@@ -1181,7 +1181,7 @@
         <v>0.316343009471893</v>
       </c>
       <c r="G28" t="n">
-        <v>0.282205849885941</v>
+        <v>0.282205820083618</v>
       </c>
       <c r="H28" t="n">
         <v>388643</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28283029794693</v>
+        <v>0.282830327749252</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1297,7 +1297,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G32" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H32" t="n">
         <v>307119</v>
@@ -1413,7 +1413,7 @@
         <v>0.327041000127792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.291749387979507</v>
+        <v>0.291749358177185</v>
       </c>
       <c r="H36" t="n">
         <v>227448</v>
@@ -1442,7 +1442,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H37" t="n">
         <v>783105</v>
@@ -1471,7 +1471,7 @@
         <v>0.337538987398148</v>
       </c>
       <c r="G38" t="n">
-        <v>0.301114499568939</v>
+        <v>0.301114529371262</v>
       </c>
       <c r="H38" t="n">
         <v>6327</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335544109344</v>
+        <v>0.294335514307022</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1529,7 +1529,7 @@
         <v>0.324941009283066</v>
       </c>
       <c r="G40" t="n">
-        <v>0.289875984191895</v>
+        <v>0.289876013994217</v>
       </c>
       <c r="H40" t="n">
         <v>857362</v>
@@ -1558,7 +1558,7 @@
         <v>0.32514101266861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.29005441069603</v>
+        <v>0.290054440498352</v>
       </c>
       <c r="H41" t="n">
         <v>53072</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500491857529</v>
+        <v>0.290500462055206</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1616,7 +1616,7 @@
         <v>0.330040007829666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.294424742460251</v>
+        <v>0.294424772262573</v>
       </c>
       <c r="H43" t="n">
         <v>236808</v>
@@ -1674,7 +1674,7 @@
         <v>0.340938001871109</v>
       </c>
       <c r="G45" t="n">
-        <v>0.304146766662598</v>
+        <v>0.304146736860275</v>
       </c>
       <c r="H45" t="n">
         <v>663295</v>
@@ -1790,7 +1790,7 @@
         <v>0.338039010763168</v>
       </c>
       <c r="G49" t="n">
-        <v>0.301560580730438</v>
+        <v>0.301560550928116</v>
       </c>
       <c r="H49" t="n">
         <v>194576</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993936538696</v>
+        <v>0.382993906736374</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.370149672031403</v>
+        <v>0.37014964222908</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2109,7 +2109,7 @@
         <v>0.429223001003265</v>
       </c>
       <c r="G60" t="n">
-        <v>0.382904708385468</v>
+        <v>0.38290473818779</v>
       </c>
       <c r="H60" t="n">
         <v>377944</v>
@@ -2225,7 +2225,7 @@
         <v>0.419023990631104</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373806297779083</v>
+        <v>0.373806327581406</v>
       </c>
       <c r="H64" t="n">
         <v>172614</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3575738966465</v>
+        <v>0.357573926448822</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2457,7 +2457,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376771211624</v>
+        <v>0.358376741409302</v>
       </c>
       <c r="H72" t="n">
         <v>393696</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183942079544</v>
+        <v>0.354183971881866</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157960414886</v>
+        <v>0.379157900810242</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2834,7 +2834,7 @@
         <v>0.429922997951508</v>
       </c>
       <c r="G85" t="n">
-        <v>0.39658984541893</v>
+        <v>0.396589815616608</v>
       </c>
       <c r="H85" t="n">
         <v>340192</v>
@@ -2950,7 +2950,7 @@
         <v>0.401127994060516</v>
       </c>
       <c r="G89" t="n">
-        <v>0.370027393102646</v>
+        <v>0.370027363300323</v>
       </c>
       <c r="H89" t="n">
         <v>311938</v>
@@ -3066,7 +3066,7 @@
         <v>0.404626995325089</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3732550740242</v>
+        <v>0.373255103826523</v>
       </c>
       <c r="H93" t="n">
         <v>433441</v>
@@ -3124,7 +3124,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G95" t="n">
-        <v>0.368920385837555</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H95" t="n">
         <v>267568</v>
@@ -3211,7 +3211,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H98" t="n">
         <v>149597</v>
@@ -3269,7 +3269,7 @@
         <v>0.386929988861084</v>
       </c>
       <c r="G100" t="n">
-        <v>0.356930166482925</v>
+        <v>0.356930196285248</v>
       </c>
       <c r="H100" t="n">
         <v>922415</v>
@@ -3298,7 +3298,7 @@
         <v>0.380831003189087</v>
       </c>
       <c r="G101" t="n">
-        <v>0.351304054260254</v>
+        <v>0.351304084062576</v>
       </c>
       <c r="H101" t="n">
         <v>1169299</v>
@@ -3356,7 +3356,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H103" t="n">
         <v>972529</v>
@@ -3414,7 +3414,7 @@
         <v>0.390929996967316</v>
       </c>
       <c r="G105" t="n">
-        <v>0.360620081424713</v>
+        <v>0.360620051622391</v>
       </c>
       <c r="H105" t="n">
         <v>196102</v>
@@ -3443,7 +3443,7 @@
         <v>0.40022799372673</v>
       </c>
       <c r="G106" t="n">
-        <v>0.369197160005569</v>
+        <v>0.369197130203247</v>
       </c>
       <c r="H106" t="n">
         <v>3752445</v>
@@ -3646,7 +3646,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H113" t="n">
         <v>105892</v>
@@ -3820,7 +3820,7 @@
         <v>0.366234004497528</v>
       </c>
       <c r="G119" t="n">
-        <v>0.337838798761368</v>
+        <v>0.33783882856369</v>
       </c>
       <c r="H119" t="n">
         <v>2519386</v>
@@ -3907,7 +3907,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862418413162</v>
+        <v>0.345862448215485</v>
       </c>
       <c r="H122" t="n">
         <v>582251</v>
@@ -3994,7 +3994,7 @@
         <v>0.344238013029099</v>
       </c>
       <c r="G125" t="n">
-        <v>0.317548215389252</v>
+        <v>0.317548245191574</v>
       </c>
       <c r="H125" t="n">
         <v>491917</v>
@@ -4139,7 +4139,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G130" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H130" t="n">
         <v>408863</v>
@@ -4168,7 +4168,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G131" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H131" t="n">
         <v>488386</v>
@@ -4226,7 +4226,7 @@
         <v>0.338838994503021</v>
       </c>
       <c r="G133" t="n">
-        <v>0.312567830085754</v>
+        <v>0.312567800283432</v>
       </c>
       <c r="H133" t="n">
         <v>58287</v>
@@ -4255,7 +4255,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G134" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H134" t="n">
         <v>235517</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169422388077</v>
+        <v>0.329169452190399</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4429,7 +4429,7 @@
         <v>0.389629989862442</v>
       </c>
       <c r="G140" t="n">
-        <v>0.359420865774155</v>
+        <v>0.359420835971832</v>
       </c>
       <c r="H140" t="n">
         <v>458480</v>
@@ -4487,7 +4487,7 @@
         <v>0.380430996417999</v>
       </c>
       <c r="G142" t="n">
-        <v>0.350935071706772</v>
+        <v>0.350935101509094</v>
       </c>
       <c r="H142" t="n">
         <v>244048</v>
@@ -4603,7 +4603,7 @@
         <v>0.381931006908417</v>
       </c>
       <c r="G146" t="n">
-        <v>0.352318793535233</v>
+        <v>0.35231876373291</v>
       </c>
       <c r="H146" t="n">
         <v>86953</v>
@@ -4690,7 +4690,7 @@
         <v>0.381830990314484</v>
       </c>
       <c r="G149" t="n">
-        <v>0.352226495742798</v>
+        <v>0.35222652554512</v>
       </c>
       <c r="H149" t="n">
         <v>304342</v>
@@ -4719,7 +4719,7 @@
         <v>0.38782998919487</v>
       </c>
       <c r="G150" t="n">
-        <v>0.357760399580002</v>
+        <v>0.357760369777679</v>
       </c>
       <c r="H150" t="n">
         <v>73463</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619968414307</v>
+        <v>0.341619998216629</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4777,7 +4777,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G152" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H152" t="n">
         <v>138916</v>
@@ -4922,7 +4922,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843703985214</v>
+        <v>0.331843733787537</v>
       </c>
       <c r="H157" t="n">
         <v>1100576</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5009,7 +5009,7 @@
         <v>0.356635987758636</v>
       </c>
       <c r="G160" t="n">
-        <v>0.328984946012497</v>
+        <v>0.328984975814819</v>
       </c>
       <c r="H160" t="n">
         <v>256812</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.331382483243942</v>
+        <v>0.33138245344162</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5241,7 +5241,7 @@
         <v>0.342938005924225</v>
       </c>
       <c r="G168" t="n">
-        <v>0.316349029541016</v>
+        <v>0.316348999738693</v>
       </c>
       <c r="H168" t="n">
         <v>570779</v>
@@ -5357,7 +5357,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.326402068138123</v>
+        <v>0.326402097940445</v>
       </c>
       <c r="H172" t="n">
         <v>220072</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.326309829950333</v>
+        <v>0.32630980014801</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5415,7 +5415,7 @@
         <v>0.341937988996506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.315426558256149</v>
+        <v>0.315426528453827</v>
       </c>
       <c r="H174" t="n">
         <v>1029741</v>
@@ -5560,7 +5560,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G179" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H179" t="n">
         <v>231414</v>
@@ -5589,7 +5589,7 @@
         <v>0.342038005590439</v>
       </c>
       <c r="G180" t="n">
-        <v>0.315518796443939</v>
+        <v>0.315518826246262</v>
       </c>
       <c r="H180" t="n">
         <v>97882</v>
@@ -5676,7 +5676,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761246442795</v>
+        <v>0.319761216640472</v>
       </c>
       <c r="H183" t="n">
         <v>499322</v>
@@ -5734,7 +5734,7 @@
         <v>0.339639008045197</v>
       </c>
       <c r="G185" t="n">
-        <v>0.313305795192719</v>
+        <v>0.313305824995041</v>
       </c>
       <c r="H185" t="n">
         <v>269383</v>
@@ -5966,7 +5966,7 @@
         <v>0.33643901348114</v>
       </c>
       <c r="G193" t="n">
-        <v>0.310353934764862</v>
+        <v>0.31035390496254</v>
       </c>
       <c r="H193" t="n">
         <v>276707</v>
@@ -5995,7 +5995,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H194" t="n">
         <v>209554</v>
@@ -6024,7 +6024,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H195" t="n">
         <v>35089</v>
@@ -6082,7 +6082,7 @@
         <v>0.336838990449905</v>
       </c>
       <c r="G197" t="n">
-        <v>0.310722887516022</v>
+        <v>0.310722917318344</v>
       </c>
       <c r="H197" t="n">
         <v>191857</v>
@@ -6111,7 +6111,7 @@
         <v>0.337038993835449</v>
       </c>
       <c r="G198" t="n">
-        <v>0.310907393693924</v>
+        <v>0.310907363891602</v>
       </c>
       <c r="H198" t="n">
         <v>482576</v>
@@ -6140,7 +6140,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.31210657954216</v>
+        <v>0.312106609344482</v>
       </c>
       <c r="H199" t="n">
         <v>29451</v>
@@ -6198,7 +6198,7 @@
         <v>0.347936987876892</v>
       </c>
       <c r="G201" t="n">
-        <v>0.320960402488708</v>
+        <v>0.320960432291031</v>
       </c>
       <c r="H201" t="n">
         <v>234454</v>
@@ -6227,7 +6227,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.323543339967728</v>
+        <v>0.32354336977005</v>
       </c>
       <c r="H202" t="n">
         <v>232428</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6401,7 +6401,7 @@
         <v>0.372732996940613</v>
       </c>
       <c r="G208" t="n">
-        <v>0.343833923339844</v>
+        <v>0.343833953142166</v>
       </c>
       <c r="H208" t="n">
         <v>21151</v>
@@ -6575,7 +6575,7 @@
         <v>0.386830002069473</v>
       </c>
       <c r="G214" t="n">
-        <v>0.356837958097458</v>
+        <v>0.356837928295135</v>
       </c>
       <c r="H214" t="n">
         <v>141958</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333532810211</v>
+        <v>0.353333503007889</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6662,7 +6662,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.338300049304962</v>
+        <v>0.33830001950264</v>
       </c>
       <c r="H217" t="n">
         <v>1242085</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028180360794</v>
+        <v>0.332028150558472</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6807,7 +6807,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G222" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H222" t="n">
         <v>259436</v>
@@ -6836,7 +6836,7 @@
         <v>0.351236999034882</v>
       </c>
       <c r="G223" t="n">
-        <v>0.324004590511322</v>
+        <v>0.324004560709</v>
       </c>
       <c r="H223" t="n">
         <v>106739</v>
@@ -6952,7 +6952,7 @@
         <v>0.355836004018784</v>
       </c>
       <c r="G227" t="n">
-        <v>0.328246980905533</v>
+        <v>0.328247010707855</v>
       </c>
       <c r="H227" t="n">
         <v>176045</v>
@@ -7126,7 +7126,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344154119492</v>
+        <v>0.322344124317169</v>
       </c>
       <c r="H233" t="n">
         <v>60253</v>
@@ -7184,7 +7184,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183267593384</v>
+        <v>0.330183297395706</v>
       </c>
       <c r="H235" t="n">
         <v>95241</v>
@@ -7271,7 +7271,7 @@
         <v>0.349936991930008</v>
       </c>
       <c r="G238" t="n">
-        <v>0.322805345058441</v>
+        <v>0.322805374860764</v>
       </c>
       <c r="H238" t="n">
         <v>60220</v>
@@ -7329,7 +7329,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.326402068138123</v>
+        <v>0.326402097940445</v>
       </c>
       <c r="H240" t="n">
         <v>211099</v>
@@ -7387,7 +7387,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332397162914276</v>
+        <v>0.332397192716599</v>
       </c>
       <c r="H242" t="n">
         <v>278620</v>
@@ -7474,7 +7474,7 @@
         <v>0.370433002710342</v>
       </c>
       <c r="G245" t="n">
-        <v>0.341712296009064</v>
+        <v>0.341712266206741</v>
       </c>
       <c r="H245" t="n">
         <v>783334</v>
@@ -7619,7 +7619,7 @@
         <v>0.377131998538971</v>
       </c>
       <c r="G250" t="n">
-        <v>0.34789189696312</v>
+        <v>0.347891867160797</v>
       </c>
       <c r="H250" t="n">
         <v>624870</v>
@@ -7735,7 +7735,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595537900925</v>
+        <v>0.352595508098602</v>
       </c>
       <c r="H254" t="n">
         <v>213674</v>
@@ -7822,7 +7822,7 @@
         <v>0.380930989980698</v>
       </c>
       <c r="G257" t="n">
-        <v>0.351396322250366</v>
+        <v>0.351396292448044</v>
       </c>
       <c r="H257" t="n">
         <v>191994</v>
@@ -7880,7 +7880,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697610139847</v>
+        <v>0.359697580337524</v>
       </c>
       <c r="H259" t="n">
         <v>372572</v>
@@ -7938,7 +7938,7 @@
         <v>0.407227009534836</v>
       </c>
       <c r="G261" t="n">
-        <v>0.37565353512764</v>
+        <v>0.375653505325317</v>
       </c>
       <c r="H261" t="n">
         <v>685961</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609376907349</v>
+        <v>0.372609347105026</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8112,7 +8112,7 @@
         <v>0.412925988435745</v>
       </c>
       <c r="G267" t="n">
-        <v>0.380910664796829</v>
+        <v>0.380910634994507</v>
       </c>
       <c r="H267" t="n">
         <v>111749</v>
@@ -8141,7 +8141,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G268" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H268" t="n">
         <v>145464</v>
@@ -8228,7 +8228,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G271" t="n">
-        <v>0.380449384450912</v>
+        <v>0.380449414253235</v>
       </c>
       <c r="H271" t="n">
         <v>143383</v>
@@ -8257,7 +8257,7 @@
         <v>0.412326008081436</v>
       </c>
       <c r="G272" t="n">
-        <v>0.380357146263123</v>
+        <v>0.380357176065445</v>
       </c>
       <c r="H272" t="n">
         <v>439414</v>
@@ -8431,7 +8431,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G278" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H278" t="n">
         <v>227740</v>
@@ -8460,7 +8460,7 @@
         <v>0.399928003549576</v>
       </c>
       <c r="G279" t="n">
-        <v>0.368920385837555</v>
+        <v>0.368920415639877</v>
       </c>
       <c r="H279" t="n">
         <v>96256</v>
@@ -8489,7 +8489,7 @@
         <v>0.403827011585236</v>
       </c>
       <c r="G280" t="n">
-        <v>0.372517108917236</v>
+        <v>0.372517138719559</v>
       </c>
       <c r="H280" t="n">
         <v>66227</v>
@@ -8576,7 +8576,7 @@
         <v>0.405526995658875</v>
       </c>
       <c r="G283" t="n">
-        <v>0.374085307121277</v>
+        <v>0.374085336923599</v>
       </c>
       <c r="H283" t="n">
         <v>186709</v>
@@ -8692,7 +8692,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G287" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H287" t="n">
         <v>280249</v>
@@ -8721,7 +8721,7 @@
         <v>0.401028007268906</v>
       </c>
       <c r="G288" t="n">
-        <v>0.369935154914856</v>
+        <v>0.369935125112534</v>
       </c>
       <c r="H288" t="n">
         <v>218241</v>
@@ -8808,7 +8808,7 @@
         <v>0.427922993898392</v>
       </c>
       <c r="G291" t="n">
-        <v>0.394744902849197</v>
+        <v>0.394744873046875</v>
       </c>
       <c r="H291" t="n">
         <v>911786</v>
@@ -8953,7 +8953,7 @@
         <v>0.470214992761612</v>
       </c>
       <c r="G296" t="n">
-        <v>0.433757871389389</v>
+        <v>0.433757841587067</v>
       </c>
       <c r="H296" t="n">
         <v>764989</v>
@@ -9040,7 +9040,7 @@
         <v>0.478413999080658</v>
       </c>
       <c r="G299" t="n">
-        <v>0.441321164369583</v>
+        <v>0.441321194171906</v>
       </c>
       <c r="H299" t="n">
         <v>731265</v>
@@ -9156,7 +9156,7 @@
         <v>0.524406015872955</v>
       </c>
       <c r="G303" t="n">
-        <v>0.483747273683548</v>
+        <v>0.48374730348587</v>
       </c>
       <c r="H303" t="n">
         <v>1152418</v>
@@ -9330,7 +9330,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G309" t="n">
-        <v>0.464839458465576</v>
+        <v>0.464839428663254</v>
       </c>
       <c r="H309" t="n">
         <v>2438508</v>
@@ -9359,7 +9359,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G310" t="n">
-        <v>0.483286082744598</v>
+        <v>0.483286052942276</v>
       </c>
       <c r="H310" t="n">
         <v>1188532</v>
@@ -9388,7 +9388,7 @@
         <v>0.558399975299835</v>
       </c>
       <c r="G311" t="n">
-        <v>0.515105545520782</v>
+        <v>0.515105605125427</v>
       </c>
       <c r="H311" t="n">
         <v>2223034</v>
@@ -9446,7 +9446,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G313" t="n">
-        <v>0.531245112419128</v>
+        <v>0.531245172023773</v>
       </c>
       <c r="H313" t="n">
         <v>1840311</v>
@@ -9649,7 +9649,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G320" t="n">
-        <v>0.557992041110992</v>
+        <v>0.557991981506348</v>
       </c>
       <c r="H320" t="n">
         <v>846974</v>
@@ -9678,7 +9678,7 @@
         <v>0.601891994476318</v>
       </c>
       <c r="G321" t="n">
-        <v>0.555225551128387</v>
+        <v>0.555225610733032</v>
       </c>
       <c r="H321" t="n">
         <v>722821</v>
@@ -9765,7 +9765,7 @@
         <v>0.645384013652802</v>
       </c>
       <c r="G324" t="n">
-        <v>0.595345497131348</v>
+        <v>0.595345556735992</v>
       </c>
       <c r="H324" t="n">
         <v>1537366</v>
@@ -9881,7 +9881,7 @@
         <v>0.65488201379776</v>
       </c>
       <c r="G328" t="n">
-        <v>0.604107141494751</v>
+        <v>0.604107081890106</v>
       </c>
       <c r="H328" t="n">
         <v>930926</v>
@@ -9910,7 +9910,7 @@
         <v>0.661381006240845</v>
       </c>
       <c r="G329" t="n">
-        <v>0.610102236270905</v>
+        <v>0.61010217666626</v>
       </c>
       <c r="H329" t="n">
         <v>1371286</v>
@@ -10200,7 +10200,7 @@
         <v>0.696874976158142</v>
       </c>
       <c r="G339" t="n">
-        <v>0.642844200134277</v>
+        <v>0.642844259738922</v>
       </c>
       <c r="H339" t="n">
         <v>725692</v>
@@ -10229,7 +10229,7 @@
         <v>0.693875014781952</v>
       </c>
       <c r="G340" t="n">
-        <v>0.64007693529129</v>
+        <v>0.640076875686646</v>
       </c>
       <c r="H340" t="n">
         <v>1222262</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097331047058</v>
+        <v>0.616097271442413</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10316,7 +10316,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G343" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H343" t="n">
         <v>1199670</v>
@@ -10345,7 +10345,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G344" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H344" t="n">
         <v>1226901</v>
@@ -10374,7 +10374,7 @@
         <v>0.653383016586304</v>
       </c>
       <c r="G345" t="n">
-        <v>0.602724313735962</v>
+        <v>0.602724373340607</v>
       </c>
       <c r="H345" t="n">
         <v>1424542</v>
@@ -10722,7 +10722,7 @@
         <v>0.68887597322464</v>
       </c>
       <c r="G357" t="n">
-        <v>0.635465383529663</v>
+        <v>0.635465443134308</v>
       </c>
       <c r="H357" t="n">
         <v>654445</v>
@@ -10809,7 +10809,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G360" t="n">
-        <v>0.609640955924988</v>
+        <v>0.609641015529633</v>
       </c>
       <c r="H360" t="n">
         <v>434952</v>
@@ -10925,7 +10925,7 @@
         <v>0.654381990432739</v>
       </c>
       <c r="G364" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H364" t="n">
         <v>375033</v>
@@ -10954,7 +10954,7 @@
         <v>0.645883977413177</v>
       </c>
       <c r="G365" t="n">
-        <v>0.608829319477081</v>
+        <v>0.608829379081726</v>
       </c>
       <c r="H365" t="n">
         <v>210377</v>
@@ -10983,7 +10983,7 @@
         <v>0.650382995605469</v>
       </c>
       <c r="G366" t="n">
-        <v>0.613070249557495</v>
+        <v>0.61307030916214</v>
       </c>
       <c r="H366" t="n">
         <v>341904</v>
@@ -11273,7 +11273,7 @@
         <v>0.617389023303986</v>
       </c>
       <c r="G376" t="n">
-        <v>0.581969141960144</v>
+        <v>0.581969201564789</v>
       </c>
       <c r="H376" t="n">
         <v>259131</v>
@@ -11389,7 +11389,7 @@
         <v>0.608891010284424</v>
       </c>
       <c r="G380" t="n">
-        <v>0.573958694934845</v>
+        <v>0.57395875453949</v>
       </c>
       <c r="H380" t="n">
         <v>251076</v>
@@ -11418,7 +11418,7 @@
         <v>0.622888028621674</v>
       </c>
       <c r="G381" t="n">
-        <v>0.587152659893036</v>
+        <v>0.587152719497681</v>
       </c>
       <c r="H381" t="n">
         <v>198695</v>
@@ -11447,7 +11447,7 @@
         <v>0.615889012813568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.580555200576782</v>
+        <v>0.580555260181427</v>
       </c>
       <c r="H382" t="n">
         <v>558855</v>
@@ -11505,7 +11505,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G384" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H384" t="n">
         <v>1352746</v>
@@ -11563,7 +11563,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G386" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H386" t="n">
         <v>141943</v>
@@ -11592,7 +11592,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G387" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H387" t="n">
         <v>349861</v>
@@ -11708,7 +11708,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G391" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H391" t="n">
         <v>289335</v>
@@ -11737,7 +11737,7 @@
         <v>0.577895998954773</v>
       </c>
       <c r="G392" t="n">
-        <v>0.544741928577423</v>
+        <v>0.544741868972778</v>
       </c>
       <c r="H392" t="n">
         <v>329337</v>
@@ -11766,7 +11766,7 @@
         <v>0.583895027637482</v>
       </c>
       <c r="G393" t="n">
-        <v>0.550396800041199</v>
+        <v>0.550396740436554</v>
       </c>
       <c r="H393" t="n">
         <v>280658</v>
@@ -11795,7 +11795,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G394" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H394" t="n">
         <v>290140</v>
@@ -11882,7 +11882,7 @@
         <v>0.565898001194</v>
       </c>
       <c r="G397" t="n">
-        <v>0.533432185649872</v>
+        <v>0.533432245254517</v>
       </c>
       <c r="H397" t="n">
         <v>459584</v>
@@ -11911,7 +11911,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G398" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H398" t="n">
         <v>210300</v>
@@ -12027,7 +12027,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G402" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H402" t="n">
         <v>228411</v>
@@ -12172,7 +12172,7 @@
         <v>0.580896019935608</v>
       </c>
       <c r="G407" t="n">
-        <v>0.547569751739502</v>
+        <v>0.547569811344147</v>
       </c>
       <c r="H407" t="n">
         <v>288350</v>
@@ -12201,7 +12201,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G408" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H408" t="n">
         <v>253441</v>
@@ -12230,7 +12230,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G409" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H409" t="n">
         <v>269272</v>
@@ -12259,7 +12259,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G410" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H410" t="n">
         <v>183867</v>
@@ -12288,7 +12288,7 @@
         <v>0.581394970417023</v>
       </c>
       <c r="G411" t="n">
-        <v>0.548040151596069</v>
+        <v>0.548040091991425</v>
       </c>
       <c r="H411" t="n">
         <v>89021</v>
@@ -12346,7 +12346,7 @@
         <v>0.589393973350525</v>
       </c>
       <c r="G413" t="n">
-        <v>0.555580258369446</v>
+        <v>0.555580198764801</v>
       </c>
       <c r="H413" t="n">
         <v>291996</v>
@@ -12433,7 +12433,7 @@
         <v>0.569397985935211</v>
       </c>
       <c r="G416" t="n">
-        <v>0.536731362342834</v>
+        <v>0.536731421947479</v>
       </c>
       <c r="H416" t="n">
         <v>473625</v>
@@ -12520,7 +12520,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G419" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H419" t="n">
         <v>180174</v>
@@ -12549,7 +12549,7 @@
         <v>0.58289498090744</v>
       </c>
       <c r="G420" t="n">
-        <v>0.549454033374786</v>
+        <v>0.549454092979431</v>
       </c>
       <c r="H420" t="n">
         <v>451568</v>
@@ -12607,7 +12607,7 @@
         <v>0.57539701461792</v>
       </c>
       <c r="G422" t="n">
-        <v>0.54238623380661</v>
+        <v>0.542386293411255</v>
       </c>
       <c r="H422" t="n">
         <v>215255</v>
@@ -12665,7 +12665,7 @@
         <v>0.571397006511688</v>
       </c>
       <c r="G424" t="n">
-        <v>0.538615703582764</v>
+        <v>0.538615763187408</v>
       </c>
       <c r="H424" t="n">
         <v>209758</v>
@@ -12723,7 +12723,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G426" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H426" t="n">
         <v>156206</v>
@@ -12752,7 +12752,7 @@
         <v>0.556400001049042</v>
       </c>
       <c r="G427" t="n">
-        <v>0.524479150772095</v>
+        <v>0.52447909116745</v>
       </c>
       <c r="H427" t="n">
         <v>232817</v>
@@ -12839,7 +12839,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G430" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H430" t="n">
         <v>130630</v>
@@ -12897,7 +12897,7 @@
         <v>0.552901029586792</v>
       </c>
       <c r="G432" t="n">
-        <v>0.521180868148804</v>
+        <v>0.521180927753448</v>
       </c>
       <c r="H432" t="n">
         <v>387167</v>
@@ -12984,7 +12984,7 @@
         <v>0.560899019241333</v>
       </c>
       <c r="G435" t="n">
-        <v>0.528720080852509</v>
+        <v>0.528720021247864</v>
       </c>
       <c r="H435" t="n">
         <v>816289</v>
@@ -13100,7 +13100,7 @@
         <v>0.59339302778244</v>
       </c>
       <c r="G439" t="n">
-        <v>0.559349834918976</v>
+        <v>0.559349894523621</v>
       </c>
       <c r="H439" t="n">
         <v>699890</v>
@@ -13129,7 +13129,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G440" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H440" t="n">
         <v>444610</v>
@@ -13158,7 +13158,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G441" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H441" t="n">
         <v>292621</v>
@@ -13245,7 +13245,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="n">
-        <v>0.603645801544189</v>
+        <v>0.603645861148834</v>
       </c>
       <c r="H444" t="n">
         <v>1107250</v>
@@ -13274,7 +13274,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="n">
-        <v>0.592807471752167</v>
+        <v>0.592807531356812</v>
       </c>
       <c r="H445" t="n">
         <v>663729</v>
@@ -13332,7 +13332,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="n">
-        <v>0.596577107906342</v>
+        <v>0.596577048301697</v>
       </c>
       <c r="H447" t="n">
         <v>238428</v>
@@ -13361,7 +13361,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="n">
-        <v>0.59516316652298</v>
+        <v>0.595163106918335</v>
       </c>
       <c r="H448" t="n">
         <v>218066</v>
@@ -13390,7 +13390,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="n">
-        <v>0.609772086143494</v>
+        <v>0.609772026538849</v>
       </c>
       <c r="H449" t="n">
         <v>909618</v>
@@ -13448,7 +13448,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="n">
-        <v>0.599876284599304</v>
+        <v>0.599876224994659</v>
       </c>
       <c r="H451" t="n">
         <v>477138</v>
@@ -13738,7 +13738,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H461" t="n">
         <v>114187</v>
@@ -13767,7 +13767,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="n">
-        <v>0.565947234630585</v>
+        <v>0.565947294235229</v>
       </c>
       <c r="H462" t="n">
         <v>238863</v>
@@ -13883,7 +13883,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="n">
-        <v>0.564533293247223</v>
+        <v>0.564533352851868</v>
       </c>
       <c r="H466" t="n">
         <v>222204</v>
@@ -13970,7 +13970,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="n">
-        <v>0.578670918941498</v>
+        <v>0.578670859336853</v>
       </c>
       <c r="H469" t="n">
         <v>139232</v>
@@ -14115,7 +14115,7 @@
         <v>0.594393014907837</v>
       </c>
       <c r="G474" t="n">
-        <v>0.560292422771454</v>
+        <v>0.560292482376099</v>
       </c>
       <c r="H474" t="n">
         <v>149208</v>
@@ -14144,7 +14144,7 @@
         <v>0.588894009590149</v>
       </c>
       <c r="G475" t="n">
-        <v>0.555108904838562</v>
+        <v>0.555108964443207</v>
       </c>
       <c r="H475" t="n">
         <v>148025</v>
@@ -14202,7 +14202,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="n">
-        <v>0.537673115730286</v>
+        <v>0.53767317533493</v>
       </c>
       <c r="H477" t="n">
         <v>352368</v>
@@ -14405,7 +14405,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="n">
-        <v>0.506100654602051</v>
+        <v>0.506100714206696</v>
       </c>
       <c r="H484" t="n">
         <v>271973</v>
@@ -14695,7 +14695,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H494" t="n">
         <v>58278</v>
@@ -14724,7 +14724,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G495" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H495" t="n">
         <v>163569</v>
@@ -14840,7 +14840,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H499" t="n">
         <v>78535</v>
@@ -14869,7 +14869,7 @@
         <v>0.573897004127502</v>
       </c>
       <c r="G500" t="n">
-        <v>0.540972292423248</v>
+        <v>0.540972352027893</v>
       </c>
       <c r="H500" t="n">
         <v>70687</v>
@@ -14927,7 +14927,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="n">
-        <v>0.515997409820557</v>
+        <v>0.515997350215912</v>
       </c>
       <c r="H502" t="n">
         <v>149092</v>
@@ -14956,7 +14956,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="n">
-        <v>0.488194495439529</v>
+        <v>0.488194525241852</v>
       </c>
       <c r="H503" t="n">
         <v>1026439</v>
@@ -14985,7 +14985,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H504" t="n">
         <v>196576</v>
@@ -15101,7 +15101,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="n">
-        <v>0.512226819992065</v>
+        <v>0.51222687959671</v>
       </c>
       <c r="H508" t="n">
         <v>41572</v>
@@ -15188,7 +15188,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H511" t="n">
         <v>235907</v>
@@ -15217,7 +15217,7 @@
         <v>0.566398024559021</v>
       </c>
       <c r="G512" t="n">
-        <v>0.5339035987854</v>
+        <v>0.533903539180756</v>
       </c>
       <c r="H512" t="n">
         <v>80711</v>
@@ -15246,7 +15246,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G513" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H513" t="n">
         <v>68229</v>
@@ -15275,7 +15275,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G514" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H514" t="n">
         <v>429758</v>
@@ -15362,7 +15362,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G517" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H517" t="n">
         <v>143705</v>
@@ -15507,7 +15507,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G522" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H522" t="n">
         <v>79164</v>
@@ -15536,7 +15536,7 @@
         <v>0.579895973205566</v>
       </c>
       <c r="G523" t="n">
-        <v>0.546627104282379</v>
+        <v>0.546627163887024</v>
       </c>
       <c r="H523" t="n">
         <v>97732</v>
@@ -15594,7 +15594,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="n">
-        <v>0.5437992811203</v>
+        <v>0.543799221515656</v>
       </c>
       <c r="H525" t="n">
         <v>53867</v>
@@ -15710,7 +15710,7 @@
         <v>0.590893983840942</v>
       </c>
       <c r="G529" t="n">
-        <v>0.556994199752808</v>
+        <v>0.556994140148163</v>
       </c>
       <c r="H529" t="n">
         <v>118746</v>
@@ -15797,7 +15797,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="n">
-        <v>0.545684516429901</v>
+        <v>0.545684456825256</v>
       </c>
       <c r="H532" t="n">
         <v>205602</v>
@@ -15855,7 +15855,7 @@
         <v>0.571896970272064</v>
       </c>
       <c r="G534" t="n">
-        <v>0.539086997509003</v>
+        <v>0.539087057113647</v>
       </c>
       <c r="H534" t="n">
         <v>98856</v>
@@ -15913,7 +15913,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="n">
-        <v>0.51835298538208</v>
+        <v>0.518352925777435</v>
       </c>
       <c r="H536" t="n">
         <v>79457</v>
@@ -15942,7 +15942,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="n">
-        <v>0.49384930729866</v>
+        <v>0.493849337100983</v>
       </c>
       <c r="H537" t="n">
         <v>518619</v>
@@ -16000,7 +16000,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H539" t="n">
         <v>178433</v>
@@ -16029,7 +16029,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="n">
-        <v>0.482539653778076</v>
+        <v>0.482539623975754</v>
       </c>
       <c r="H540" t="n">
         <v>175327</v>
@@ -16116,7 +16116,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="n">
-        <v>0.478770047426224</v>
+        <v>0.478770077228546</v>
       </c>
       <c r="H543" t="n">
         <v>269915</v>
@@ -16145,7 +16145,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H544" t="n">
         <v>168852</v>
@@ -16174,7 +16174,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="n">
-        <v>0.49290668964386</v>
+        <v>0.492906719446182</v>
       </c>
       <c r="H545" t="n">
         <v>96811</v>
@@ -16261,7 +16261,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="n">
-        <v>0.490078777074814</v>
+        <v>0.490078747272491</v>
       </c>
       <c r="H548" t="n">
         <v>145160</v>
@@ -16290,7 +16290,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H549" t="n">
         <v>92949</v>
@@ -16319,7 +16319,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H550" t="n">
         <v>133866</v>
@@ -16377,7 +16377,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="n">
-        <v>0.489137142896652</v>
+        <v>0.48913711309433</v>
       </c>
       <c r="H552" t="n">
         <v>240396</v>
@@ -16580,7 +16580,7 @@
         <v>0.559898972511292</v>
       </c>
       <c r="G559" t="n">
-        <v>0.527777314186096</v>
+        <v>0.527777373790741</v>
       </c>
       <c r="H559" t="n">
         <v>314325</v>
@@ -16725,7 +16725,7 @@
         <v>0.554899990558624</v>
       </c>
       <c r="G564" t="n">
-        <v>0.523065209388733</v>
+        <v>0.523065149784088</v>
       </c>
       <c r="H564" t="n">
         <v>355078</v>
@@ -16783,7 +16783,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="n">
-        <v>0.491021364927292</v>
+        <v>0.491021424531937</v>
       </c>
       <c r="H566" t="n">
         <v>370087</v>
@@ -16812,7 +16812,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="n">
-        <v>0.487251818180084</v>
+        <v>0.487251847982407</v>
       </c>
       <c r="H567" t="n">
         <v>425158</v>
@@ -16870,7 +16870,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="n">
-        <v>0.467931687831879</v>
+        <v>0.467931717634201</v>
       </c>
       <c r="H569" t="n">
         <v>298487</v>
@@ -17218,7 +17218,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="n">
-        <v>0.451909810304642</v>
+        <v>0.451909840106964</v>
       </c>
       <c r="H581" t="n">
         <v>283637</v>
@@ -17421,7 +17421,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="n">
-        <v>0.469815999269485</v>
+        <v>0.469816029071808</v>
       </c>
       <c r="H588" t="n">
         <v>121246</v>
@@ -17537,7 +17537,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H592" t="n">
         <v>106747</v>
@@ -17624,7 +17624,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H595" t="n">
         <v>147417</v>
@@ -17682,7 +17682,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H597" t="n">
         <v>59239</v>
@@ -17711,7 +17711,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H598" t="n">
         <v>241824</v>
@@ -17827,7 +17827,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H602" t="n">
         <v>287903</v>
@@ -17885,7 +17885,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H604" t="n">
         <v>1272412</v>
@@ -17914,7 +17914,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H605" t="n">
         <v>1104869</v>
@@ -18001,7 +18001,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H608" t="n">
         <v>43571</v>
@@ -18030,7 +18030,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H609" t="n">
         <v>69465</v>
@@ -18088,7 +18088,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="n">
-        <v>0.458977669477463</v>
+        <v>0.458977699279785</v>
       </c>
       <c r="H611" t="n">
         <v>57385</v>
@@ -18117,7 +18117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H612" t="n">
         <v>209658</v>
@@ -18146,7 +18146,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H613" t="n">
         <v>10902</v>
@@ -18204,7 +18204,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="n">
-        <v>0.458036005496979</v>
+        <v>0.458035975694656</v>
       </c>
       <c r="H615" t="n">
         <v>157901</v>
@@ -18233,7 +18233,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H616" t="n">
         <v>192728</v>
@@ -18291,7 +18291,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="n">
-        <v>0.466517776250839</v>
+        <v>0.466517746448517</v>
       </c>
       <c r="H618" t="n">
         <v>74901</v>
@@ -18407,7 +18407,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="n">
-        <v>0.458506345748901</v>
+        <v>0.458506375551224</v>
       </c>
       <c r="H622" t="n">
         <v>442685</v>
@@ -80154,6 +80154,35 @@
         <v>129826</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.763999998569489</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.749000012874603</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>394105</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.419223994016647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373984724283218</v>
+        <v>0.373984754085541</v>
       </c>
       <c r="H4" t="n">
         <v>28227</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920339107513</v>
+        <v>0.367920368909836</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -630,7 +630,7 @@
         <v>0.406127005815506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.362301051616669</v>
+        <v>0.362301081418991</v>
       </c>
       <c r="H9" t="n">
         <v>183012</v>
@@ -804,7 +804,7 @@
         <v>0.354936003684998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316634207963943</v>
+        <v>0.316634178161621</v>
       </c>
       <c r="H15" t="n">
         <v>315990</v>
@@ -833,7 +833,7 @@
         <v>0.365433990955353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.325999289751053</v>
+        <v>0.325999319553375</v>
       </c>
       <c r="H16" t="n">
         <v>293259</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272164583206</v>
+        <v>0.321272134780884</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -1007,7 +1007,7 @@
         <v>0.370133012533188</v>
       </c>
       <c r="G22" t="n">
-        <v>0.330191284418106</v>
+        <v>0.330191254615784</v>
       </c>
       <c r="H22" t="n">
         <v>1594825</v>
@@ -1210,7 +1210,7 @@
         <v>0.329540997743607</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293979585170746</v>
+        <v>0.293979614973068</v>
       </c>
       <c r="H29" t="n">
         <v>282359</v>
@@ -1239,7 +1239,7 @@
         <v>0.317043006420135</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282830327749252</v>
+        <v>0.28283029794693</v>
       </c>
       <c r="H30" t="n">
         <v>239091</v>
@@ -1355,7 +1355,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984805345535</v>
+        <v>0.288984835147858</v>
       </c>
       <c r="H34" t="n">
         <v>920116</v>
@@ -1500,7 +1500,7 @@
         <v>0.329939991235733</v>
       </c>
       <c r="G39" t="n">
-        <v>0.294335514307022</v>
+        <v>0.294335544109344</v>
       </c>
       <c r="H39" t="n">
         <v>133602</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500462055206</v>
+        <v>0.290500432252884</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1819,7 +1819,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471352577209</v>
+        <v>0.301471382379532</v>
       </c>
       <c r="H50" t="n">
         <v>368157</v>
@@ -2051,7 +2051,7 @@
         <v>0.429322987794876</v>
       </c>
       <c r="G58" t="n">
-        <v>0.382993906736374</v>
+        <v>0.382993936538696</v>
       </c>
       <c r="H58" t="n">
         <v>819768</v>
@@ -2138,7 +2138,7 @@
         <v>0.423523992300034</v>
       </c>
       <c r="G61" t="n">
-        <v>0.377820700407028</v>
+        <v>0.377820730209351</v>
       </c>
       <c r="H61" t="n">
         <v>76617</v>
@@ -2196,7 +2196,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063541889191</v>
+        <v>0.384063512086868</v>
       </c>
       <c r="H63" t="n">
         <v>163812</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178721904755</v>
+        <v>0.359178751707077</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2486,7 +2486,7 @@
         <v>0.395229011774063</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352579087018967</v>
+        <v>0.352579116821289</v>
       </c>
       <c r="H73" t="n">
         <v>623896</v>
@@ -2602,7 +2602,7 @@
         <v>0.395428985357285</v>
       </c>
       <c r="G77" t="n">
-        <v>0.352757483720779</v>
+        <v>0.352757513523102</v>
       </c>
       <c r="H77" t="n">
         <v>206044</v>
@@ -2718,7 +2718,7 @@
         <v>0.405927002429962</v>
       </c>
       <c r="G81" t="n">
-        <v>0.362122654914856</v>
+        <v>0.362122625112534</v>
       </c>
       <c r="H81" t="n">
         <v>732739</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157900810242</v>
+        <v>0.379157930612564</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -80180,9 +80180,38 @@
         <v>0.754999995231628</v>
       </c>
       <c r="H2752" t="n">
-        <v>394105</v>
+        <v>401822</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.750999987125397</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.757000029087067</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.749000012874603</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>155531</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.422524005174637</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37692865729332</v>
+        <v>0.376928627490997</v>
       </c>
       <c r="H3" t="n">
         <v>34874</v>
@@ -514,7 +514,7 @@
         <v>0.412425994873047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.367920368909836</v>
+        <v>0.367920309305191</v>
       </c>
       <c r="H5" t="n">
         <v>83279</v>
@@ -572,7 +572,7 @@
         <v>0.410126000642776</v>
       </c>
       <c r="G7" t="n">
-        <v>0.365868508815765</v>
+        <v>0.365868479013443</v>
       </c>
       <c r="H7" t="n">
         <v>71244</v>
@@ -601,7 +601,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.366849839687347</v>
+        <v>0.366849809885025</v>
       </c>
       <c r="H8" t="n">
         <v>58014</v>
@@ -833,7 +833,7 @@
         <v>0.365433990955353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.325999319553375</v>
+        <v>0.325999289751053</v>
       </c>
       <c r="H16" t="n">
         <v>293259</v>
@@ -891,7 +891,7 @@
         <v>0.360134989023209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.321272134780884</v>
+        <v>0.321272164583206</v>
       </c>
       <c r="H18" t="n">
         <v>942408</v>
@@ -920,7 +920,7 @@
         <v>0.360334992408752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.321450531482697</v>
+        <v>0.321450561285019</v>
       </c>
       <c r="H19" t="n">
         <v>460284</v>
@@ -1036,7 +1036,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314671576023102</v>
+        <v>0.314671605825424</v>
       </c>
       <c r="H23" t="n">
         <v>2368187</v>
@@ -1094,7 +1094,7 @@
         <v>0.344538003206253</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307358264923096</v>
+        <v>0.307358235120773</v>
       </c>
       <c r="H25" t="n">
         <v>217873</v>
@@ -1123,7 +1123,7 @@
         <v>0.346038013696671</v>
       </c>
       <c r="G26" t="n">
-        <v>0.308696389198303</v>
+        <v>0.308696359395981</v>
       </c>
       <c r="H26" t="n">
         <v>149000</v>
@@ -1152,7 +1152,7 @@
         <v>0.328440994024277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.292998313903809</v>
+        <v>0.292998284101486</v>
       </c>
       <c r="H27" t="n">
         <v>582541</v>
@@ -1268,7 +1268,7 @@
         <v>0.323742002248764</v>
       </c>
       <c r="G31" t="n">
-        <v>0.288806408643723</v>
+        <v>0.2888063788414</v>
       </c>
       <c r="H31" t="n">
         <v>538832</v>
@@ -1355,7 +1355,7 @@
         <v>0.323942005634308</v>
       </c>
       <c r="G34" t="n">
-        <v>0.288984835147858</v>
+        <v>0.288984805345535</v>
       </c>
       <c r="H34" t="n">
         <v>920116</v>
@@ -1384,7 +1384,7 @@
         <v>0.331440001726151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.295673698186874</v>
+        <v>0.295673668384552</v>
       </c>
       <c r="H35" t="n">
         <v>189584</v>
@@ -1587,7 +1587,7 @@
         <v>0.325641006231308</v>
       </c>
       <c r="G42" t="n">
-        <v>0.290500432252884</v>
+        <v>0.290500491857529</v>
       </c>
       <c r="H42" t="n">
         <v>538377</v>
@@ -1645,7 +1645,7 @@
         <v>0.336638987064362</v>
       </c>
       <c r="G44" t="n">
-        <v>0.300311625003815</v>
+        <v>0.300311654806137</v>
       </c>
       <c r="H44" t="n">
         <v>929955</v>
@@ -1761,7 +1761,7 @@
         <v>0.33983901143074</v>
       </c>
       <c r="G48" t="n">
-        <v>0.303166329860687</v>
+        <v>0.303166300058365</v>
       </c>
       <c r="H48" t="n">
         <v>159693</v>
@@ -1819,7 +1819,7 @@
         <v>0.337938994169235</v>
       </c>
       <c r="G50" t="n">
-        <v>0.301471382379532</v>
+        <v>0.301471322774887</v>
       </c>
       <c r="H50" t="n">
         <v>368157</v>
@@ -1848,7 +1848,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.313869595527649</v>
+        <v>0.313869625329971</v>
       </c>
       <c r="H51" t="n">
         <v>251359</v>
@@ -1964,7 +1964,7 @@
         <v>0.373833000659943</v>
       </c>
       <c r="G55" t="n">
-        <v>0.333491951227188</v>
+        <v>0.33349198102951</v>
       </c>
       <c r="H55" t="n">
         <v>361299</v>
@@ -2080,7 +2080,7 @@
         <v>0.414925009012222</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37014964222908</v>
+        <v>0.370149672031403</v>
       </c>
       <c r="H59" t="n">
         <v>791355</v>
@@ -2167,7 +2167,7 @@
         <v>0.429722994565964</v>
       </c>
       <c r="G62" t="n">
-        <v>0.383350759744644</v>
+        <v>0.383350729942322</v>
       </c>
       <c r="H62" t="n">
         <v>181871</v>
@@ -2196,7 +2196,7 @@
         <v>0.430521994829178</v>
       </c>
       <c r="G63" t="n">
-        <v>0.384063512086868</v>
+        <v>0.384063541889191</v>
       </c>
       <c r="H63" t="n">
         <v>163812</v>
@@ -2312,7 +2312,7 @@
         <v>0.397127985954285</v>
       </c>
       <c r="G67" t="n">
-        <v>0.35427314043045</v>
+        <v>0.354273170232773</v>
       </c>
       <c r="H67" t="n">
         <v>172954</v>
@@ -2370,7 +2370,7 @@
         <v>0.400828003883362</v>
       </c>
       <c r="G69" t="n">
-        <v>0.357573926448822</v>
+        <v>0.3575738966465</v>
       </c>
       <c r="H69" t="n">
         <v>491294</v>
@@ -2399,7 +2399,7 @@
         <v>0.402626991271973</v>
       </c>
       <c r="G70" t="n">
-        <v>0.359178751707077</v>
+        <v>0.359178721904755</v>
       </c>
       <c r="H70" t="n">
         <v>768029</v>
@@ -2457,7 +2457,7 @@
         <v>0.401728004217148</v>
       </c>
       <c r="G72" t="n">
-        <v>0.358376741409302</v>
+        <v>0.358376771211624</v>
       </c>
       <c r="H72" t="n">
         <v>393696</v>
@@ -2515,7 +2515,7 @@
         <v>0.397027999162674</v>
       </c>
       <c r="G74" t="n">
-        <v>0.354183971881866</v>
+        <v>0.354183942079544</v>
       </c>
       <c r="H74" t="n">
         <v>102240</v>
@@ -2602,7 +2602,7 @@
         <v>0.395428985357285</v>
       </c>
       <c r="G77" t="n">
-        <v>0.352757513523102</v>
+        <v>0.352757483720779</v>
       </c>
       <c r="H77" t="n">
         <v>206044</v>
@@ -2631,7 +2631,7 @@
         <v>0.401827991008759</v>
       </c>
       <c r="G78" t="n">
-        <v>0.358465969562531</v>
+        <v>0.358465999364853</v>
       </c>
       <c r="H78" t="n">
         <v>145425</v>
@@ -2805,7 +2805,7 @@
         <v>0.42502298951149</v>
       </c>
       <c r="G84" t="n">
-        <v>0.379157930612564</v>
+        <v>0.379157900810242</v>
       </c>
       <c r="H84" t="n">
         <v>853215</v>
@@ -2921,7 +2921,7 @@
         <v>0.404026985168457</v>
       </c>
       <c r="G88" t="n">
-        <v>0.372701615095139</v>
+        <v>0.372701585292816</v>
       </c>
       <c r="H88" t="n">
         <v>354215</v>
@@ -3008,7 +3008,7 @@
         <v>0.402727007865906</v>
       </c>
       <c r="G91" t="n">
-        <v>0.371502429246902</v>
+        <v>0.37150239944458</v>
       </c>
       <c r="H91" t="n">
         <v>148553</v>
@@ -3153,7 +3153,7 @@
         <v>0.399827986955643</v>
       </c>
       <c r="G96" t="n">
-        <v>0.368828147649765</v>
+        <v>0.368828177452087</v>
       </c>
       <c r="H96" t="n">
         <v>378647</v>
@@ -3182,7 +3182,7 @@
         <v>0.393429011106491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.362925320863724</v>
+        <v>0.362925291061401</v>
       </c>
       <c r="H97" t="n">
         <v>371654</v>
@@ -3211,7 +3211,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G98" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H98" t="n">
         <v>149597</v>
@@ -3356,7 +3356,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H103" t="n">
         <v>972529</v>
@@ -3472,7 +3472,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G107" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H107" t="n">
         <v>1327868</v>
@@ -3588,7 +3588,7 @@
         <v>0.394928991794586</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36430898308754</v>
+        <v>0.364309012889862</v>
       </c>
       <c r="H111" t="n">
         <v>269379</v>
@@ -3617,7 +3617,7 @@
         <v>0.388429999351501</v>
       </c>
       <c r="G112" t="n">
-        <v>0.358313888311386</v>
+        <v>0.358313918113708</v>
       </c>
       <c r="H112" t="n">
         <v>133757</v>
@@ -3646,7 +3646,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G113" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H113" t="n">
         <v>105892</v>
@@ -3733,7 +3733,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H116" t="n">
         <v>471777</v>
@@ -3907,7 +3907,7 @@
         <v>0.374931991100311</v>
       </c>
       <c r="G122" t="n">
-        <v>0.345862448215485</v>
+        <v>0.345862418413162</v>
       </c>
       <c r="H122" t="n">
         <v>582251</v>
@@ -3936,7 +3936,7 @@
         <v>0.389730006456375</v>
       </c>
       <c r="G123" t="n">
-        <v>0.359513133764267</v>
+        <v>0.359513103961945</v>
       </c>
       <c r="H123" t="n">
         <v>361479</v>
@@ -4110,7 +4110,7 @@
         <v>0.350237011909485</v>
       </c>
       <c r="G129" t="n">
-        <v>0.323082119226456</v>
+        <v>0.323082089424133</v>
       </c>
       <c r="H129" t="n">
         <v>128422</v>
@@ -4284,7 +4284,7 @@
         <v>0.35683599114418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.329169452190399</v>
+        <v>0.329169481992722</v>
       </c>
       <c r="H135" t="n">
         <v>53756</v>
@@ -4342,7 +4342,7 @@
         <v>0.374033004045486</v>
       </c>
       <c r="G137" t="n">
-        <v>0.345033138990402</v>
+        <v>0.34503310918808</v>
       </c>
       <c r="H137" t="n">
         <v>55292</v>
@@ -4603,7 +4603,7 @@
         <v>0.381931006908417</v>
       </c>
       <c r="G146" t="n">
-        <v>0.35231876373291</v>
+        <v>0.352318793535233</v>
       </c>
       <c r="H146" t="n">
         <v>86953</v>
@@ -4719,7 +4719,7 @@
         <v>0.38782998919487</v>
       </c>
       <c r="G150" t="n">
-        <v>0.357760369777679</v>
+        <v>0.357760399580002</v>
       </c>
       <c r="H150" t="n">
         <v>73463</v>
@@ -4748,7 +4748,7 @@
         <v>0.370332986116409</v>
       </c>
       <c r="G151" t="n">
-        <v>0.341619998216629</v>
+        <v>0.341620028018951</v>
       </c>
       <c r="H151" t="n">
         <v>404731</v>
@@ -4922,7 +4922,7 @@
         <v>0.359735012054443</v>
       </c>
       <c r="G157" t="n">
-        <v>0.331843733787537</v>
+        <v>0.331843703985214</v>
       </c>
       <c r="H157" t="n">
         <v>1100576</v>
@@ -4980,7 +4980,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G159" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H159" t="n">
         <v>975620</v>
@@ -5038,7 +5038,7 @@
         <v>0.359234988689423</v>
       </c>
       <c r="G161" t="n">
-        <v>0.33138245344162</v>
+        <v>0.331382423639297</v>
       </c>
       <c r="H161" t="n">
         <v>125301</v>
@@ -5154,7 +5154,7 @@
         <v>0.350937008857727</v>
       </c>
       <c r="G165" t="n">
-        <v>0.323727816343307</v>
+        <v>0.32372784614563</v>
       </c>
       <c r="H165" t="n">
         <v>1547058</v>
@@ -5241,7 +5241,7 @@
         <v>0.342938005924225</v>
       </c>
       <c r="G168" t="n">
-        <v>0.316348999738693</v>
+        <v>0.316349029541016</v>
       </c>
       <c r="H168" t="n">
         <v>570779</v>
@@ -5357,7 +5357,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G172" t="n">
-        <v>0.326402097940445</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H172" t="n">
         <v>220072</v>
@@ -5386,7 +5386,7 @@
         <v>0.353736013174057</v>
       </c>
       <c r="G173" t="n">
-        <v>0.32630980014801</v>
+        <v>0.326309829950333</v>
       </c>
       <c r="H173" t="n">
         <v>61371</v>
@@ -5444,7 +5444,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G175" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H175" t="n">
         <v>311100</v>
@@ -5473,7 +5473,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G176" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H176" t="n">
         <v>198283</v>
@@ -5502,7 +5502,7 @@
         <v>0.345238000154495</v>
       </c>
       <c r="G177" t="n">
-        <v>0.318470686674118</v>
+        <v>0.31847071647644</v>
       </c>
       <c r="H177" t="n">
         <v>167208</v>
@@ -5531,7 +5531,7 @@
         <v>0.349736988544464</v>
       </c>
       <c r="G178" t="n">
-        <v>0.322620838880539</v>
+        <v>0.322620868682861</v>
       </c>
       <c r="H178" t="n">
         <v>68182</v>
@@ -5676,7 +5676,7 @@
         <v>0.346637010574341</v>
       </c>
       <c r="G183" t="n">
-        <v>0.319761216640472</v>
+        <v>0.319761246442795</v>
       </c>
       <c r="H183" t="n">
         <v>499322</v>
@@ -5792,7 +5792,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G187" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H187" t="n">
         <v>969165</v>
@@ -5850,7 +5850,7 @@
         <v>0.335938990116119</v>
       </c>
       <c r="G189" t="n">
-        <v>0.309892684221268</v>
+        <v>0.309892654418945</v>
       </c>
       <c r="H189" t="n">
         <v>96038</v>
@@ -5995,7 +5995,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G194" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H194" t="n">
         <v>209554</v>
@@ -6024,7 +6024,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G195" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H195" t="n">
         <v>35089</v>
@@ -6082,7 +6082,7 @@
         <v>0.336838990449905</v>
       </c>
       <c r="G197" t="n">
-        <v>0.310722917318344</v>
+        <v>0.310722887516022</v>
       </c>
       <c r="H197" t="n">
         <v>191857</v>
@@ -6111,7 +6111,7 @@
         <v>0.337038993835449</v>
       </c>
       <c r="G198" t="n">
-        <v>0.310907363891602</v>
+        <v>0.310907393693924</v>
       </c>
       <c r="H198" t="n">
         <v>482576</v>
@@ -6140,7 +6140,7 @@
         <v>0.338339000940323</v>
       </c>
       <c r="G199" t="n">
-        <v>0.312106609344482</v>
+        <v>0.31210657954216</v>
       </c>
       <c r="H199" t="n">
         <v>29451</v>
@@ -6227,7 +6227,7 @@
         <v>0.350737005472183</v>
       </c>
       <c r="G202" t="n">
-        <v>0.32354336977005</v>
+        <v>0.323543339967728</v>
       </c>
       <c r="H202" t="n">
         <v>232428</v>
@@ -6285,7 +6285,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G204" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H204" t="n">
         <v>671302</v>
@@ -6314,7 +6314,7 @@
         <v>0.36693400144577</v>
       </c>
       <c r="G205" t="n">
-        <v>0.338484555482864</v>
+        <v>0.338484525680542</v>
       </c>
       <c r="H205" t="n">
         <v>279724</v>
@@ -6488,7 +6488,7 @@
         <v>0.383830994367599</v>
       </c>
       <c r="G211" t="n">
-        <v>0.354071497917175</v>
+        <v>0.354071468114853</v>
       </c>
       <c r="H211" t="n">
         <v>206307</v>
@@ -6517,7 +6517,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G212" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H212" t="n">
         <v>184112</v>
@@ -6546,7 +6546,7 @@
         <v>0.384231001138687</v>
       </c>
       <c r="G213" t="n">
-        <v>0.354440450668335</v>
+        <v>0.354440480470657</v>
       </c>
       <c r="H213" t="n">
         <v>256167</v>
@@ -6604,7 +6604,7 @@
         <v>0.383031010627747</v>
       </c>
       <c r="G215" t="n">
-        <v>0.353333503007889</v>
+        <v>0.353333473205566</v>
       </c>
       <c r="H215" t="n">
         <v>253016</v>
@@ -6662,7 +6662,7 @@
         <v>0.366733998060226</v>
       </c>
       <c r="G217" t="n">
-        <v>0.33830001950264</v>
+        <v>0.338300049304962</v>
       </c>
       <c r="H217" t="n">
         <v>1242085</v>
@@ -6691,7 +6691,7 @@
         <v>0.359934985637665</v>
       </c>
       <c r="G218" t="n">
-        <v>0.332028150558472</v>
+        <v>0.332028180360794</v>
       </c>
       <c r="H218" t="n">
         <v>1728283</v>
@@ -6749,7 +6749,7 @@
         <v>0.35963499546051</v>
       </c>
       <c r="G220" t="n">
-        <v>0.331751435995102</v>
+        <v>0.331751465797424</v>
       </c>
       <c r="H220" t="n">
         <v>241870</v>
@@ -6778,7 +6778,7 @@
         <v>0.353536009788513</v>
       </c>
       <c r="G221" t="n">
-        <v>0.326125353574753</v>
+        <v>0.32612532377243</v>
       </c>
       <c r="H221" t="n">
         <v>240850</v>
@@ -6894,7 +6894,7 @@
         <v>0.350037008523941</v>
       </c>
       <c r="G225" t="n">
-        <v>0.322897613048553</v>
+        <v>0.322897642850876</v>
       </c>
       <c r="H225" t="n">
         <v>81571</v>
@@ -6923,7 +6923,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G226" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H226" t="n">
         <v>90191</v>
@@ -7010,7 +7010,7 @@
         <v>0.352436006069183</v>
       </c>
       <c r="G229" t="n">
-        <v>0.325110614299774</v>
+        <v>0.325110644102097</v>
       </c>
       <c r="H229" t="n">
         <v>52752</v>
@@ -7068,7 +7068,7 @@
         <v>0.351837009191513</v>
       </c>
       <c r="G231" t="n">
-        <v>0.324558049440384</v>
+        <v>0.324558079242706</v>
       </c>
       <c r="H231" t="n">
         <v>85940</v>
@@ -7126,7 +7126,7 @@
         <v>0.34943699836731</v>
       </c>
       <c r="G233" t="n">
-        <v>0.322344124317169</v>
+        <v>0.322344154119492</v>
       </c>
       <c r="H233" t="n">
         <v>60253</v>
@@ -7155,7 +7155,7 @@
         <v>0.352735996246338</v>
       </c>
       <c r="G234" t="n">
-        <v>0.325387358665466</v>
+        <v>0.325387388467789</v>
       </c>
       <c r="H234" t="n">
         <v>61950</v>
@@ -7184,7 +7184,7 @@
         <v>0.357935011386871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.330183297395706</v>
+        <v>0.330183267593384</v>
       </c>
       <c r="H235" t="n">
         <v>95241</v>
@@ -7329,7 +7329,7 @@
         <v>0.353835999965668</v>
       </c>
       <c r="G240" t="n">
-        <v>0.326402097940445</v>
+        <v>0.326402068138123</v>
       </c>
       <c r="H240" t="n">
         <v>211099</v>
@@ -7561,7 +7561,7 @@
         <v>0.372933000326157</v>
       </c>
       <c r="G248" t="n">
-        <v>0.344018399715424</v>
+        <v>0.344018429517746</v>
       </c>
       <c r="H248" t="n">
         <v>335681</v>
@@ -7648,7 +7648,7 @@
         <v>0.382930994033813</v>
       </c>
       <c r="G251" t="n">
-        <v>0.353241264820099</v>
+        <v>0.353241235017776</v>
       </c>
       <c r="H251" t="n">
         <v>591930</v>
@@ -7735,7 +7735,7 @@
         <v>0.382230997085571</v>
       </c>
       <c r="G254" t="n">
-        <v>0.352595508098602</v>
+        <v>0.352595537900925</v>
       </c>
       <c r="H254" t="n">
         <v>213674</v>
@@ -7880,7 +7880,7 @@
         <v>0.389930009841919</v>
       </c>
       <c r="G259" t="n">
-        <v>0.359697580337524</v>
+        <v>0.359697610139847</v>
       </c>
       <c r="H259" t="n">
         <v>372572</v>
@@ -8025,7 +8025,7 @@
         <v>0.412625998258591</v>
       </c>
       <c r="G264" t="n">
-        <v>0.380633920431137</v>
+        <v>0.380633890628815</v>
       </c>
       <c r="H264" t="n">
         <v>828739</v>
@@ -8054,7 +8054,7 @@
         <v>0.403926998376846</v>
       </c>
       <c r="G265" t="n">
-        <v>0.372609347105026</v>
+        <v>0.372609376907349</v>
       </c>
       <c r="H265" t="n">
         <v>636688</v>
@@ -8199,7 +8199,7 @@
         <v>0.411226004362106</v>
       </c>
       <c r="G270" t="n">
-        <v>0.379342466592789</v>
+        <v>0.379342436790466</v>
       </c>
       <c r="H270" t="n">
         <v>170128</v>
@@ -8750,7 +8750,7 @@
         <v>0.404926985502243</v>
       </c>
       <c r="G289" t="n">
-        <v>0.373531848192215</v>
+        <v>0.373531818389893</v>
       </c>
       <c r="H289" t="n">
         <v>229876</v>
@@ -8895,7 +8895,7 @@
         <v>0.469814985990524</v>
       </c>
       <c r="G294" t="n">
-        <v>0.433388859033585</v>
+        <v>0.433388888835907</v>
       </c>
       <c r="H294" t="n">
         <v>517174</v>
@@ -9011,7 +9011,7 @@
         <v>0.473015010356903</v>
       </c>
       <c r="G298" t="n">
-        <v>0.436340808868408</v>
+        <v>0.436340779066086</v>
       </c>
       <c r="H298" t="n">
         <v>273396</v>
@@ -9098,7 +9098,7 @@
         <v>0.506408989429474</v>
       </c>
       <c r="G301" t="n">
-        <v>0.467145621776581</v>
+        <v>0.467145651578903</v>
       </c>
       <c r="H301" t="n">
         <v>1481695</v>
@@ -9185,7 +9185,7 @@
         <v>0.529905021190643</v>
       </c>
       <c r="G304" t="n">
-        <v>0.48881995677948</v>
+        <v>0.488819897174835</v>
       </c>
       <c r="H304" t="n">
         <v>1764261</v>
@@ -9446,7 +9446,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G313" t="n">
-        <v>0.531245172023773</v>
+        <v>0.531245112419128</v>
       </c>
       <c r="H313" t="n">
         <v>1840311</v>
@@ -9504,7 +9504,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G315" t="n">
-        <v>0.521099805831909</v>
+        <v>0.521099865436554</v>
       </c>
       <c r="H315" t="n">
         <v>1732441</v>
@@ -9562,7 +9562,7 @@
         <v>0.593892991542816</v>
       </c>
       <c r="G317" t="n">
-        <v>0.547846734523773</v>
+        <v>0.547846794128418</v>
       </c>
       <c r="H317" t="n">
         <v>846434</v>
@@ -9591,7 +9591,7 @@
         <v>0.588393986225128</v>
       </c>
       <c r="G318" t="n">
-        <v>0.542774140834808</v>
+        <v>0.542774081230164</v>
       </c>
       <c r="H318" t="n">
         <v>750114</v>
@@ -9823,7 +9823,7 @@
         <v>0.646384000778198</v>
       </c>
       <c r="G326" t="n">
-        <v>0.596267938613892</v>
+        <v>0.596267998218536</v>
       </c>
       <c r="H326" t="n">
         <v>478574</v>
@@ -10084,7 +10084,7 @@
         <v>0.687875986099243</v>
       </c>
       <c r="G335" t="n">
-        <v>0.634543001651764</v>
+        <v>0.634542942047119</v>
       </c>
       <c r="H335" t="n">
         <v>2493902</v>
@@ -10287,7 +10287,7 @@
         <v>0.667879998683929</v>
       </c>
       <c r="G342" t="n">
-        <v>0.616097271442413</v>
+        <v>0.616097331047058</v>
       </c>
       <c r="H342" t="n">
         <v>1809999</v>
@@ -10316,7 +10316,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G343" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H343" t="n">
         <v>1199670</v>
@@ -10345,7 +10345,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G344" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H344" t="n">
         <v>1226901</v>
@@ -10403,7 +10403,7 @@
         <v>0.680877983570099</v>
       </c>
       <c r="G346" t="n">
-        <v>0.628087520599365</v>
+        <v>0.62808758020401</v>
       </c>
       <c r="H346" t="n">
         <v>1835882</v>
@@ -10461,7 +10461,7 @@
         <v>0.669879972934723</v>
       </c>
       <c r="G348" t="n">
-        <v>0.617942273616791</v>
+        <v>0.617942214012146</v>
       </c>
       <c r="H348" t="n">
         <v>976577</v>
@@ -10635,7 +10635,7 @@
         <v>0.658882021903992</v>
       </c>
       <c r="G354" t="n">
-        <v>0.607796967029572</v>
+        <v>0.607797026634216</v>
       </c>
       <c r="H354" t="n">
         <v>1281515</v>
@@ -10809,7 +10809,7 @@
         <v>0.660880982875824</v>
       </c>
       <c r="G360" t="n">
-        <v>0.609641015529633</v>
+        <v>0.609640955924988</v>
       </c>
       <c r="H360" t="n">
         <v>434952</v>
@@ -10838,7 +10838,7 @@
         <v>0.660381019115448</v>
       </c>
       <c r="G361" t="n">
-        <v>0.609179735183716</v>
+        <v>0.609179794788361</v>
       </c>
       <c r="H361" t="n">
         <v>498433</v>
@@ -80209,9 +80209,38 @@
         <v>0.754000008106232</v>
       </c>
       <c r="H2753" t="n">
-        <v>155531</v>
+        <v>155532</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.742999970912933</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.746999979019165</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.746999979019165</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>258569</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
